--- a/back/public/export/arquivo.xlsx
+++ b/back/public/export/arquivo.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7226" uniqueCount="7226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7224" uniqueCount="7224">
   <si>
     <t>id</t>
   </si>
@@ -12487,241 +12487,241 @@
     <t>GESTÃO DE ATIVOS INTANGÍVEIS NÃO FINANCEIROS</t>
   </si>
   <si>
+    <t>Gestão de instalações de esportes</t>
+  </si>
+  <si>
+    <t>GESTÃO DE INSTALAÇÕES DE ESPORTES</t>
+  </si>
+  <si>
+    <t>Gestão de redes de esgoto</t>
+  </si>
+  <si>
+    <t>GESTÃO DE REDES DE ESGOTO</t>
+  </si>
+  <si>
+    <t>Gestão de terminais aquaviários</t>
+  </si>
+  <si>
+    <t>GESTÃO DE TERMINAIS AQUAVIÁRIOS</t>
+  </si>
+  <si>
+    <t>Gestão e administração da propriedade imobiliária</t>
+  </si>
+  <si>
+    <t>GESTÃO E ADMINISTRAÇÃO DA PROPRIEDADE IMOBILIÁRIA</t>
+  </si>
+  <si>
+    <t>Gestão e manutenção de cemitérios</t>
+  </si>
+  <si>
+    <t>GESTÃO E MANUTENÇÃO DE CEMITÉRIOS</t>
+  </si>
+  <si>
+    <t>Ginástica - Ap</t>
+  </si>
+  <si>
+    <t>GINÁSTICA - AP</t>
+  </si>
+  <si>
+    <t>Ginástica Laboral Preventiva</t>
+  </si>
+  <si>
+    <t>GINÁSTICA LABORAL PREVENTIVA</t>
+  </si>
+  <si>
+    <t>Giz</t>
+  </si>
+  <si>
+    <t>GIZ</t>
+  </si>
+  <si>
+    <t>GPS - Aparelhos</t>
+  </si>
+  <si>
+    <t>GPS - APARELHOS</t>
+  </si>
+  <si>
+    <t>Grades</t>
+  </si>
+  <si>
+    <t>GRADES</t>
+  </si>
+  <si>
+    <t>Gráficas</t>
+  </si>
+  <si>
+    <t>GRÁFICAS</t>
+  </si>
+  <si>
+    <t>Gráficas - Art e Equip</t>
+  </si>
+  <si>
+    <t>GRÁFICAS - ART E EQUIP</t>
+  </si>
+  <si>
+    <t>Grama</t>
+  </si>
+  <si>
+    <t>GRAMA</t>
+  </si>
+  <si>
+    <t>Grama Sintética</t>
+  </si>
+  <si>
+    <t>GRAMA SINTÉTICA</t>
+  </si>
+  <si>
+    <t>Grampeadores</t>
+  </si>
+  <si>
+    <t>GRAMPEADORES</t>
+  </si>
+  <si>
+    <t>Grampeadores e Pregadores Pneumáticos</t>
+  </si>
+  <si>
+    <t>GRAMPEADORES E PREGADORES PNEUMÁTICOS</t>
+  </si>
+  <si>
+    <t>Grampos</t>
+  </si>
+  <si>
+    <t>GRAMPOS</t>
+  </si>
+  <si>
+    <t>Granito</t>
+  </si>
+  <si>
+    <t>GRANITO</t>
+  </si>
+  <si>
+    <t>Granjas</t>
+  </si>
+  <si>
+    <t>GRANJAS</t>
+  </si>
+  <si>
+    <t>Gravação em Chapas Metálicas</t>
+  </si>
+  <si>
+    <t>GRAVAÇÃO EM CHAPAS METÁLICAS</t>
+  </si>
+  <si>
+    <t>Gravação Pantográfica</t>
+  </si>
+  <si>
+    <t>GRAVAÇÃO PANTOGRÁFICA</t>
+  </si>
+  <si>
+    <t>GRAVADOR(A) DE CARIMBOS</t>
+  </si>
+  <si>
+    <t>Gravadores</t>
+  </si>
+  <si>
+    <t>GRAVADORES</t>
+  </si>
+  <si>
+    <t>Grelhados (Restaurantes)</t>
+  </si>
+  <si>
+    <t>GRELHADOS (RESTAURANTES)</t>
+  </si>
+  <si>
+    <t>Grupos Geradores</t>
+  </si>
+  <si>
+    <t>GRUPOS GERADORES</t>
+  </si>
+  <si>
+    <t>Guaraná</t>
+  </si>
+  <si>
+    <t>GUARANÁ</t>
+  </si>
+  <si>
+    <t>Guarda-Chuvas</t>
+  </si>
+  <si>
+    <t>GUARDA-CHUVAS</t>
+  </si>
+  <si>
+    <t>Guarda-Documentos</t>
+  </si>
+  <si>
+    <t>GUARDA-DOCUMENTOS</t>
+  </si>
+  <si>
+    <t>Guarda-Móveis</t>
+  </si>
+  <si>
+    <t>GUARDA-MÓVEIS</t>
+  </si>
+  <si>
+    <t>Guarda-móveis</t>
+  </si>
+  <si>
+    <t>Guarda-Sóis</t>
+  </si>
+  <si>
+    <t>GUARDA-SÓIS</t>
+  </si>
+  <si>
+    <t>Guarda-Volumes</t>
+  </si>
+  <si>
+    <t>GUARDA-VOLUMES</t>
+  </si>
+  <si>
+    <t>GUARDADOR(A) DE MÓVEIS</t>
+  </si>
+  <si>
+    <t>GUIA DE TURISMO</t>
+  </si>
+  <si>
+    <t>Guilhotinas</t>
+  </si>
+  <si>
+    <t>GUILHOTINAS</t>
+  </si>
+  <si>
+    <t>GUINCHEIRO INDEPENDENTE - REBOQUE DE VEÍCULOS</t>
+  </si>
+  <si>
+    <t>Guinchos</t>
+  </si>
+  <si>
+    <t>GUINCHOS</t>
+  </si>
+  <si>
+    <t>Guinchos - Fab e Manutenção</t>
+  </si>
+  <si>
+    <t>GUINCHOS - FAB E MANUTENÇÃO</t>
+  </si>
+  <si>
+    <t>Guindastes</t>
+  </si>
+  <si>
+    <t>GUINDASTES</t>
+  </si>
+  <si>
+    <t>Guindastes - Conserto e Peças</t>
+  </si>
+  <si>
+    <t>GUINDASTES - CONSERTO E PEÇAS</t>
+  </si>
+  <si>
+    <t>Guindastes - Fab</t>
+  </si>
+  <si>
+    <t>GUINDASTES - FAB</t>
+  </si>
+  <si>
     <t>Gestão de espaços para artes cênicas, espetáculos e outras atividades artísticas</t>
   </si>
   <si>
-    <t>GESTÃO DE ESPAÇOS PARA ARTES CÊNICAS, ESPETÁCULOS E OUTRAS ATIVIDADES ARTÍSTICAS</t>
-  </si>
-  <si>
-    <t>Gestão de instalações de esportes</t>
-  </si>
-  <si>
-    <t>GESTÃO DE INSTALAÇÕES DE ESPORTES</t>
-  </si>
-  <si>
-    <t>Gestão de redes de esgoto</t>
-  </si>
-  <si>
-    <t>GESTÃO DE REDES DE ESGOTO</t>
-  </si>
-  <si>
-    <t>Gestão de terminais aquaviários</t>
-  </si>
-  <si>
-    <t>GESTÃO DE TERMINAIS AQUAVIÁRIOS</t>
-  </si>
-  <si>
-    <t>Gestão e administração da propriedade imobiliária</t>
-  </si>
-  <si>
-    <t>GESTÃO E ADMINISTRAÇÃO DA PROPRIEDADE IMOBILIÁRIA</t>
-  </si>
-  <si>
-    <t>Gestão e manutenção de cemitérios</t>
-  </si>
-  <si>
-    <t>GESTÃO E MANUTENÇÃO DE CEMITÉRIOS</t>
-  </si>
-  <si>
-    <t>Ginástica - Ap</t>
-  </si>
-  <si>
-    <t>GINÁSTICA - AP</t>
-  </si>
-  <si>
-    <t>Ginástica Laboral Preventiva</t>
-  </si>
-  <si>
-    <t>GINÁSTICA LABORAL PREVENTIVA</t>
-  </si>
-  <si>
-    <t>Giz</t>
-  </si>
-  <si>
-    <t>GIZ</t>
-  </si>
-  <si>
-    <t>GPS - Aparelhos</t>
-  </si>
-  <si>
-    <t>GPS - APARELHOS</t>
-  </si>
-  <si>
-    <t>Grades</t>
-  </si>
-  <si>
-    <t>GRADES</t>
-  </si>
-  <si>
-    <t>Gráficas</t>
-  </si>
-  <si>
-    <t>GRÁFICAS</t>
-  </si>
-  <si>
-    <t>Gráficas - Art e Equip</t>
-  </si>
-  <si>
-    <t>GRÁFICAS - ART E EQUIP</t>
-  </si>
-  <si>
-    <t>Grama</t>
-  </si>
-  <si>
-    <t>GRAMA</t>
-  </si>
-  <si>
-    <t>Grama Sintética</t>
-  </si>
-  <si>
-    <t>GRAMA SINTÉTICA</t>
-  </si>
-  <si>
-    <t>Grampeadores</t>
-  </si>
-  <si>
-    <t>GRAMPEADORES</t>
-  </si>
-  <si>
-    <t>Grampeadores e Pregadores Pneumáticos</t>
-  </si>
-  <si>
-    <t>GRAMPEADORES E PREGADORES PNEUMÁTICOS</t>
-  </si>
-  <si>
-    <t>Grampos</t>
-  </si>
-  <si>
-    <t>GRAMPOS</t>
-  </si>
-  <si>
-    <t>Granito</t>
-  </si>
-  <si>
-    <t>GRANITO</t>
-  </si>
-  <si>
-    <t>Granjas</t>
-  </si>
-  <si>
-    <t>GRANJAS</t>
-  </si>
-  <si>
-    <t>Gravação em Chapas Metálicas</t>
-  </si>
-  <si>
-    <t>GRAVAÇÃO EM CHAPAS METÁLICAS</t>
-  </si>
-  <si>
-    <t>Gravação Pantográfica</t>
-  </si>
-  <si>
-    <t>GRAVAÇÃO PANTOGRÁFICA</t>
-  </si>
-  <si>
-    <t>GRAVADOR(A) DE CARIMBOS</t>
-  </si>
-  <si>
-    <t>Gravadores</t>
-  </si>
-  <si>
-    <t>GRAVADORES</t>
-  </si>
-  <si>
-    <t>Grelhados (Restaurantes)</t>
-  </si>
-  <si>
-    <t>GRELHADOS (RESTAURANTES)</t>
-  </si>
-  <si>
-    <t>Grupos Geradores</t>
-  </si>
-  <si>
-    <t>GRUPOS GERADORES</t>
-  </si>
-  <si>
-    <t>Guaraná</t>
-  </si>
-  <si>
-    <t>GUARANÁ</t>
-  </si>
-  <si>
-    <t>Guarda-Chuvas</t>
-  </si>
-  <si>
-    <t>GUARDA-CHUVAS</t>
-  </si>
-  <si>
-    <t>Guarda-Documentos</t>
-  </si>
-  <si>
-    <t>GUARDA-DOCUMENTOS</t>
-  </si>
-  <si>
-    <t>Guarda-Móveis</t>
-  </si>
-  <si>
-    <t>GUARDA-MÓVEIS</t>
-  </si>
-  <si>
-    <t>Guarda-móveis</t>
-  </si>
-  <si>
-    <t>Guarda-Sóis</t>
-  </si>
-  <si>
-    <t>GUARDA-SÓIS</t>
-  </si>
-  <si>
-    <t>Guarda-Volumes</t>
-  </si>
-  <si>
-    <t>GUARDA-VOLUMES</t>
-  </si>
-  <si>
-    <t>GUARDADOR(A) DE MÓVEIS</t>
-  </si>
-  <si>
-    <t>GUIA DE TURISMO</t>
-  </si>
-  <si>
-    <t>Guilhotinas</t>
-  </si>
-  <si>
-    <t>GUILHOTINAS</t>
-  </si>
-  <si>
-    <t>GUINCHEIRO INDEPENDENTE - REBOQUE DE VEÍCULOS</t>
-  </si>
-  <si>
-    <t>Guinchos</t>
-  </si>
-  <si>
-    <t>GUINCHOS</t>
-  </si>
-  <si>
-    <t>Guinchos - Fab e Manutenção</t>
-  </si>
-  <si>
-    <t>GUINCHOS - FAB E MANUTENÇÃO</t>
-  </si>
-  <si>
-    <t>Guindastes</t>
-  </si>
-  <si>
-    <t>GUINDASTES</t>
-  </si>
-  <si>
-    <t>Guindastes - Conserto e Peças</t>
-  </si>
-  <si>
-    <t>GUINDASTES - CONSERTO E PEÇAS</t>
-  </si>
-  <si>
-    <t>Guindastes - Fab</t>
-  </si>
-  <si>
-    <t>GUINDASTES - FAB</t>
+    <t>TEATROS1</t>
   </si>
   <si>
     <t>Hamburguerias</t>
@@ -18994,6 +18994,9 @@
     <t>ROUPAS UNISSEX - LOJAS</t>
   </si>
   <si>
+    <t>Serviços advocatícios</t>
+  </si>
+  <si>
     <t>Serviços de arquitetura</t>
   </si>
   <si>
@@ -19426,12 +19429,6 @@
     <t>SERVIÇO MÓVEL ESPECIALIZADO - SME</t>
   </si>
   <si>
-    <t>Serviços advocatícios</t>
-  </si>
-  <si>
-    <t>SERVIÇOS ADVOCATÍCIOS</t>
-  </si>
-  <si>
     <t>Serviços ambulantes de alimentação</t>
   </si>
   <si>
@@ -20188,6 +20185,9 @@
     <t>SURF - ART E EQUIP</t>
   </si>
   <si>
+    <t>Teatros</t>
+  </si>
+  <si>
     <t>Tabacaria</t>
   </si>
   <si>
@@ -20306,12 +20306,6 @@
   </si>
   <si>
     <t>TEAR MANUAL</t>
-  </si>
-  <si>
-    <t>Teatros</t>
-  </si>
-  <si>
-    <t>TEATROS</t>
   </si>
   <si>
     <t>Tecelagem de fios de algodão</t>
@@ -52119,7 +52113,7 @@
     </row>
     <row r="2171" spans="1:4">
       <c r="A2171" s="0" t="n">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="B2171" s="0" t="s">
         <v>4158</v>
@@ -52133,7 +52127,7 @@
     </row>
     <row r="2172" spans="1:4">
       <c r="A2172" s="0" t="n">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B2172" s="0" t="s">
         <v>4160</v>
@@ -52147,7 +52141,7 @@
     </row>
     <row r="2173" spans="1:4">
       <c r="A2173" s="0" t="n">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="B2173" s="0" t="s">
         <v>4162</v>
@@ -52161,7 +52155,7 @@
     </row>
     <row r="2174" spans="1:4">
       <c r="A2174" s="0" t="n">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="B2174" s="0" t="s">
         <v>4164</v>
@@ -52175,7 +52169,7 @@
     </row>
     <row r="2175" spans="1:4">
       <c r="A2175" s="0" t="n">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B2175" s="0" t="s">
         <v>4166</v>
@@ -52189,7 +52183,7 @@
     </row>
     <row r="2176" spans="1:4">
       <c r="A2176" s="0" t="n">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="B2176" s="0" t="s">
         <v>4168</v>
@@ -52203,7 +52197,7 @@
     </row>
     <row r="2177" spans="1:4">
       <c r="A2177" s="0" t="n">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="B2177" s="0" t="s">
         <v>4170</v>
@@ -52217,7 +52211,7 @@
     </row>
     <row r="2178" spans="1:4">
       <c r="A2178" s="0" t="n">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="B2178" s="0" t="s">
         <v>4172</v>
@@ -52231,7 +52225,7 @@
     </row>
     <row r="2179" spans="1:4">
       <c r="A2179" s="0" t="n">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="B2179" s="0" t="s">
         <v>4174</v>
@@ -52245,7 +52239,7 @@
     </row>
     <row r="2180" spans="1:4">
       <c r="A2180" s="0" t="n">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="B2180" s="0" t="s">
         <v>4176</v>
@@ -52259,7 +52253,7 @@
     </row>
     <row r="2181" spans="1:4">
       <c r="A2181" s="0" t="n">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="B2181" s="0" t="s">
         <v>4178</v>
@@ -52273,7 +52267,7 @@
     </row>
     <row r="2182" spans="1:4">
       <c r="A2182" s="0" t="n">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B2182" s="0" t="s">
         <v>4180</v>
@@ -52287,7 +52281,7 @@
     </row>
     <row r="2183" spans="1:4">
       <c r="A2183" s="0" t="n">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="B2183" s="0" t="s">
         <v>4182</v>
@@ -52301,7 +52295,7 @@
     </row>
     <row r="2184" spans="1:4">
       <c r="A2184" s="0" t="n">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="B2184" s="0" t="s">
         <v>4184</v>
@@ -52315,7 +52309,7 @@
     </row>
     <row r="2185" spans="1:4">
       <c r="A2185" s="0" t="n">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="B2185" s="0" t="s">
         <v>4186</v>
@@ -52329,7 +52323,7 @@
     </row>
     <row r="2186" spans="1:4">
       <c r="A2186" s="0" t="n">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="B2186" s="0" t="s">
         <v>4188</v>
@@ -52343,7 +52337,7 @@
     </row>
     <row r="2187" spans="1:4">
       <c r="A2187" s="0" t="n">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B2187" s="0" t="s">
         <v>4190</v>
@@ -52357,7 +52351,7 @@
     </row>
     <row r="2188" spans="1:4">
       <c r="A2188" s="0" t="n">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="B2188" s="0" t="s">
         <v>4192</v>
@@ -52371,7 +52365,7 @@
     </row>
     <row r="2189" spans="1:4">
       <c r="A2189" s="0" t="n">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="B2189" s="0" t="s">
         <v>4194</v>
@@ -52385,7 +52379,7 @@
     </row>
     <row r="2190" spans="1:4">
       <c r="A2190" s="0" t="n">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B2190" s="0" t="s">
         <v>4196</v>
@@ -52399,7 +52393,7 @@
     </row>
     <row r="2191" spans="1:4">
       <c r="A2191" s="0" t="n">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="B2191" s="0" t="s">
         <v>4198</v>
@@ -52413,13 +52407,13 @@
     </row>
     <row r="2192" spans="1:4">
       <c r="A2192" s="0" t="n">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="B2192" s="0" t="s">
         <v>4200</v>
       </c>
       <c r="C2192" s="0" t="s">
-        <v>4201</v>
+        <v>4200</v>
       </c>
       <c r="D2192" s="0" t="s">
         <v>15</v>
@@ -52427,10 +52421,10 @@
     </row>
     <row r="2193" spans="1:4">
       <c r="A2193" s="0" t="n">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B2193" s="0" t="s">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="C2193" s="0" t="s">
         <v>4202</v>
@@ -52441,7 +52435,7 @@
     </row>
     <row r="2194" spans="1:4">
       <c r="A2194" s="0" t="n">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="B2194" s="0" t="s">
         <v>4203</v>
@@ -52455,7 +52449,7 @@
     </row>
     <row r="2195" spans="1:4">
       <c r="A2195" s="0" t="n">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="B2195" s="0" t="s">
         <v>4205</v>
@@ -52469,7 +52463,7 @@
     </row>
     <row r="2196" spans="1:4">
       <c r="A2196" s="0" t="n">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="B2196" s="0" t="s">
         <v>4207</v>
@@ -52483,7 +52477,7 @@
     </row>
     <row r="2197" spans="1:4">
       <c r="A2197" s="0" t="n">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="B2197" s="0" t="s">
         <v>4209</v>
@@ -52497,7 +52491,7 @@
     </row>
     <row r="2198" spans="1:4">
       <c r="A2198" s="0" t="n">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="B2198" s="0" t="s">
         <v>4211</v>
@@ -52511,7 +52505,7 @@
     </row>
     <row r="2199" spans="1:4">
       <c r="A2199" s="0" t="n">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B2199" s="0" t="s">
         <v>4213</v>
@@ -52525,13 +52519,13 @@
     </row>
     <row r="2200" spans="1:4">
       <c r="A2200" s="0" t="n">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B2200" s="0" t="s">
         <v>4215</v>
       </c>
       <c r="C2200" s="0" t="s">
-        <v>4216</v>
+        <v>4214</v>
       </c>
       <c r="D2200" s="0" t="s">
         <v>15</v>
@@ -52539,13 +52533,13 @@
     </row>
     <row r="2201" spans="1:4">
       <c r="A2201" s="0" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B2201" s="0" t="s">
+        <v>4216</v>
+      </c>
+      <c r="C2201" s="0" t="s">
         <v>4217</v>
-      </c>
-      <c r="C2201" s="0" t="s">
-        <v>4216</v>
       </c>
       <c r="D2201" s="0" t="s">
         <v>15</v>
@@ -52553,7 +52547,7 @@
     </row>
     <row r="2202" spans="1:4">
       <c r="A2202" s="0" t="n">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="B2202" s="0" t="s">
         <v>4218</v>
@@ -52567,13 +52561,13 @@
     </row>
     <row r="2203" spans="1:4">
       <c r="A2203" s="0" t="n">
-        <v>2206</v>
+        <v>2202</v>
       </c>
       <c r="B2203" s="0" t="s">
         <v>4220</v>
       </c>
       <c r="C2203" s="0" t="s">
-        <v>4221</v>
+        <v>4220</v>
       </c>
       <c r="D2203" s="0" t="s">
         <v>15</v>
@@ -52581,13 +52575,13 @@
     </row>
     <row r="2204" spans="1:4">
       <c r="A2204" s="0" t="n">
-        <v>2202</v>
+        <v>2207</v>
       </c>
       <c r="B2204" s="0" t="s">
-        <v>4222</v>
+        <v>4221</v>
       </c>
       <c r="C2204" s="0" t="s">
-        <v>4222</v>
+        <v>4221</v>
       </c>
       <c r="D2204" s="0" t="s">
         <v>15</v>
@@ -52595,10 +52589,10 @@
     </row>
     <row r="2205" spans="1:4">
       <c r="A2205" s="0" t="n">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B2205" s="0" t="s">
-        <v>4223</v>
+        <v>4222</v>
       </c>
       <c r="C2205" s="0" t="s">
         <v>4223</v>
@@ -52609,13 +52603,13 @@
     </row>
     <row r="2206" spans="1:4">
       <c r="A2206" s="0" t="n">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="B2206" s="0" t="s">
         <v>4224</v>
       </c>
       <c r="C2206" s="0" t="s">
-        <v>4225</v>
+        <v>4224</v>
       </c>
       <c r="D2206" s="0" t="s">
         <v>15</v>
@@ -52623,10 +52617,10 @@
     </row>
     <row r="2207" spans="1:4">
       <c r="A2207" s="0" t="n">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="B2207" s="0" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
       <c r="C2207" s="0" t="s">
         <v>4226</v>
@@ -52637,7 +52631,7 @@
     </row>
     <row r="2208" spans="1:4">
       <c r="A2208" s="0" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="B2208" s="0" t="s">
         <v>4227</v>
@@ -52651,7 +52645,7 @@
     </row>
     <row r="2209" spans="1:4">
       <c r="A2209" s="0" t="n">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B2209" s="0" t="s">
         <v>4229</v>
@@ -52665,7 +52659,7 @@
     </row>
     <row r="2210" spans="1:4">
       <c r="A2210" s="0" t="n">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="B2210" s="0" t="s">
         <v>4231</v>
@@ -52679,7 +52673,7 @@
     </row>
     <row r="2211" spans="1:4">
       <c r="A2211" s="0" t="n">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B2211" s="0" t="s">
         <v>4233</v>
@@ -52693,7 +52687,7 @@
     </row>
     <row r="2212" spans="1:4">
       <c r="A2212" s="0" t="n">
-        <v>2214</v>
+        <v>2173</v>
       </c>
       <c r="B2212" s="0" t="s">
         <v>4235</v>
@@ -68415,13 +68409,13 @@
     </row>
     <row r="3335" spans="1:4">
       <c r="A3335" s="0" t="n">
-        <v>3426</v>
+        <v>3416</v>
       </c>
       <c r="B3335" s="0" t="s">
         <v>6327</v>
       </c>
       <c r="C3335" s="0" t="s">
-        <v>6328</v>
+        <v>89</v>
       </c>
       <c r="D3335" s="0" t="s">
         <v>15</v>
@@ -68429,13 +68423,13 @@
     </row>
     <row r="3336" spans="1:4">
       <c r="A3336" s="0" t="n">
-        <v>3430</v>
+        <v>3426</v>
       </c>
       <c r="B3336" s="0" t="s">
+        <v>6328</v>
+      </c>
+      <c r="C3336" s="0" t="s">
         <v>6329</v>
-      </c>
-      <c r="C3336" s="0" t="s">
-        <v>6330</v>
       </c>
       <c r="D3336" s="0" t="s">
         <v>15</v>
@@ -68443,13 +68437,13 @@
     </row>
     <row r="3337" spans="1:4">
       <c r="A3337" s="0" t="n">
-        <v>3342</v>
+        <v>3430</v>
       </c>
       <c r="B3337" s="0" t="s">
+        <v>6330</v>
+      </c>
+      <c r="C3337" s="0" t="s">
         <v>6331</v>
-      </c>
-      <c r="C3337" s="0" t="s">
-        <v>6332</v>
       </c>
       <c r="D3337" s="0" t="s">
         <v>15</v>
@@ -68457,13 +68451,13 @@
     </row>
     <row r="3338" spans="1:4">
       <c r="A3338" s="0" t="n">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="B3338" s="0" t="s">
+        <v>6332</v>
+      </c>
+      <c r="C3338" s="0" t="s">
         <v>6333</v>
-      </c>
-      <c r="C3338" s="0" t="s">
-        <v>6334</v>
       </c>
       <c r="D3338" s="0" t="s">
         <v>15</v>
@@ -68471,13 +68465,13 @@
     </row>
     <row r="3339" spans="1:4">
       <c r="A3339" s="0" t="n">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="B3339" s="0" t="s">
+        <v>6334</v>
+      </c>
+      <c r="C3339" s="0" t="s">
         <v>6335</v>
-      </c>
-      <c r="C3339" s="0" t="s">
-        <v>6336</v>
       </c>
       <c r="D3339" s="0" t="s">
         <v>15</v>
@@ -68485,13 +68479,13 @@
     </row>
     <row r="3340" spans="1:4">
       <c r="A3340" s="0" t="n">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="B3340" s="0" t="s">
+        <v>6336</v>
+      </c>
+      <c r="C3340" s="0" t="s">
         <v>6337</v>
-      </c>
-      <c r="C3340" s="0" t="s">
-        <v>6338</v>
       </c>
       <c r="D3340" s="0" t="s">
         <v>15</v>
@@ -68499,13 +68493,13 @@
     </row>
     <row r="3341" spans="1:4">
       <c r="A3341" s="0" t="n">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="B3341" s="0" t="s">
+        <v>6338</v>
+      </c>
+      <c r="C3341" s="0" t="s">
         <v>6339</v>
-      </c>
-      <c r="C3341" s="0" t="s">
-        <v>6340</v>
       </c>
       <c r="D3341" s="0" t="s">
         <v>15</v>
@@ -68513,13 +68507,13 @@
     </row>
     <row r="3342" spans="1:4">
       <c r="A3342" s="0" t="n">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="B3342" s="0" t="s">
+        <v>6340</v>
+      </c>
+      <c r="C3342" s="0" t="s">
         <v>6341</v>
-      </c>
-      <c r="C3342" s="0" t="s">
-        <v>6342</v>
       </c>
       <c r="D3342" s="0" t="s">
         <v>15</v>
@@ -68527,13 +68521,13 @@
     </row>
     <row r="3343" spans="1:4">
       <c r="A3343" s="0" t="n">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="B3343" s="0" t="s">
+        <v>6342</v>
+      </c>
+      <c r="C3343" s="0" t="s">
         <v>6343</v>
-      </c>
-      <c r="C3343" s="0" t="s">
-        <v>6344</v>
       </c>
       <c r="D3343" s="0" t="s">
         <v>15</v>
@@ -68541,10 +68535,10 @@
     </row>
     <row r="3344" spans="1:4">
       <c r="A3344" s="0" t="n">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="B3344" s="0" t="s">
-        <v>6345</v>
+        <v>6344</v>
       </c>
       <c r="C3344" s="0" t="s">
         <v>6345</v>
@@ -68555,13 +68549,13 @@
     </row>
     <row r="3345" spans="1:4">
       <c r="A3345" s="0" t="n">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="B3345" s="0" t="s">
         <v>6346</v>
       </c>
       <c r="C3345" s="0" t="s">
-        <v>6347</v>
+        <v>6346</v>
       </c>
       <c r="D3345" s="0" t="s">
         <v>15</v>
@@ -68569,10 +68563,10 @@
     </row>
     <row r="3346" spans="1:4">
       <c r="A3346" s="0" t="n">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="B3346" s="0" t="s">
-        <v>6348</v>
+        <v>6347</v>
       </c>
       <c r="C3346" s="0" t="s">
         <v>6348</v>
@@ -68583,13 +68577,13 @@
     </row>
     <row r="3347" spans="1:4">
       <c r="A3347" s="0" t="n">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="B3347" s="0" t="s">
         <v>6349</v>
       </c>
       <c r="C3347" s="0" t="s">
-        <v>6350</v>
+        <v>6349</v>
       </c>
       <c r="D3347" s="0" t="s">
         <v>15</v>
@@ -68597,13 +68591,13 @@
     </row>
     <row r="3348" spans="1:4">
       <c r="A3348" s="0" t="n">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="B3348" s="0" t="s">
+        <v>6350</v>
+      </c>
+      <c r="C3348" s="0" t="s">
         <v>6351</v>
-      </c>
-      <c r="C3348" s="0" t="s">
-        <v>6352</v>
       </c>
       <c r="D3348" s="0" t="s">
         <v>15</v>
@@ -68611,10 +68605,10 @@
     </row>
     <row r="3349" spans="1:4">
       <c r="A3349" s="0" t="n">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="B3349" s="0" t="s">
-        <v>6353</v>
+        <v>6352</v>
       </c>
       <c r="C3349" s="0" t="s">
         <v>6353</v>
@@ -68625,13 +68619,13 @@
     </row>
     <row r="3350" spans="1:4">
       <c r="A3350" s="0" t="n">
-        <v>3356</v>
+        <v>3354</v>
       </c>
       <c r="B3350" s="0" t="s">
         <v>6354</v>
       </c>
       <c r="C3350" s="0" t="s">
-        <v>6355</v>
+        <v>6354</v>
       </c>
       <c r="D3350" s="0" t="s">
         <v>15</v>
@@ -68639,13 +68633,13 @@
     </row>
     <row r="3351" spans="1:4">
       <c r="A3351" s="0" t="n">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="B3351" s="0" t="s">
+        <v>6355</v>
+      </c>
+      <c r="C3351" s="0" t="s">
         <v>6356</v>
-      </c>
-      <c r="C3351" s="0" t="s">
-        <v>6357</v>
       </c>
       <c r="D3351" s="0" t="s">
         <v>15</v>
@@ -68653,13 +68647,13 @@
     </row>
     <row r="3352" spans="1:4">
       <c r="A3352" s="0" t="n">
-        <v>3357</v>
+        <v>3355</v>
       </c>
       <c r="B3352" s="0" t="s">
+        <v>6357</v>
+      </c>
+      <c r="C3352" s="0" t="s">
         <v>6358</v>
-      </c>
-      <c r="C3352" s="0" t="s">
-        <v>6359</v>
       </c>
       <c r="D3352" s="0" t="s">
         <v>15</v>
@@ -68667,13 +68661,13 @@
     </row>
     <row r="3353" spans="1:4">
       <c r="A3353" s="0" t="n">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="B3353" s="0" t="s">
+        <v>6359</v>
+      </c>
+      <c r="C3353" s="0" t="s">
         <v>6360</v>
-      </c>
-      <c r="C3353" s="0" t="s">
-        <v>6361</v>
       </c>
       <c r="D3353" s="0" t="s">
         <v>15</v>
@@ -68681,13 +68675,13 @@
     </row>
     <row r="3354" spans="1:4">
       <c r="A3354" s="0" t="n">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="B3354" s="0" t="s">
+        <v>6361</v>
+      </c>
+      <c r="C3354" s="0" t="s">
         <v>6362</v>
-      </c>
-      <c r="C3354" s="0" t="s">
-        <v>6363</v>
       </c>
       <c r="D3354" s="0" t="s">
         <v>15</v>
@@ -68695,13 +68689,13 @@
     </row>
     <row r="3355" spans="1:4">
       <c r="A3355" s="0" t="n">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="B3355" s="0" t="s">
+        <v>6363</v>
+      </c>
+      <c r="C3355" s="0" t="s">
         <v>6364</v>
-      </c>
-      <c r="C3355" s="0" t="s">
-        <v>6365</v>
       </c>
       <c r="D3355" s="0" t="s">
         <v>15</v>
@@ -68709,13 +68703,13 @@
     </row>
     <row r="3356" spans="1:4">
       <c r="A3356" s="0" t="n">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="B3356" s="0" t="s">
+        <v>6365</v>
+      </c>
+      <c r="C3356" s="0" t="s">
         <v>6366</v>
-      </c>
-      <c r="C3356" s="0" t="s">
-        <v>6367</v>
       </c>
       <c r="D3356" s="0" t="s">
         <v>15</v>
@@ -68723,10 +68717,10 @@
     </row>
     <row r="3357" spans="1:4">
       <c r="A3357" s="0" t="n">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="B3357" s="0" t="s">
-        <v>6368</v>
+        <v>6367</v>
       </c>
       <c r="C3357" s="0" t="s">
         <v>6368</v>
@@ -68737,13 +68731,13 @@
     </row>
     <row r="3358" spans="1:4">
       <c r="A3358" s="0" t="n">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="B3358" s="0" t="s">
         <v>6369</v>
       </c>
       <c r="C3358" s="0" t="s">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="D3358" s="0" t="s">
         <v>15</v>
@@ -68751,13 +68745,13 @@
     </row>
     <row r="3359" spans="1:4">
       <c r="A3359" s="0" t="n">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="B3359" s="0" t="s">
+        <v>6370</v>
+      </c>
+      <c r="C3359" s="0" t="s">
         <v>6371</v>
-      </c>
-      <c r="C3359" s="0" t="s">
-        <v>6372</v>
       </c>
       <c r="D3359" s="0" t="s">
         <v>15</v>
@@ -68765,13 +68759,13 @@
     </row>
     <row r="3360" spans="1:4">
       <c r="A3360" s="0" t="n">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B3360" s="0" t="s">
+        <v>6372</v>
+      </c>
+      <c r="C3360" s="0" t="s">
         <v>6373</v>
-      </c>
-      <c r="C3360" s="0" t="s">
-        <v>6374</v>
       </c>
       <c r="D3360" s="0" t="s">
         <v>15</v>
@@ -68779,13 +68773,13 @@
     </row>
     <row r="3361" spans="1:4">
       <c r="A3361" s="0" t="n">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="B3361" s="0" t="s">
+        <v>6374</v>
+      </c>
+      <c r="C3361" s="0" t="s">
         <v>6375</v>
-      </c>
-      <c r="C3361" s="0" t="s">
-        <v>6376</v>
       </c>
       <c r="D3361" s="0" t="s">
         <v>15</v>
@@ -68793,13 +68787,13 @@
     </row>
     <row r="3362" spans="1:4">
       <c r="A3362" s="0" t="n">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="B3362" s="0" t="s">
+        <v>6376</v>
+      </c>
+      <c r="C3362" s="0" t="s">
         <v>6377</v>
-      </c>
-      <c r="C3362" s="0" t="s">
-        <v>6378</v>
       </c>
       <c r="D3362" s="0" t="s">
         <v>15</v>
@@ -68807,13 +68801,13 @@
     </row>
     <row r="3363" spans="1:4">
       <c r="A3363" s="0" t="n">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="B3363" s="0" t="s">
+        <v>6378</v>
+      </c>
+      <c r="C3363" s="0" t="s">
         <v>6379</v>
-      </c>
-      <c r="C3363" s="0" t="s">
-        <v>6380</v>
       </c>
       <c r="D3363" s="0" t="s">
         <v>15</v>
@@ -68821,13 +68815,13 @@
     </row>
     <row r="3364" spans="1:4">
       <c r="A3364" s="0" t="n">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="B3364" s="0" t="s">
+        <v>6380</v>
+      </c>
+      <c r="C3364" s="0" t="s">
         <v>6381</v>
-      </c>
-      <c r="C3364" s="0" t="s">
-        <v>6382</v>
       </c>
       <c r="D3364" s="0" t="s">
         <v>15</v>
@@ -68835,13 +68829,13 @@
     </row>
     <row r="3365" spans="1:4">
       <c r="A3365" s="0" t="n">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="B3365" s="0" t="s">
+        <v>6382</v>
+      </c>
+      <c r="C3365" s="0" t="s">
         <v>6383</v>
-      </c>
-      <c r="C3365" s="0" t="s">
-        <v>6384</v>
       </c>
       <c r="D3365" s="0" t="s">
         <v>15</v>
@@ -68849,13 +68843,13 @@
     </row>
     <row r="3366" spans="1:4">
       <c r="A3366" s="0" t="n">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="B3366" s="0" t="s">
+        <v>6384</v>
+      </c>
+      <c r="C3366" s="0" t="s">
         <v>6385</v>
-      </c>
-      <c r="C3366" s="0" t="s">
-        <v>6386</v>
       </c>
       <c r="D3366" s="0" t="s">
         <v>15</v>
@@ -68863,13 +68857,13 @@
     </row>
     <row r="3367" spans="1:4">
       <c r="A3367" s="0" t="n">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="B3367" s="0" t="s">
+        <v>6386</v>
+      </c>
+      <c r="C3367" s="0" t="s">
         <v>6387</v>
-      </c>
-      <c r="C3367" s="0" t="s">
-        <v>6388</v>
       </c>
       <c r="D3367" s="0" t="s">
         <v>15</v>
@@ -68877,13 +68871,13 @@
     </row>
     <row r="3368" spans="1:4">
       <c r="A3368" s="0" t="n">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="B3368" s="0" t="s">
+        <v>6388</v>
+      </c>
+      <c r="C3368" s="0" t="s">
         <v>6389</v>
-      </c>
-      <c r="C3368" s="0" t="s">
-        <v>6390</v>
       </c>
       <c r="D3368" s="0" t="s">
         <v>15</v>
@@ -68891,13 +68885,13 @@
     </row>
     <row r="3369" spans="1:4">
       <c r="A3369" s="0" t="n">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="B3369" s="0" t="s">
+        <v>6390</v>
+      </c>
+      <c r="C3369" s="0" t="s">
         <v>6391</v>
-      </c>
-      <c r="C3369" s="0" t="s">
-        <v>6392</v>
       </c>
       <c r="D3369" s="0" t="s">
         <v>15</v>
@@ -68905,13 +68899,13 @@
     </row>
     <row r="3370" spans="1:4">
       <c r="A3370" s="0" t="n">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="B3370" s="0" t="s">
+        <v>6392</v>
+      </c>
+      <c r="C3370" s="0" t="s">
         <v>6393</v>
-      </c>
-      <c r="C3370" s="0" t="s">
-        <v>6394</v>
       </c>
       <c r="D3370" s="0" t="s">
         <v>15</v>
@@ -68919,13 +68913,13 @@
     </row>
     <row r="3371" spans="1:4">
       <c r="A3371" s="0" t="n">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="B3371" s="0" t="s">
+        <v>6394</v>
+      </c>
+      <c r="C3371" s="0" t="s">
         <v>6395</v>
-      </c>
-      <c r="C3371" s="0" t="s">
-        <v>6396</v>
       </c>
       <c r="D3371" s="0" t="s">
         <v>15</v>
@@ -68933,13 +68927,13 @@
     </row>
     <row r="3372" spans="1:4">
       <c r="A3372" s="0" t="n">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="B3372" s="0" t="s">
+        <v>6396</v>
+      </c>
+      <c r="C3372" s="0" t="s">
         <v>6397</v>
-      </c>
-      <c r="C3372" s="0" t="s">
-        <v>6398</v>
       </c>
       <c r="D3372" s="0" t="s">
         <v>15</v>
@@ -68947,13 +68941,13 @@
     </row>
     <row r="3373" spans="1:4">
       <c r="A3373" s="0" t="n">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="B3373" s="0" t="s">
+        <v>6398</v>
+      </c>
+      <c r="C3373" s="0" t="s">
         <v>6399</v>
-      </c>
-      <c r="C3373" s="0" t="s">
-        <v>6400</v>
       </c>
       <c r="D3373" s="0" t="s">
         <v>15</v>
@@ -68961,13 +68955,13 @@
     </row>
     <row r="3374" spans="1:4">
       <c r="A3374" s="0" t="n">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="B3374" s="0" t="s">
+        <v>6400</v>
+      </c>
+      <c r="C3374" s="0" t="s">
         <v>6401</v>
-      </c>
-      <c r="C3374" s="0" t="s">
-        <v>6402</v>
       </c>
       <c r="D3374" s="0" t="s">
         <v>15</v>
@@ -68975,13 +68969,13 @@
     </row>
     <row r="3375" spans="1:4">
       <c r="A3375" s="0" t="n">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="B3375" s="0" t="s">
+        <v>6402</v>
+      </c>
+      <c r="C3375" s="0" t="s">
         <v>6403</v>
-      </c>
-      <c r="C3375" s="0" t="s">
-        <v>6404</v>
       </c>
       <c r="D3375" s="0" t="s">
         <v>15</v>
@@ -68989,13 +68983,13 @@
     </row>
     <row r="3376" spans="1:4">
       <c r="A3376" s="0" t="n">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="B3376" s="0" t="s">
+        <v>6404</v>
+      </c>
+      <c r="C3376" s="0" t="s">
         <v>6405</v>
-      </c>
-      <c r="C3376" s="0" t="s">
-        <v>6406</v>
       </c>
       <c r="D3376" s="0" t="s">
         <v>15</v>
@@ -69003,13 +68997,13 @@
     </row>
     <row r="3377" spans="1:4">
       <c r="A3377" s="0" t="n">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="B3377" s="0" t="s">
+        <v>6406</v>
+      </c>
+      <c r="C3377" s="0" t="s">
         <v>6407</v>
-      </c>
-      <c r="C3377" s="0" t="s">
-        <v>6408</v>
       </c>
       <c r="D3377" s="0" t="s">
         <v>15</v>
@@ -69017,13 +69011,13 @@
     </row>
     <row r="3378" spans="1:4">
       <c r="A3378" s="0" t="n">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="B3378" s="0" t="s">
+        <v>6408</v>
+      </c>
+      <c r="C3378" s="0" t="s">
         <v>6409</v>
-      </c>
-      <c r="C3378" s="0" t="s">
-        <v>6410</v>
       </c>
       <c r="D3378" s="0" t="s">
         <v>15</v>
@@ -69031,13 +69025,13 @@
     </row>
     <row r="3379" spans="1:4">
       <c r="A3379" s="0" t="n">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="B3379" s="0" t="s">
+        <v>6410</v>
+      </c>
+      <c r="C3379" s="0" t="s">
         <v>6411</v>
-      </c>
-      <c r="C3379" s="0" t="s">
-        <v>6412</v>
       </c>
       <c r="D3379" s="0" t="s">
         <v>15</v>
@@ -69045,13 +69039,13 @@
     </row>
     <row r="3380" spans="1:4">
       <c r="A3380" s="0" t="n">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="B3380" s="0" t="s">
+        <v>6412</v>
+      </c>
+      <c r="C3380" s="0" t="s">
         <v>6413</v>
-      </c>
-      <c r="C3380" s="0" t="s">
-        <v>6414</v>
       </c>
       <c r="D3380" s="0" t="s">
         <v>15</v>
@@ -69059,13 +69053,13 @@
     </row>
     <row r="3381" spans="1:4">
       <c r="A3381" s="0" t="n">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="B3381" s="0" t="s">
+        <v>6414</v>
+      </c>
+      <c r="C3381" s="0" t="s">
         <v>6415</v>
-      </c>
-      <c r="C3381" s="0" t="s">
-        <v>6416</v>
       </c>
       <c r="D3381" s="0" t="s">
         <v>15</v>
@@ -69073,10 +69067,10 @@
     </row>
     <row r="3382" spans="1:4">
       <c r="A3382" s="0" t="n">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="B3382" s="0" t="s">
-        <v>6417</v>
+        <v>6416</v>
       </c>
       <c r="C3382" s="0" t="s">
         <v>6417</v>
@@ -69087,13 +69081,13 @@
     </row>
     <row r="3383" spans="1:4">
       <c r="A3383" s="0" t="n">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="B3383" s="0" t="s">
         <v>6418</v>
       </c>
       <c r="C3383" s="0" t="s">
-        <v>6419</v>
+        <v>6418</v>
       </c>
       <c r="D3383" s="0" t="s">
         <v>15</v>
@@ -69101,13 +69095,13 @@
     </row>
     <row r="3384" spans="1:4">
       <c r="A3384" s="0" t="n">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="B3384" s="0" t="s">
+        <v>6419</v>
+      </c>
+      <c r="C3384" s="0" t="s">
         <v>6420</v>
-      </c>
-      <c r="C3384" s="0" t="s">
-        <v>6421</v>
       </c>
       <c r="D3384" s="0" t="s">
         <v>15</v>
@@ -69115,13 +69109,13 @@
     </row>
     <row r="3385" spans="1:4">
       <c r="A3385" s="0" t="n">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="B3385" s="0" t="s">
+        <v>6421</v>
+      </c>
+      <c r="C3385" s="0" t="s">
         <v>6422</v>
-      </c>
-      <c r="C3385" s="0" t="s">
-        <v>6423</v>
       </c>
       <c r="D3385" s="0" t="s">
         <v>15</v>
@@ -69129,13 +69123,13 @@
     </row>
     <row r="3386" spans="1:4">
       <c r="A3386" s="0" t="n">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="B3386" s="0" t="s">
+        <v>6423</v>
+      </c>
+      <c r="C3386" s="0" t="s">
         <v>6424</v>
-      </c>
-      <c r="C3386" s="0" t="s">
-        <v>6425</v>
       </c>
       <c r="D3386" s="0" t="s">
         <v>15</v>
@@ -69143,10 +69137,10 @@
     </row>
     <row r="3387" spans="1:4">
       <c r="A3387" s="0" t="n">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="B3387" s="0" t="s">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="C3387" s="0" t="s">
         <v>6426</v>
@@ -69157,7 +69151,7 @@
     </row>
     <row r="3388" spans="1:4">
       <c r="A3388" s="0" t="n">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="B3388" s="0" t="s">
         <v>6427</v>
@@ -69171,7 +69165,7 @@
     </row>
     <row r="3389" spans="1:4">
       <c r="A3389" s="0" t="n">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="B3389" s="0" t="s">
         <v>6428</v>
@@ -69185,13 +69179,13 @@
     </row>
     <row r="3390" spans="1:4">
       <c r="A3390" s="0" t="n">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B3390" s="0" t="s">
         <v>6429</v>
       </c>
       <c r="C3390" s="0" t="s">
-        <v>6430</v>
+        <v>6429</v>
       </c>
       <c r="D3390" s="0" t="s">
         <v>15</v>
@@ -69199,13 +69193,13 @@
     </row>
     <row r="3391" spans="1:4">
       <c r="A3391" s="0" t="n">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="B3391" s="0" t="s">
+        <v>6430</v>
+      </c>
+      <c r="C3391" s="0" t="s">
         <v>6431</v>
-      </c>
-      <c r="C3391" s="0" t="s">
-        <v>6432</v>
       </c>
       <c r="D3391" s="0" t="s">
         <v>15</v>
@@ -69213,13 +69207,13 @@
     </row>
     <row r="3392" spans="1:4">
       <c r="A3392" s="0" t="n">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="B3392" s="0" t="s">
+        <v>6432</v>
+      </c>
+      <c r="C3392" s="0" t="s">
         <v>6433</v>
-      </c>
-      <c r="C3392" s="0" t="s">
-        <v>6434</v>
       </c>
       <c r="D3392" s="0" t="s">
         <v>15</v>
@@ -69227,13 +69221,13 @@
     </row>
     <row r="3393" spans="1:4">
       <c r="A3393" s="0" t="n">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="B3393" s="0" t="s">
+        <v>6434</v>
+      </c>
+      <c r="C3393" s="0" t="s">
         <v>6435</v>
-      </c>
-      <c r="C3393" s="0" t="s">
-        <v>6436</v>
       </c>
       <c r="D3393" s="0" t="s">
         <v>15</v>
@@ -69241,13 +69235,13 @@
     </row>
     <row r="3394" spans="1:4">
       <c r="A3394" s="0" t="n">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="B3394" s="0" t="s">
+        <v>6436</v>
+      </c>
+      <c r="C3394" s="0" t="s">
         <v>6437</v>
-      </c>
-      <c r="C3394" s="0" t="s">
-        <v>6438</v>
       </c>
       <c r="D3394" s="0" t="s">
         <v>15</v>
@@ -69255,13 +69249,13 @@
     </row>
     <row r="3395" spans="1:4">
       <c r="A3395" s="0" t="n">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="B3395" s="0" t="s">
+        <v>6438</v>
+      </c>
+      <c r="C3395" s="0" t="s">
         <v>6439</v>
-      </c>
-      <c r="C3395" s="0" t="s">
-        <v>6440</v>
       </c>
       <c r="D3395" s="0" t="s">
         <v>15</v>
@@ -69269,13 +69263,13 @@
     </row>
     <row r="3396" spans="1:4">
       <c r="A3396" s="0" t="n">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="B3396" s="0" t="s">
+        <v>6440</v>
+      </c>
+      <c r="C3396" s="0" t="s">
         <v>6441</v>
-      </c>
-      <c r="C3396" s="0" t="s">
-        <v>6442</v>
       </c>
       <c r="D3396" s="0" t="s">
         <v>15</v>
@@ -69283,13 +69277,13 @@
     </row>
     <row r="3397" spans="1:4">
       <c r="A3397" s="0" t="n">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="B3397" s="0" t="s">
+        <v>6442</v>
+      </c>
+      <c r="C3397" s="0" t="s">
         <v>6443</v>
-      </c>
-      <c r="C3397" s="0" t="s">
-        <v>6444</v>
       </c>
       <c r="D3397" s="0" t="s">
         <v>15</v>
@@ -69297,13 +69291,13 @@
     </row>
     <row r="3398" spans="1:4">
       <c r="A3398" s="0" t="n">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="B3398" s="0" t="s">
+        <v>6444</v>
+      </c>
+      <c r="C3398" s="0" t="s">
         <v>6445</v>
-      </c>
-      <c r="C3398" s="0" t="s">
-        <v>6446</v>
       </c>
       <c r="D3398" s="0" t="s">
         <v>15</v>
@@ -69311,13 +69305,13 @@
     </row>
     <row r="3399" spans="1:4">
       <c r="A3399" s="0" t="n">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="B3399" s="0" t="s">
+        <v>6446</v>
+      </c>
+      <c r="C3399" s="0" t="s">
         <v>6447</v>
-      </c>
-      <c r="C3399" s="0" t="s">
-        <v>6448</v>
       </c>
       <c r="D3399" s="0" t="s">
         <v>15</v>
@@ -69325,13 +69319,13 @@
     </row>
     <row r="3400" spans="1:4">
       <c r="A3400" s="0" t="n">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B3400" s="0" t="s">
+        <v>6448</v>
+      </c>
+      <c r="C3400" s="0" t="s">
         <v>6449</v>
-      </c>
-      <c r="C3400" s="0" t="s">
-        <v>6450</v>
       </c>
       <c r="D3400" s="0" t="s">
         <v>15</v>
@@ -69339,13 +69333,13 @@
     </row>
     <row r="3401" spans="1:4">
       <c r="A3401" s="0" t="n">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B3401" s="0" t="s">
+        <v>6450</v>
+      </c>
+      <c r="C3401" s="0" t="s">
         <v>6451</v>
-      </c>
-      <c r="C3401" s="0" t="s">
-        <v>6452</v>
       </c>
       <c r="D3401" s="0" t="s">
         <v>15</v>
@@ -69353,13 +69347,13 @@
     </row>
     <row r="3402" spans="1:4">
       <c r="A3402" s="0" t="n">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B3402" s="0" t="s">
+        <v>6452</v>
+      </c>
+      <c r="C3402" s="0" t="s">
         <v>6453</v>
-      </c>
-      <c r="C3402" s="0" t="s">
-        <v>6454</v>
       </c>
       <c r="D3402" s="0" t="s">
         <v>15</v>
@@ -69367,13 +69361,13 @@
     </row>
     <row r="3403" spans="1:4">
       <c r="A3403" s="0" t="n">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B3403" s="0" t="s">
+        <v>6454</v>
+      </c>
+      <c r="C3403" s="0" t="s">
         <v>6455</v>
-      </c>
-      <c r="C3403" s="0" t="s">
-        <v>6456</v>
       </c>
       <c r="D3403" s="0" t="s">
         <v>15</v>
@@ -69381,13 +69375,13 @@
     </row>
     <row r="3404" spans="1:4">
       <c r="A3404" s="0" t="n">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B3404" s="0" t="s">
+        <v>6456</v>
+      </c>
+      <c r="C3404" s="0" t="s">
         <v>6457</v>
-      </c>
-      <c r="C3404" s="0" t="s">
-        <v>6458</v>
       </c>
       <c r="D3404" s="0" t="s">
         <v>15</v>
@@ -69395,13 +69389,13 @@
     </row>
     <row r="3405" spans="1:4">
       <c r="A3405" s="0" t="n">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B3405" s="0" t="s">
+        <v>6458</v>
+      </c>
+      <c r="C3405" s="0" t="s">
         <v>6459</v>
-      </c>
-      <c r="C3405" s="0" t="s">
-        <v>6460</v>
       </c>
       <c r="D3405" s="0" t="s">
         <v>15</v>
@@ -69409,13 +69403,13 @@
     </row>
     <row r="3406" spans="1:4">
       <c r="A3406" s="0" t="n">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B3406" s="0" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C3406" s="0" t="s">
         <v>6461</v>
-      </c>
-      <c r="C3406" s="0" t="s">
-        <v>6462</v>
       </c>
       <c r="D3406" s="0" t="s">
         <v>15</v>
@@ -69423,13 +69417,13 @@
     </row>
     <row r="3407" spans="1:4">
       <c r="A3407" s="0" t="n">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B3407" s="0" t="s">
+        <v>6462</v>
+      </c>
+      <c r="C3407" s="0" t="s">
         <v>6463</v>
-      </c>
-      <c r="C3407" s="0" t="s">
-        <v>6464</v>
       </c>
       <c r="D3407" s="0" t="s">
         <v>15</v>
@@ -69437,13 +69431,13 @@
     </row>
     <row r="3408" spans="1:4">
       <c r="A3408" s="0" t="n">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B3408" s="0" t="s">
+        <v>6464</v>
+      </c>
+      <c r="C3408" s="0" t="s">
         <v>6465</v>
-      </c>
-      <c r="C3408" s="0" t="s">
-        <v>6466</v>
       </c>
       <c r="D3408" s="0" t="s">
         <v>15</v>
@@ -69451,13 +69445,13 @@
     </row>
     <row r="3409" spans="1:4">
       <c r="A3409" s="0" t="n">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B3409" s="0" t="s">
+        <v>6466</v>
+      </c>
+      <c r="C3409" s="0" t="s">
         <v>6467</v>
-      </c>
-      <c r="C3409" s="0" t="s">
-        <v>6468</v>
       </c>
       <c r="D3409" s="0" t="s">
         <v>15</v>
@@ -69465,13 +69459,13 @@
     </row>
     <row r="3410" spans="1:4">
       <c r="A3410" s="0" t="n">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B3410" s="0" t="s">
+        <v>6468</v>
+      </c>
+      <c r="C3410" s="0" t="s">
         <v>6469</v>
-      </c>
-      <c r="C3410" s="0" t="s">
-        <v>6470</v>
       </c>
       <c r="D3410" s="0" t="s">
         <v>15</v>
@@ -69479,13 +69473,13 @@
     </row>
     <row r="3411" spans="1:4">
       <c r="A3411" s="0" t="n">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B3411" s="0" t="s">
+        <v>6470</v>
+      </c>
+      <c r="C3411" s="0" t="s">
         <v>6471</v>
-      </c>
-      <c r="C3411" s="0" t="s">
-        <v>6472</v>
       </c>
       <c r="D3411" s="0" t="s">
         <v>15</v>
@@ -69496,10 +69490,10 @@
         <v>3417</v>
       </c>
       <c r="B3412" s="0" t="s">
+        <v>6472</v>
+      </c>
+      <c r="C3412" s="0" t="s">
         <v>6473</v>
-      </c>
-      <c r="C3412" s="0" t="s">
-        <v>6474</v>
       </c>
       <c r="D3412" s="0" t="s">
         <v>15</v>
@@ -69510,10 +69504,10 @@
         <v>3418</v>
       </c>
       <c r="B3413" s="0" t="s">
+        <v>6474</v>
+      </c>
+      <c r="C3413" s="0" t="s">
         <v>6475</v>
-      </c>
-      <c r="C3413" s="0" t="s">
-        <v>6476</v>
       </c>
       <c r="D3413" s="0" t="s">
         <v>15</v>
@@ -69524,10 +69518,10 @@
         <v>3419</v>
       </c>
       <c r="B3414" s="0" t="s">
+        <v>6476</v>
+      </c>
+      <c r="C3414" s="0" t="s">
         <v>6477</v>
-      </c>
-      <c r="C3414" s="0" t="s">
-        <v>6478</v>
       </c>
       <c r="D3414" s="0" t="s">
         <v>15</v>
@@ -69538,10 +69532,10 @@
         <v>3420</v>
       </c>
       <c r="B3415" s="0" t="s">
+        <v>6478</v>
+      </c>
+      <c r="C3415" s="0" t="s">
         <v>6479</v>
-      </c>
-      <c r="C3415" s="0" t="s">
-        <v>6480</v>
       </c>
       <c r="D3415" s="0" t="s">
         <v>15</v>
@@ -69552,10 +69546,10 @@
         <v>3421</v>
       </c>
       <c r="B3416" s="0" t="s">
+        <v>6480</v>
+      </c>
+      <c r="C3416" s="0" t="s">
         <v>6481</v>
-      </c>
-      <c r="C3416" s="0" t="s">
-        <v>6482</v>
       </c>
       <c r="D3416" s="0" t="s">
         <v>15</v>
@@ -69566,10 +69560,10 @@
         <v>3422</v>
       </c>
       <c r="B3417" s="0" t="s">
+        <v>6482</v>
+      </c>
+      <c r="C3417" s="0" t="s">
         <v>6483</v>
-      </c>
-      <c r="C3417" s="0" t="s">
-        <v>6484</v>
       </c>
       <c r="D3417" s="0" t="s">
         <v>15</v>
@@ -69580,10 +69574,10 @@
         <v>3423</v>
       </c>
       <c r="B3418" s="0" t="s">
+        <v>6484</v>
+      </c>
+      <c r="C3418" s="0" t="s">
         <v>6485</v>
-      </c>
-      <c r="C3418" s="0" t="s">
-        <v>6486</v>
       </c>
       <c r="D3418" s="0" t="s">
         <v>15</v>
@@ -69594,10 +69588,10 @@
         <v>3424</v>
       </c>
       <c r="B3419" s="0" t="s">
+        <v>6486</v>
+      </c>
+      <c r="C3419" s="0" t="s">
         <v>6487</v>
-      </c>
-      <c r="C3419" s="0" t="s">
-        <v>6488</v>
       </c>
       <c r="D3419" s="0" t="s">
         <v>15</v>
@@ -69608,10 +69602,10 @@
         <v>3425</v>
       </c>
       <c r="B3420" s="0" t="s">
+        <v>6488</v>
+      </c>
+      <c r="C3420" s="0" t="s">
         <v>6489</v>
-      </c>
-      <c r="C3420" s="0" t="s">
-        <v>6490</v>
       </c>
       <c r="D3420" s="0" t="s">
         <v>15</v>
@@ -69622,10 +69616,10 @@
         <v>3427</v>
       </c>
       <c r="B3421" s="0" t="s">
+        <v>6490</v>
+      </c>
+      <c r="C3421" s="0" t="s">
         <v>6491</v>
-      </c>
-      <c r="C3421" s="0" t="s">
-        <v>6492</v>
       </c>
       <c r="D3421" s="0" t="s">
         <v>15</v>
@@ -69636,10 +69630,10 @@
         <v>3428</v>
       </c>
       <c r="B3422" s="0" t="s">
+        <v>6492</v>
+      </c>
+      <c r="C3422" s="0" t="s">
         <v>6493</v>
-      </c>
-      <c r="C3422" s="0" t="s">
-        <v>6494</v>
       </c>
       <c r="D3422" s="0" t="s">
         <v>15</v>
@@ -69650,10 +69644,10 @@
         <v>3429</v>
       </c>
       <c r="B3423" s="0" t="s">
+        <v>6494</v>
+      </c>
+      <c r="C3423" s="0" t="s">
         <v>6495</v>
-      </c>
-      <c r="C3423" s="0" t="s">
-        <v>6496</v>
       </c>
       <c r="D3423" s="0" t="s">
         <v>15</v>
@@ -69664,10 +69658,10 @@
         <v>3431</v>
       </c>
       <c r="B3424" s="0" t="s">
+        <v>6496</v>
+      </c>
+      <c r="C3424" s="0" t="s">
         <v>6497</v>
-      </c>
-      <c r="C3424" s="0" t="s">
-        <v>6498</v>
       </c>
       <c r="D3424" s="0" t="s">
         <v>15</v>
@@ -69678,10 +69672,10 @@
         <v>3432</v>
       </c>
       <c r="B3425" s="0" t="s">
+        <v>6498</v>
+      </c>
+      <c r="C3425" s="0" t="s">
         <v>6499</v>
-      </c>
-      <c r="C3425" s="0" t="s">
-        <v>6500</v>
       </c>
       <c r="D3425" s="0" t="s">
         <v>15</v>
@@ -69692,10 +69686,10 @@
         <v>3433</v>
       </c>
       <c r="B3426" s="0" t="s">
+        <v>6500</v>
+      </c>
+      <c r="C3426" s="0" t="s">
         <v>6501</v>
-      </c>
-      <c r="C3426" s="0" t="s">
-        <v>6502</v>
       </c>
       <c r="D3426" s="0" t="s">
         <v>15</v>
@@ -69706,10 +69700,10 @@
         <v>3434</v>
       </c>
       <c r="B3427" s="0" t="s">
+        <v>6502</v>
+      </c>
+      <c r="C3427" s="0" t="s">
         <v>6503</v>
-      </c>
-      <c r="C3427" s="0" t="s">
-        <v>6504</v>
       </c>
       <c r="D3427" s="0" t="s">
         <v>15</v>
@@ -69720,10 +69714,10 @@
         <v>3435</v>
       </c>
       <c r="B3428" s="0" t="s">
+        <v>6504</v>
+      </c>
+      <c r="C3428" s="0" t="s">
         <v>6505</v>
-      </c>
-      <c r="C3428" s="0" t="s">
-        <v>6506</v>
       </c>
       <c r="D3428" s="0" t="s">
         <v>15</v>
@@ -69734,10 +69728,10 @@
         <v>3436</v>
       </c>
       <c r="B3429" s="0" t="s">
+        <v>6506</v>
+      </c>
+      <c r="C3429" s="0" t="s">
         <v>6507</v>
-      </c>
-      <c r="C3429" s="0" t="s">
-        <v>6508</v>
       </c>
       <c r="D3429" s="0" t="s">
         <v>15</v>
@@ -69748,10 +69742,10 @@
         <v>3437</v>
       </c>
       <c r="B3430" s="0" t="s">
+        <v>6508</v>
+      </c>
+      <c r="C3430" s="0" t="s">
         <v>6509</v>
-      </c>
-      <c r="C3430" s="0" t="s">
-        <v>6510</v>
       </c>
       <c r="D3430" s="0" t="s">
         <v>15</v>
@@ -69762,10 +69756,10 @@
         <v>3438</v>
       </c>
       <c r="B3431" s="0" t="s">
+        <v>6510</v>
+      </c>
+      <c r="C3431" s="0" t="s">
         <v>6511</v>
-      </c>
-      <c r="C3431" s="0" t="s">
-        <v>6512</v>
       </c>
       <c r="D3431" s="0" t="s">
         <v>15</v>
@@ -69776,10 +69770,10 @@
         <v>3439</v>
       </c>
       <c r="B3432" s="0" t="s">
+        <v>6512</v>
+      </c>
+      <c r="C3432" s="0" t="s">
         <v>6513</v>
-      </c>
-      <c r="C3432" s="0" t="s">
-        <v>6514</v>
       </c>
       <c r="D3432" s="0" t="s">
         <v>15</v>
@@ -69790,10 +69784,10 @@
         <v>3440</v>
       </c>
       <c r="B3433" s="0" t="s">
+        <v>6514</v>
+      </c>
+      <c r="C3433" s="0" t="s">
         <v>6515</v>
-      </c>
-      <c r="C3433" s="0" t="s">
-        <v>6516</v>
       </c>
       <c r="D3433" s="0" t="s">
         <v>15</v>
@@ -69804,10 +69798,10 @@
         <v>3441</v>
       </c>
       <c r="B3434" s="0" t="s">
+        <v>6516</v>
+      </c>
+      <c r="C3434" s="0" t="s">
         <v>6517</v>
-      </c>
-      <c r="C3434" s="0" t="s">
-        <v>6518</v>
       </c>
       <c r="D3434" s="0" t="s">
         <v>15</v>
@@ -69818,10 +69812,10 @@
         <v>3442</v>
       </c>
       <c r="B3435" s="0" t="s">
+        <v>6518</v>
+      </c>
+      <c r="C3435" s="0" t="s">
         <v>6519</v>
-      </c>
-      <c r="C3435" s="0" t="s">
-        <v>6520</v>
       </c>
       <c r="D3435" s="0" t="s">
         <v>15</v>
@@ -69832,10 +69826,10 @@
         <v>3443</v>
       </c>
       <c r="B3436" s="0" t="s">
+        <v>6520</v>
+      </c>
+      <c r="C3436" s="0" t="s">
         <v>6521</v>
-      </c>
-      <c r="C3436" s="0" t="s">
-        <v>6522</v>
       </c>
       <c r="D3436" s="0" t="s">
         <v>15</v>
@@ -69846,10 +69840,10 @@
         <v>3444</v>
       </c>
       <c r="B3437" s="0" t="s">
+        <v>6522</v>
+      </c>
+      <c r="C3437" s="0" t="s">
         <v>6523</v>
-      </c>
-      <c r="C3437" s="0" t="s">
-        <v>6524</v>
       </c>
       <c r="D3437" s="0" t="s">
         <v>15</v>
@@ -69860,10 +69854,10 @@
         <v>3445</v>
       </c>
       <c r="B3438" s="0" t="s">
+        <v>6524</v>
+      </c>
+      <c r="C3438" s="0" t="s">
         <v>6525</v>
-      </c>
-      <c r="C3438" s="0" t="s">
-        <v>6526</v>
       </c>
       <c r="D3438" s="0" t="s">
         <v>15</v>
@@ -69874,10 +69868,10 @@
         <v>3446</v>
       </c>
       <c r="B3439" s="0" t="s">
+        <v>6526</v>
+      </c>
+      <c r="C3439" s="0" t="s">
         <v>6527</v>
-      </c>
-      <c r="C3439" s="0" t="s">
-        <v>6528</v>
       </c>
       <c r="D3439" s="0" t="s">
         <v>15</v>
@@ -69888,10 +69882,10 @@
         <v>3447</v>
       </c>
       <c r="B3440" s="0" t="s">
+        <v>6528</v>
+      </c>
+      <c r="C3440" s="0" t="s">
         <v>6529</v>
-      </c>
-      <c r="C3440" s="0" t="s">
-        <v>6530</v>
       </c>
       <c r="D3440" s="0" t="s">
         <v>15</v>
@@ -69902,10 +69896,10 @@
         <v>3448</v>
       </c>
       <c r="B3441" s="0" t="s">
+        <v>6530</v>
+      </c>
+      <c r="C3441" s="0" t="s">
         <v>6531</v>
-      </c>
-      <c r="C3441" s="0" t="s">
-        <v>6532</v>
       </c>
       <c r="D3441" s="0" t="s">
         <v>15</v>
@@ -69916,10 +69910,10 @@
         <v>3449</v>
       </c>
       <c r="B3442" s="0" t="s">
+        <v>6532</v>
+      </c>
+      <c r="C3442" s="0" t="s">
         <v>6533</v>
-      </c>
-      <c r="C3442" s="0" t="s">
-        <v>6534</v>
       </c>
       <c r="D3442" s="0" t="s">
         <v>15</v>
@@ -69930,10 +69924,10 @@
         <v>3450</v>
       </c>
       <c r="B3443" s="0" t="s">
+        <v>6534</v>
+      </c>
+      <c r="C3443" s="0" t="s">
         <v>6535</v>
-      </c>
-      <c r="C3443" s="0" t="s">
-        <v>6536</v>
       </c>
       <c r="D3443" s="0" t="s">
         <v>15</v>
@@ -69944,10 +69938,10 @@
         <v>3451</v>
       </c>
       <c r="B3444" s="0" t="s">
+        <v>6536</v>
+      </c>
+      <c r="C3444" s="0" t="s">
         <v>6537</v>
-      </c>
-      <c r="C3444" s="0" t="s">
-        <v>6538</v>
       </c>
       <c r="D3444" s="0" t="s">
         <v>15</v>
@@ -69958,10 +69952,10 @@
         <v>3452</v>
       </c>
       <c r="B3445" s="0" t="s">
+        <v>6538</v>
+      </c>
+      <c r="C3445" s="0" t="s">
         <v>6539</v>
-      </c>
-      <c r="C3445" s="0" t="s">
-        <v>6540</v>
       </c>
       <c r="D3445" s="0" t="s">
         <v>15</v>
@@ -69972,10 +69966,10 @@
         <v>3453</v>
       </c>
       <c r="B3446" s="0" t="s">
+        <v>6540</v>
+      </c>
+      <c r="C3446" s="0" t="s">
         <v>6541</v>
-      </c>
-      <c r="C3446" s="0" t="s">
-        <v>6542</v>
       </c>
       <c r="D3446" s="0" t="s">
         <v>15</v>
@@ -69986,10 +69980,10 @@
         <v>3454</v>
       </c>
       <c r="B3447" s="0" t="s">
+        <v>6542</v>
+      </c>
+      <c r="C3447" s="0" t="s">
         <v>6543</v>
-      </c>
-      <c r="C3447" s="0" t="s">
-        <v>6544</v>
       </c>
       <c r="D3447" s="0" t="s">
         <v>15</v>
@@ -70000,10 +69994,10 @@
         <v>3455</v>
       </c>
       <c r="B3448" s="0" t="s">
+        <v>6544</v>
+      </c>
+      <c r="C3448" s="0" t="s">
         <v>6545</v>
-      </c>
-      <c r="C3448" s="0" t="s">
-        <v>6546</v>
       </c>
       <c r="D3448" s="0" t="s">
         <v>15</v>
@@ -70014,10 +70008,10 @@
         <v>3456</v>
       </c>
       <c r="B3449" s="0" t="s">
+        <v>6546</v>
+      </c>
+      <c r="C3449" s="0" t="s">
         <v>6547</v>
-      </c>
-      <c r="C3449" s="0" t="s">
-        <v>6548</v>
       </c>
       <c r="D3449" s="0" t="s">
         <v>15</v>
@@ -70028,10 +70022,10 @@
         <v>3457</v>
       </c>
       <c r="B3450" s="0" t="s">
+        <v>6548</v>
+      </c>
+      <c r="C3450" s="0" t="s">
         <v>6549</v>
-      </c>
-      <c r="C3450" s="0" t="s">
-        <v>6550</v>
       </c>
       <c r="D3450" s="0" t="s">
         <v>15</v>
@@ -70042,10 +70036,10 @@
         <v>3458</v>
       </c>
       <c r="B3451" s="0" t="s">
+        <v>6550</v>
+      </c>
+      <c r="C3451" s="0" t="s">
         <v>6551</v>
-      </c>
-      <c r="C3451" s="0" t="s">
-        <v>6552</v>
       </c>
       <c r="D3451" s="0" t="s">
         <v>15</v>
@@ -70056,10 +70050,10 @@
         <v>3459</v>
       </c>
       <c r="B3452" s="0" t="s">
+        <v>6552</v>
+      </c>
+      <c r="C3452" s="0" t="s">
         <v>6553</v>
-      </c>
-      <c r="C3452" s="0" t="s">
-        <v>6554</v>
       </c>
       <c r="D3452" s="0" t="s">
         <v>15</v>
@@ -70070,10 +70064,10 @@
         <v>3460</v>
       </c>
       <c r="B3453" s="0" t="s">
+        <v>6554</v>
+      </c>
+      <c r="C3453" s="0" t="s">
         <v>6555</v>
-      </c>
-      <c r="C3453" s="0" t="s">
-        <v>6556</v>
       </c>
       <c r="D3453" s="0" t="s">
         <v>15</v>
@@ -70084,10 +70078,10 @@
         <v>3461</v>
       </c>
       <c r="B3454" s="0" t="s">
+        <v>6556</v>
+      </c>
+      <c r="C3454" s="0" t="s">
         <v>6557</v>
-      </c>
-      <c r="C3454" s="0" t="s">
-        <v>6558</v>
       </c>
       <c r="D3454" s="0" t="s">
         <v>15</v>
@@ -70098,10 +70092,10 @@
         <v>3462</v>
       </c>
       <c r="B3455" s="0" t="s">
+        <v>6558</v>
+      </c>
+      <c r="C3455" s="0" t="s">
         <v>6559</v>
-      </c>
-      <c r="C3455" s="0" t="s">
-        <v>6560</v>
       </c>
       <c r="D3455" s="0" t="s">
         <v>15</v>
@@ -70112,10 +70106,10 @@
         <v>3463</v>
       </c>
       <c r="B3456" s="0" t="s">
+        <v>6560</v>
+      </c>
+      <c r="C3456" s="0" t="s">
         <v>6561</v>
-      </c>
-      <c r="C3456" s="0" t="s">
-        <v>6562</v>
       </c>
       <c r="D3456" s="0" t="s">
         <v>15</v>
@@ -70126,10 +70120,10 @@
         <v>3464</v>
       </c>
       <c r="B3457" s="0" t="s">
+        <v>6562</v>
+      </c>
+      <c r="C3457" s="0" t="s">
         <v>6563</v>
-      </c>
-      <c r="C3457" s="0" t="s">
-        <v>6564</v>
       </c>
       <c r="D3457" s="0" t="s">
         <v>15</v>
@@ -70140,10 +70134,10 @@
         <v>3465</v>
       </c>
       <c r="B3458" s="0" t="s">
+        <v>6564</v>
+      </c>
+      <c r="C3458" s="0" t="s">
         <v>6565</v>
-      </c>
-      <c r="C3458" s="0" t="s">
-        <v>6566</v>
       </c>
       <c r="D3458" s="0" t="s">
         <v>15</v>
@@ -70154,10 +70148,10 @@
         <v>3466</v>
       </c>
       <c r="B3459" s="0" t="s">
+        <v>6566</v>
+      </c>
+      <c r="C3459" s="0" t="s">
         <v>6567</v>
-      </c>
-      <c r="C3459" s="0" t="s">
-        <v>6568</v>
       </c>
       <c r="D3459" s="0" t="s">
         <v>15</v>
@@ -70168,10 +70162,10 @@
         <v>3467</v>
       </c>
       <c r="B3460" s="0" t="s">
+        <v>6568</v>
+      </c>
+      <c r="C3460" s="0" t="s">
         <v>6569</v>
-      </c>
-      <c r="C3460" s="0" t="s">
-        <v>6570</v>
       </c>
       <c r="D3460" s="0" t="s">
         <v>15</v>
@@ -70182,10 +70176,10 @@
         <v>3468</v>
       </c>
       <c r="B3461" s="0" t="s">
+        <v>6570</v>
+      </c>
+      <c r="C3461" s="0" t="s">
         <v>6571</v>
-      </c>
-      <c r="C3461" s="0" t="s">
-        <v>6572</v>
       </c>
       <c r="D3461" s="0" t="s">
         <v>15</v>
@@ -70196,10 +70190,10 @@
         <v>3469</v>
       </c>
       <c r="B3462" s="0" t="s">
+        <v>6572</v>
+      </c>
+      <c r="C3462" s="0" t="s">
         <v>6573</v>
-      </c>
-      <c r="C3462" s="0" t="s">
-        <v>6574</v>
       </c>
       <c r="D3462" s="0" t="s">
         <v>15</v>
@@ -70210,10 +70204,10 @@
         <v>3470</v>
       </c>
       <c r="B3463" s="0" t="s">
+        <v>6574</v>
+      </c>
+      <c r="C3463" s="0" t="s">
         <v>6575</v>
-      </c>
-      <c r="C3463" s="0" t="s">
-        <v>6576</v>
       </c>
       <c r="D3463" s="0" t="s">
         <v>15</v>
@@ -70224,10 +70218,10 @@
         <v>3471</v>
       </c>
       <c r="B3464" s="0" t="s">
+        <v>6576</v>
+      </c>
+      <c r="C3464" s="0" t="s">
         <v>6577</v>
-      </c>
-      <c r="C3464" s="0" t="s">
-        <v>6578</v>
       </c>
       <c r="D3464" s="0" t="s">
         <v>15</v>
@@ -70238,10 +70232,10 @@
         <v>3472</v>
       </c>
       <c r="B3465" s="0" t="s">
+        <v>6578</v>
+      </c>
+      <c r="C3465" s="0" t="s">
         <v>6579</v>
-      </c>
-      <c r="C3465" s="0" t="s">
-        <v>6580</v>
       </c>
       <c r="D3465" s="0" t="s">
         <v>15</v>
@@ -70252,10 +70246,10 @@
         <v>3473</v>
       </c>
       <c r="B3466" s="0" t="s">
+        <v>6580</v>
+      </c>
+      <c r="C3466" s="0" t="s">
         <v>6581</v>
-      </c>
-      <c r="C3466" s="0" t="s">
-        <v>6582</v>
       </c>
       <c r="D3466" s="0" t="s">
         <v>15</v>
@@ -70266,10 +70260,10 @@
         <v>3474</v>
       </c>
       <c r="B3467" s="0" t="s">
+        <v>6582</v>
+      </c>
+      <c r="C3467" s="0" t="s">
         <v>6583</v>
-      </c>
-      <c r="C3467" s="0" t="s">
-        <v>6584</v>
       </c>
       <c r="D3467" s="0" t="s">
         <v>15</v>
@@ -70280,10 +70274,10 @@
         <v>3475</v>
       </c>
       <c r="B3468" s="0" t="s">
+        <v>6584</v>
+      </c>
+      <c r="C3468" s="0" t="s">
         <v>6585</v>
-      </c>
-      <c r="C3468" s="0" t="s">
-        <v>6586</v>
       </c>
       <c r="D3468" s="0" t="s">
         <v>15</v>
@@ -70294,10 +70288,10 @@
         <v>3476</v>
       </c>
       <c r="B3469" s="0" t="s">
+        <v>6586</v>
+      </c>
+      <c r="C3469" s="0" t="s">
         <v>6587</v>
-      </c>
-      <c r="C3469" s="0" t="s">
-        <v>6588</v>
       </c>
       <c r="D3469" s="0" t="s">
         <v>15</v>
@@ -70308,10 +70302,10 @@
         <v>3477</v>
       </c>
       <c r="B3470" s="0" t="s">
+        <v>6588</v>
+      </c>
+      <c r="C3470" s="0" t="s">
         <v>6589</v>
-      </c>
-      <c r="C3470" s="0" t="s">
-        <v>6590</v>
       </c>
       <c r="D3470" s="0" t="s">
         <v>15</v>
@@ -70322,10 +70316,10 @@
         <v>3478</v>
       </c>
       <c r="B3471" s="0" t="s">
+        <v>6590</v>
+      </c>
+      <c r="C3471" s="0" t="s">
         <v>6591</v>
-      </c>
-      <c r="C3471" s="0" t="s">
-        <v>6592</v>
       </c>
       <c r="D3471" s="0" t="s">
         <v>15</v>
@@ -70336,10 +70330,10 @@
         <v>3479</v>
       </c>
       <c r="B3472" s="0" t="s">
+        <v>6592</v>
+      </c>
+      <c r="C3472" s="0" t="s">
         <v>6593</v>
-      </c>
-      <c r="C3472" s="0" t="s">
-        <v>6594</v>
       </c>
       <c r="D3472" s="0" t="s">
         <v>15</v>
@@ -70350,10 +70344,10 @@
         <v>3480</v>
       </c>
       <c r="B3473" s="0" t="s">
+        <v>6594</v>
+      </c>
+      <c r="C3473" s="0" t="s">
         <v>6595</v>
-      </c>
-      <c r="C3473" s="0" t="s">
-        <v>6596</v>
       </c>
       <c r="D3473" s="0" t="s">
         <v>15</v>
@@ -70364,10 +70358,10 @@
         <v>3481</v>
       </c>
       <c r="B3474" s="0" t="s">
+        <v>6596</v>
+      </c>
+      <c r="C3474" s="0" t="s">
         <v>6597</v>
-      </c>
-      <c r="C3474" s="0" t="s">
-        <v>6598</v>
       </c>
       <c r="D3474" s="0" t="s">
         <v>15</v>
@@ -70378,10 +70372,10 @@
         <v>3482</v>
       </c>
       <c r="B3475" s="0" t="s">
+        <v>6598</v>
+      </c>
+      <c r="C3475" s="0" t="s">
         <v>6599</v>
-      </c>
-      <c r="C3475" s="0" t="s">
-        <v>6600</v>
       </c>
       <c r="D3475" s="0" t="s">
         <v>15</v>
@@ -70392,10 +70386,10 @@
         <v>3483</v>
       </c>
       <c r="B3476" s="0" t="s">
+        <v>6600</v>
+      </c>
+      <c r="C3476" s="0" t="s">
         <v>6601</v>
-      </c>
-      <c r="C3476" s="0" t="s">
-        <v>6602</v>
       </c>
       <c r="D3476" s="0" t="s">
         <v>15</v>
@@ -70406,10 +70400,10 @@
         <v>3484</v>
       </c>
       <c r="B3477" s="0" t="s">
+        <v>6602</v>
+      </c>
+      <c r="C3477" s="0" t="s">
         <v>6603</v>
-      </c>
-      <c r="C3477" s="0" t="s">
-        <v>6604</v>
       </c>
       <c r="D3477" s="0" t="s">
         <v>15</v>
@@ -70420,10 +70414,10 @@
         <v>3485</v>
       </c>
       <c r="B3478" s="0" t="s">
+        <v>6604</v>
+      </c>
+      <c r="C3478" s="0" t="s">
         <v>6605</v>
-      </c>
-      <c r="C3478" s="0" t="s">
-        <v>6606</v>
       </c>
       <c r="D3478" s="0" t="s">
         <v>15</v>
@@ -70434,10 +70428,10 @@
         <v>3486</v>
       </c>
       <c r="B3479" s="0" t="s">
+        <v>6606</v>
+      </c>
+      <c r="C3479" s="0" t="s">
         <v>6607</v>
-      </c>
-      <c r="C3479" s="0" t="s">
-        <v>6608</v>
       </c>
       <c r="D3479" s="0" t="s">
         <v>15</v>
@@ -70448,10 +70442,10 @@
         <v>3487</v>
       </c>
       <c r="B3480" s="0" t="s">
+        <v>6608</v>
+      </c>
+      <c r="C3480" s="0" t="s">
         <v>6609</v>
-      </c>
-      <c r="C3480" s="0" t="s">
-        <v>6610</v>
       </c>
       <c r="D3480" s="0" t="s">
         <v>15</v>
@@ -70462,10 +70456,10 @@
         <v>3488</v>
       </c>
       <c r="B3481" s="0" t="s">
+        <v>6610</v>
+      </c>
+      <c r="C3481" s="0" t="s">
         <v>6611</v>
-      </c>
-      <c r="C3481" s="0" t="s">
-        <v>6612</v>
       </c>
       <c r="D3481" s="0" t="s">
         <v>15</v>
@@ -70476,10 +70470,10 @@
         <v>3489</v>
       </c>
       <c r="B3482" s="0" t="s">
+        <v>6612</v>
+      </c>
+      <c r="C3482" s="0" t="s">
         <v>6613</v>
-      </c>
-      <c r="C3482" s="0" t="s">
-        <v>6614</v>
       </c>
       <c r="D3482" s="0" t="s">
         <v>15</v>
@@ -70490,10 +70484,10 @@
         <v>3490</v>
       </c>
       <c r="B3483" s="0" t="s">
+        <v>6614</v>
+      </c>
+      <c r="C3483" s="0" t="s">
         <v>6615</v>
-      </c>
-      <c r="C3483" s="0" t="s">
-        <v>6616</v>
       </c>
       <c r="D3483" s="0" t="s">
         <v>15</v>
@@ -70504,10 +70498,10 @@
         <v>3491</v>
       </c>
       <c r="B3484" s="0" t="s">
+        <v>6616</v>
+      </c>
+      <c r="C3484" s="0" t="s">
         <v>6617</v>
-      </c>
-      <c r="C3484" s="0" t="s">
-        <v>6618</v>
       </c>
       <c r="D3484" s="0" t="s">
         <v>15</v>
@@ -70518,10 +70512,10 @@
         <v>3492</v>
       </c>
       <c r="B3485" s="0" t="s">
+        <v>6618</v>
+      </c>
+      <c r="C3485" s="0" t="s">
         <v>6619</v>
-      </c>
-      <c r="C3485" s="0" t="s">
-        <v>6620</v>
       </c>
       <c r="D3485" s="0" t="s">
         <v>15</v>
@@ -70532,10 +70526,10 @@
         <v>3493</v>
       </c>
       <c r="B3486" s="0" t="s">
+        <v>6620</v>
+      </c>
+      <c r="C3486" s="0" t="s">
         <v>6621</v>
-      </c>
-      <c r="C3486" s="0" t="s">
-        <v>6622</v>
       </c>
       <c r="D3486" s="0" t="s">
         <v>15</v>
@@ -70546,10 +70540,10 @@
         <v>3494</v>
       </c>
       <c r="B3487" s="0" t="s">
+        <v>6622</v>
+      </c>
+      <c r="C3487" s="0" t="s">
         <v>6623</v>
-      </c>
-      <c r="C3487" s="0" t="s">
-        <v>6624</v>
       </c>
       <c r="D3487" s="0" t="s">
         <v>15</v>
@@ -70560,10 +70554,10 @@
         <v>3495</v>
       </c>
       <c r="B3488" s="0" t="s">
+        <v>6624</v>
+      </c>
+      <c r="C3488" s="0" t="s">
         <v>6625</v>
-      </c>
-      <c r="C3488" s="0" t="s">
-        <v>6626</v>
       </c>
       <c r="D3488" s="0" t="s">
         <v>15</v>
@@ -70574,10 +70568,10 @@
         <v>3496</v>
       </c>
       <c r="B3489" s="0" t="s">
+        <v>6626</v>
+      </c>
+      <c r="C3489" s="0" t="s">
         <v>6627</v>
-      </c>
-      <c r="C3489" s="0" t="s">
-        <v>6628</v>
       </c>
       <c r="D3489" s="0" t="s">
         <v>15</v>
@@ -70588,10 +70582,10 @@
         <v>3497</v>
       </c>
       <c r="B3490" s="0" t="s">
+        <v>6628</v>
+      </c>
+      <c r="C3490" s="0" t="s">
         <v>6629</v>
-      </c>
-      <c r="C3490" s="0" t="s">
-        <v>6630</v>
       </c>
       <c r="D3490" s="0" t="s">
         <v>15</v>
@@ -70602,10 +70596,10 @@
         <v>3498</v>
       </c>
       <c r="B3491" s="0" t="s">
+        <v>6630</v>
+      </c>
+      <c r="C3491" s="0" t="s">
         <v>6631</v>
-      </c>
-      <c r="C3491" s="0" t="s">
-        <v>6632</v>
       </c>
       <c r="D3491" s="0" t="s">
         <v>15</v>
@@ -70616,10 +70610,10 @@
         <v>3499</v>
       </c>
       <c r="B3492" s="0" t="s">
+        <v>6632</v>
+      </c>
+      <c r="C3492" s="0" t="s">
         <v>6633</v>
-      </c>
-      <c r="C3492" s="0" t="s">
-        <v>6634</v>
       </c>
       <c r="D3492" s="0" t="s">
         <v>15</v>
@@ -70630,10 +70624,10 @@
         <v>3500</v>
       </c>
       <c r="B3493" s="0" t="s">
+        <v>6634</v>
+      </c>
+      <c r="C3493" s="0" t="s">
         <v>6635</v>
-      </c>
-      <c r="C3493" s="0" t="s">
-        <v>6636</v>
       </c>
       <c r="D3493" s="0" t="s">
         <v>15</v>
@@ -70644,10 +70638,10 @@
         <v>3501</v>
       </c>
       <c r="B3494" s="0" t="s">
-        <v>6637</v>
+        <v>6636</v>
       </c>
       <c r="C3494" s="0" t="s">
-        <v>6637</v>
+        <v>6636</v>
       </c>
       <c r="D3494" s="0" t="s">
         <v>15</v>
@@ -70658,10 +70652,10 @@
         <v>3502</v>
       </c>
       <c r="B3495" s="0" t="s">
+        <v>6637</v>
+      </c>
+      <c r="C3495" s="0" t="s">
         <v>6638</v>
-      </c>
-      <c r="C3495" s="0" t="s">
-        <v>6639</v>
       </c>
       <c r="D3495" s="0" t="s">
         <v>15</v>
@@ -70672,10 +70666,10 @@
         <v>3503</v>
       </c>
       <c r="B3496" s="0" t="s">
+        <v>6639</v>
+      </c>
+      <c r="C3496" s="0" t="s">
         <v>6640</v>
-      </c>
-      <c r="C3496" s="0" t="s">
-        <v>6641</v>
       </c>
       <c r="D3496" s="0" t="s">
         <v>15</v>
@@ -70686,10 +70680,10 @@
         <v>3504</v>
       </c>
       <c r="B3497" s="0" t="s">
+        <v>6641</v>
+      </c>
+      <c r="C3497" s="0" t="s">
         <v>6642</v>
-      </c>
-      <c r="C3497" s="0" t="s">
-        <v>6643</v>
       </c>
       <c r="D3497" s="0" t="s">
         <v>15</v>
@@ -70700,10 +70694,10 @@
         <v>3505</v>
       </c>
       <c r="B3498" s="0" t="s">
+        <v>6643</v>
+      </c>
+      <c r="C3498" s="0" t="s">
         <v>6644</v>
-      </c>
-      <c r="C3498" s="0" t="s">
-        <v>6645</v>
       </c>
       <c r="D3498" s="0" t="s">
         <v>15</v>
@@ -70714,10 +70708,10 @@
         <v>3506</v>
       </c>
       <c r="B3499" s="0" t="s">
+        <v>6645</v>
+      </c>
+      <c r="C3499" s="0" t="s">
         <v>6646</v>
-      </c>
-      <c r="C3499" s="0" t="s">
-        <v>6647</v>
       </c>
       <c r="D3499" s="0" t="s">
         <v>15</v>
@@ -70728,10 +70722,10 @@
         <v>3507</v>
       </c>
       <c r="B3500" s="0" t="s">
+        <v>6647</v>
+      </c>
+      <c r="C3500" s="0" t="s">
         <v>6648</v>
-      </c>
-      <c r="C3500" s="0" t="s">
-        <v>6649</v>
       </c>
       <c r="D3500" s="0" t="s">
         <v>15</v>
@@ -70742,10 +70736,10 @@
         <v>3508</v>
       </c>
       <c r="B3501" s="0" t="s">
+        <v>6649</v>
+      </c>
+      <c r="C3501" s="0" t="s">
         <v>6650</v>
-      </c>
-      <c r="C3501" s="0" t="s">
-        <v>6651</v>
       </c>
       <c r="D3501" s="0" t="s">
         <v>15</v>
@@ -70756,10 +70750,10 @@
         <v>3509</v>
       </c>
       <c r="B3502" s="0" t="s">
+        <v>6651</v>
+      </c>
+      <c r="C3502" s="0" t="s">
         <v>6652</v>
-      </c>
-      <c r="C3502" s="0" t="s">
-        <v>6653</v>
       </c>
       <c r="D3502" s="0" t="s">
         <v>15</v>
@@ -70770,10 +70764,10 @@
         <v>3510</v>
       </c>
       <c r="B3503" s="0" t="s">
+        <v>6653</v>
+      </c>
+      <c r="C3503" s="0" t="s">
         <v>6654</v>
-      </c>
-      <c r="C3503" s="0" t="s">
-        <v>6655</v>
       </c>
       <c r="D3503" s="0" t="s">
         <v>15</v>
@@ -70784,10 +70778,10 @@
         <v>3511</v>
       </c>
       <c r="B3504" s="0" t="s">
+        <v>6655</v>
+      </c>
+      <c r="C3504" s="0" t="s">
         <v>6656</v>
-      </c>
-      <c r="C3504" s="0" t="s">
-        <v>6657</v>
       </c>
       <c r="D3504" s="0" t="s">
         <v>15</v>
@@ -70798,10 +70792,10 @@
         <v>3512</v>
       </c>
       <c r="B3505" s="0" t="s">
+        <v>6657</v>
+      </c>
+      <c r="C3505" s="0" t="s">
         <v>6658</v>
-      </c>
-      <c r="C3505" s="0" t="s">
-        <v>6659</v>
       </c>
       <c r="D3505" s="0" t="s">
         <v>15</v>
@@ -70812,10 +70806,10 @@
         <v>3513</v>
       </c>
       <c r="B3506" s="0" t="s">
+        <v>6659</v>
+      </c>
+      <c r="C3506" s="0" t="s">
         <v>6660</v>
-      </c>
-      <c r="C3506" s="0" t="s">
-        <v>6661</v>
       </c>
       <c r="D3506" s="0" t="s">
         <v>15</v>
@@ -70826,10 +70820,10 @@
         <v>3514</v>
       </c>
       <c r="B3507" s="0" t="s">
+        <v>6661</v>
+      </c>
+      <c r="C3507" s="0" t="s">
         <v>6662</v>
-      </c>
-      <c r="C3507" s="0" t="s">
-        <v>6663</v>
       </c>
       <c r="D3507" s="0" t="s">
         <v>15</v>
@@ -70840,10 +70834,10 @@
         <v>3515</v>
       </c>
       <c r="B3508" s="0" t="s">
+        <v>6663</v>
+      </c>
+      <c r="C3508" s="0" t="s">
         <v>6664</v>
-      </c>
-      <c r="C3508" s="0" t="s">
-        <v>6665</v>
       </c>
       <c r="D3508" s="0" t="s">
         <v>15</v>
@@ -70854,10 +70848,10 @@
         <v>3516</v>
       </c>
       <c r="B3509" s="0" t="s">
-        <v>6666</v>
+        <v>6665</v>
       </c>
       <c r="C3509" s="0" t="s">
-        <v>6666</v>
+        <v>6665</v>
       </c>
       <c r="D3509" s="0" t="s">
         <v>15</v>
@@ -70868,10 +70862,10 @@
         <v>3517</v>
       </c>
       <c r="B3510" s="0" t="s">
+        <v>6666</v>
+      </c>
+      <c r="C3510" s="0" t="s">
         <v>6667</v>
-      </c>
-      <c r="C3510" s="0" t="s">
-        <v>6668</v>
       </c>
       <c r="D3510" s="0" t="s">
         <v>15</v>
@@ -70882,10 +70876,10 @@
         <v>3518</v>
       </c>
       <c r="B3511" s="0" t="s">
+        <v>6668</v>
+      </c>
+      <c r="C3511" s="0" t="s">
         <v>6669</v>
-      </c>
-      <c r="C3511" s="0" t="s">
-        <v>6670</v>
       </c>
       <c r="D3511" s="0" t="s">
         <v>15</v>
@@ -70896,10 +70890,10 @@
         <v>3519</v>
       </c>
       <c r="B3512" s="0" t="s">
+        <v>6670</v>
+      </c>
+      <c r="C3512" s="0" t="s">
         <v>6671</v>
-      </c>
-      <c r="C3512" s="0" t="s">
-        <v>6672</v>
       </c>
       <c r="D3512" s="0" t="s">
         <v>15</v>
@@ -70910,10 +70904,10 @@
         <v>3520</v>
       </c>
       <c r="B3513" s="0" t="s">
+        <v>6672</v>
+      </c>
+      <c r="C3513" s="0" t="s">
         <v>6673</v>
-      </c>
-      <c r="C3513" s="0" t="s">
-        <v>6674</v>
       </c>
       <c r="D3513" s="0" t="s">
         <v>15</v>
@@ -70924,10 +70918,10 @@
         <v>3521</v>
       </c>
       <c r="B3514" s="0" t="s">
+        <v>6674</v>
+      </c>
+      <c r="C3514" s="0" t="s">
         <v>6675</v>
-      </c>
-      <c r="C3514" s="0" t="s">
-        <v>6676</v>
       </c>
       <c r="D3514" s="0" t="s">
         <v>15</v>
@@ -70938,10 +70932,10 @@
         <v>3522</v>
       </c>
       <c r="B3515" s="0" t="s">
+        <v>6676</v>
+      </c>
+      <c r="C3515" s="0" t="s">
         <v>6677</v>
-      </c>
-      <c r="C3515" s="0" t="s">
-        <v>6678</v>
       </c>
       <c r="D3515" s="0" t="s">
         <v>15</v>
@@ -70952,10 +70946,10 @@
         <v>3523</v>
       </c>
       <c r="B3516" s="0" t="s">
+        <v>6678</v>
+      </c>
+      <c r="C3516" s="0" t="s">
         <v>6679</v>
-      </c>
-      <c r="C3516" s="0" t="s">
-        <v>6680</v>
       </c>
       <c r="D3516" s="0" t="s">
         <v>15</v>
@@ -70966,10 +70960,10 @@
         <v>3524</v>
       </c>
       <c r="B3517" s="0" t="s">
+        <v>6680</v>
+      </c>
+      <c r="C3517" s="0" t="s">
         <v>6681</v>
-      </c>
-      <c r="C3517" s="0" t="s">
-        <v>6682</v>
       </c>
       <c r="D3517" s="0" t="s">
         <v>15</v>
@@ -70980,10 +70974,10 @@
         <v>3525</v>
       </c>
       <c r="B3518" s="0" t="s">
+        <v>6682</v>
+      </c>
+      <c r="C3518" s="0" t="s">
         <v>6683</v>
-      </c>
-      <c r="C3518" s="0" t="s">
-        <v>6684</v>
       </c>
       <c r="D3518" s="0" t="s">
         <v>15</v>
@@ -70994,10 +70988,10 @@
         <v>3526</v>
       </c>
       <c r="B3519" s="0" t="s">
+        <v>6684</v>
+      </c>
+      <c r="C3519" s="0" t="s">
         <v>6685</v>
-      </c>
-      <c r="C3519" s="0" t="s">
-        <v>6686</v>
       </c>
       <c r="D3519" s="0" t="s">
         <v>15</v>
@@ -71008,10 +71002,10 @@
         <v>3527</v>
       </c>
       <c r="B3520" s="0" t="s">
-        <v>6687</v>
+        <v>6686</v>
       </c>
       <c r="C3520" s="0" t="s">
-        <v>6687</v>
+        <v>6686</v>
       </c>
       <c r="D3520" s="0" t="s">
         <v>15</v>
@@ -71022,10 +71016,10 @@
         <v>3528</v>
       </c>
       <c r="B3521" s="0" t="s">
-        <v>6688</v>
+        <v>6687</v>
       </c>
       <c r="C3521" s="0" t="s">
-        <v>6688</v>
+        <v>6687</v>
       </c>
       <c r="D3521" s="0" t="s">
         <v>15</v>
@@ -71036,10 +71030,10 @@
         <v>3529</v>
       </c>
       <c r="B3522" s="0" t="s">
+        <v>6688</v>
+      </c>
+      <c r="C3522" s="0" t="s">
         <v>6689</v>
-      </c>
-      <c r="C3522" s="0" t="s">
-        <v>6690</v>
       </c>
       <c r="D3522" s="0" t="s">
         <v>15</v>
@@ -71050,10 +71044,10 @@
         <v>3530</v>
       </c>
       <c r="B3523" s="0" t="s">
+        <v>6690</v>
+      </c>
+      <c r="C3523" s="0" t="s">
         <v>6691</v>
-      </c>
-      <c r="C3523" s="0" t="s">
-        <v>6692</v>
       </c>
       <c r="D3523" s="0" t="s">
         <v>15</v>
@@ -71064,10 +71058,10 @@
         <v>3531</v>
       </c>
       <c r="B3524" s="0" t="s">
+        <v>6692</v>
+      </c>
+      <c r="C3524" s="0" t="s">
         <v>6693</v>
-      </c>
-      <c r="C3524" s="0" t="s">
-        <v>6694</v>
       </c>
       <c r="D3524" s="0" t="s">
         <v>15</v>
@@ -71078,10 +71072,10 @@
         <v>3532</v>
       </c>
       <c r="B3525" s="0" t="s">
+        <v>6694</v>
+      </c>
+      <c r="C3525" s="0" t="s">
         <v>6695</v>
-      </c>
-      <c r="C3525" s="0" t="s">
-        <v>6696</v>
       </c>
       <c r="D3525" s="0" t="s">
         <v>15</v>
@@ -71092,10 +71086,10 @@
         <v>3533</v>
       </c>
       <c r="B3526" s="0" t="s">
+        <v>6696</v>
+      </c>
+      <c r="C3526" s="0" t="s">
         <v>6697</v>
-      </c>
-      <c r="C3526" s="0" t="s">
-        <v>6698</v>
       </c>
       <c r="D3526" s="0" t="s">
         <v>15</v>
@@ -71106,10 +71100,10 @@
         <v>3534</v>
       </c>
       <c r="B3527" s="0" t="s">
+        <v>6698</v>
+      </c>
+      <c r="C3527" s="0" t="s">
         <v>6699</v>
-      </c>
-      <c r="C3527" s="0" t="s">
-        <v>6700</v>
       </c>
       <c r="D3527" s="0" t="s">
         <v>15</v>
@@ -71120,10 +71114,10 @@
         <v>3535</v>
       </c>
       <c r="B3528" s="0" t="s">
+        <v>6700</v>
+      </c>
+      <c r="C3528" s="0" t="s">
         <v>6701</v>
-      </c>
-      <c r="C3528" s="0" t="s">
-        <v>6702</v>
       </c>
       <c r="D3528" s="0" t="s">
         <v>15</v>
@@ -71134,10 +71128,10 @@
         <v>3536</v>
       </c>
       <c r="B3529" s="0" t="s">
+        <v>6702</v>
+      </c>
+      <c r="C3529" s="0" t="s">
         <v>6703</v>
-      </c>
-      <c r="C3529" s="0" t="s">
-        <v>6704</v>
       </c>
       <c r="D3529" s="0" t="s">
         <v>15</v>
@@ -71148,10 +71142,10 @@
         <v>3537</v>
       </c>
       <c r="B3530" s="0" t="s">
+        <v>6704</v>
+      </c>
+      <c r="C3530" s="0" t="s">
         <v>6705</v>
-      </c>
-      <c r="C3530" s="0" t="s">
-        <v>6706</v>
       </c>
       <c r="D3530" s="0" t="s">
         <v>15</v>
@@ -71162,10 +71156,10 @@
         <v>3538</v>
       </c>
       <c r="B3531" s="0" t="s">
+        <v>6706</v>
+      </c>
+      <c r="C3531" s="0" t="s">
         <v>6707</v>
-      </c>
-      <c r="C3531" s="0" t="s">
-        <v>6708</v>
       </c>
       <c r="D3531" s="0" t="s">
         <v>15</v>
@@ -71176,10 +71170,10 @@
         <v>3539</v>
       </c>
       <c r="B3532" s="0" t="s">
+        <v>6708</v>
+      </c>
+      <c r="C3532" s="0" t="s">
         <v>6709</v>
-      </c>
-      <c r="C3532" s="0" t="s">
-        <v>6710</v>
       </c>
       <c r="D3532" s="0" t="s">
         <v>15</v>
@@ -71190,10 +71184,10 @@
         <v>3540</v>
       </c>
       <c r="B3533" s="0" t="s">
+        <v>6710</v>
+      </c>
+      <c r="C3533" s="0" t="s">
         <v>6711</v>
-      </c>
-      <c r="C3533" s="0" t="s">
-        <v>6712</v>
       </c>
       <c r="D3533" s="0" t="s">
         <v>15</v>
@@ -71204,10 +71198,10 @@
         <v>3541</v>
       </c>
       <c r="B3534" s="0" t="s">
+        <v>6712</v>
+      </c>
+      <c r="C3534" s="0" t="s">
         <v>6713</v>
-      </c>
-      <c r="C3534" s="0" t="s">
-        <v>6714</v>
       </c>
       <c r="D3534" s="0" t="s">
         <v>15</v>
@@ -71218,10 +71212,10 @@
         <v>3542</v>
       </c>
       <c r="B3535" s="0" t="s">
+        <v>6714</v>
+      </c>
+      <c r="C3535" s="0" t="s">
         <v>6715</v>
-      </c>
-      <c r="C3535" s="0" t="s">
-        <v>6716</v>
       </c>
       <c r="D3535" s="0" t="s">
         <v>15</v>
@@ -71232,10 +71226,10 @@
         <v>3543</v>
       </c>
       <c r="B3536" s="0" t="s">
+        <v>6716</v>
+      </c>
+      <c r="C3536" s="0" t="s">
         <v>6717</v>
-      </c>
-      <c r="C3536" s="0" t="s">
-        <v>6718</v>
       </c>
       <c r="D3536" s="0" t="s">
         <v>15</v>
@@ -71246,10 +71240,10 @@
         <v>3544</v>
       </c>
       <c r="B3537" s="0" t="s">
+        <v>6718</v>
+      </c>
+      <c r="C3537" s="0" t="s">
         <v>6719</v>
-      </c>
-      <c r="C3537" s="0" t="s">
-        <v>6720</v>
       </c>
       <c r="D3537" s="0" t="s">
         <v>15</v>
@@ -71260,10 +71254,10 @@
         <v>3545</v>
       </c>
       <c r="B3538" s="0" t="s">
+        <v>6720</v>
+      </c>
+      <c r="C3538" s="0" t="s">
         <v>6721</v>
-      </c>
-      <c r="C3538" s="0" t="s">
-        <v>6722</v>
       </c>
       <c r="D3538" s="0" t="s">
         <v>15</v>
@@ -71274,10 +71268,10 @@
         <v>3546</v>
       </c>
       <c r="B3539" s="0" t="s">
+        <v>6722</v>
+      </c>
+      <c r="C3539" s="0" t="s">
         <v>6723</v>
-      </c>
-      <c r="C3539" s="0" t="s">
-        <v>6724</v>
       </c>
       <c r="D3539" s="0" t="s">
         <v>15</v>
@@ -71285,13 +71279,13 @@
     </row>
     <row r="3540" spans="1:4">
       <c r="A3540" s="0" t="n">
-        <v>3547</v>
+        <v>3569</v>
       </c>
       <c r="B3540" s="0" t="s">
-        <v>6725</v>
+        <v>6724</v>
       </c>
       <c r="C3540" s="0" t="s">
-        <v>6726</v>
+        <v>4235</v>
       </c>
       <c r="D3540" s="0" t="s">
         <v>15</v>
@@ -71299,13 +71293,13 @@
     </row>
     <row r="3541" spans="1:4">
       <c r="A3541" s="0" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="B3541" s="0" t="s">
-        <v>6727</v>
+        <v>6725</v>
       </c>
       <c r="C3541" s="0" t="s">
-        <v>6728</v>
+        <v>6726</v>
       </c>
       <c r="D3541" s="0" t="s">
         <v>15</v>
@@ -71313,13 +71307,13 @@
     </row>
     <row r="3542" spans="1:4">
       <c r="A3542" s="0" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="B3542" s="0" t="s">
-        <v>6729</v>
+        <v>6727</v>
       </c>
       <c r="C3542" s="0" t="s">
-        <v>6730</v>
+        <v>6728</v>
       </c>
       <c r="D3542" s="0" t="s">
         <v>15</v>
@@ -71327,13 +71321,13 @@
     </row>
     <row r="3543" spans="1:4">
       <c r="A3543" s="0" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="B3543" s="0" t="s">
-        <v>6731</v>
+        <v>6729</v>
       </c>
       <c r="C3543" s="0" t="s">
-        <v>6732</v>
+        <v>6730</v>
       </c>
       <c r="D3543" s="0" t="s">
         <v>15</v>
@@ -71341,13 +71335,13 @@
     </row>
     <row r="3544" spans="1:4">
       <c r="A3544" s="0" t="n">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="B3544" s="0" t="s">
-        <v>6733</v>
+        <v>6731</v>
       </c>
       <c r="C3544" s="0" t="s">
-        <v>6734</v>
+        <v>6732</v>
       </c>
       <c r="D3544" s="0" t="s">
         <v>15</v>
@@ -71355,13 +71349,13 @@
     </row>
     <row r="3545" spans="1:4">
       <c r="A3545" s="0" t="n">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="B3545" s="0" t="s">
-        <v>6735</v>
+        <v>6733</v>
       </c>
       <c r="C3545" s="0" t="s">
-        <v>6736</v>
+        <v>6734</v>
       </c>
       <c r="D3545" s="0" t="s">
         <v>15</v>
@@ -71369,13 +71363,13 @@
     </row>
     <row r="3546" spans="1:4">
       <c r="A3546" s="0" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="B3546" s="0" t="s">
-        <v>6737</v>
+        <v>6735</v>
       </c>
       <c r="C3546" s="0" t="s">
-        <v>6738</v>
+        <v>6736</v>
       </c>
       <c r="D3546" s="0" t="s">
         <v>15</v>
@@ -71383,13 +71377,13 @@
     </row>
     <row r="3547" spans="1:4">
       <c r="A3547" s="0" t="n">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="B3547" s="0" t="s">
-        <v>6739</v>
+        <v>6737</v>
       </c>
       <c r="C3547" s="0" t="s">
-        <v>6739</v>
+        <v>6738</v>
       </c>
       <c r="D3547" s="0" t="s">
         <v>15</v>
@@ -71397,13 +71391,13 @@
     </row>
     <row r="3548" spans="1:4">
       <c r="A3548" s="0" t="n">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="B3548" s="0" t="s">
-        <v>6740</v>
+        <v>6739</v>
       </c>
       <c r="C3548" s="0" t="s">
-        <v>6741</v>
+        <v>6739</v>
       </c>
       <c r="D3548" s="0" t="s">
         <v>15</v>
@@ -71411,13 +71405,13 @@
     </row>
     <row r="3549" spans="1:4">
       <c r="A3549" s="0" t="n">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="B3549" s="0" t="s">
-        <v>6742</v>
+        <v>6740</v>
       </c>
       <c r="C3549" s="0" t="s">
-        <v>6743</v>
+        <v>6741</v>
       </c>
       <c r="D3549" s="0" t="s">
         <v>15</v>
@@ -71425,13 +71419,13 @@
     </row>
     <row r="3550" spans="1:4">
       <c r="A3550" s="0" t="n">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B3550" s="0" t="s">
-        <v>6744</v>
+        <v>6742</v>
       </c>
       <c r="C3550" s="0" t="s">
-        <v>6744</v>
+        <v>6743</v>
       </c>
       <c r="D3550" s="0" t="s">
         <v>15</v>
@@ -71439,13 +71433,13 @@
     </row>
     <row r="3551" spans="1:4">
       <c r="A3551" s="0" t="n">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="B3551" s="0" t="s">
-        <v>6745</v>
+        <v>6744</v>
       </c>
       <c r="C3551" s="0" t="s">
-        <v>6746</v>
+        <v>6744</v>
       </c>
       <c r="D3551" s="0" t="s">
         <v>15</v>
@@ -71453,13 +71447,13 @@
     </row>
     <row r="3552" spans="1:4">
       <c r="A3552" s="0" t="n">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="B3552" s="0" t="s">
-        <v>6747</v>
+        <v>6745</v>
       </c>
       <c r="C3552" s="0" t="s">
-        <v>6748</v>
+        <v>6746</v>
       </c>
       <c r="D3552" s="0" t="s">
         <v>15</v>
@@ -71467,13 +71461,13 @@
     </row>
     <row r="3553" spans="1:4">
       <c r="A3553" s="0" t="n">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="B3553" s="0" t="s">
-        <v>6749</v>
+        <v>6747</v>
       </c>
       <c r="C3553" s="0" t="s">
-        <v>6750</v>
+        <v>6748</v>
       </c>
       <c r="D3553" s="0" t="s">
         <v>15</v>
@@ -71481,13 +71475,13 @@
     </row>
     <row r="3554" spans="1:4">
       <c r="A3554" s="0" t="n">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="B3554" s="0" t="s">
-        <v>6751</v>
+        <v>6749</v>
       </c>
       <c r="C3554" s="0" t="s">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="D3554" s="0" t="s">
         <v>15</v>
@@ -71495,13 +71489,13 @@
     </row>
     <row r="3555" spans="1:4">
       <c r="A3555" s="0" t="n">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="B3555" s="0" t="s">
-        <v>6752</v>
+        <v>6751</v>
       </c>
       <c r="C3555" s="0" t="s">
-        <v>6753</v>
+        <v>6751</v>
       </c>
       <c r="D3555" s="0" t="s">
         <v>15</v>
@@ -71509,13 +71503,13 @@
     </row>
     <row r="3556" spans="1:4">
       <c r="A3556" s="0" t="n">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="B3556" s="0" t="s">
-        <v>6754</v>
+        <v>6752</v>
       </c>
       <c r="C3556" s="0" t="s">
-        <v>6755</v>
+        <v>6753</v>
       </c>
       <c r="D3556" s="0" t="s">
         <v>15</v>
@@ -71523,13 +71517,13 @@
     </row>
     <row r="3557" spans="1:4">
       <c r="A3557" s="0" t="n">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="B3557" s="0" t="s">
-        <v>6756</v>
+        <v>6754</v>
       </c>
       <c r="C3557" s="0" t="s">
-        <v>6757</v>
+        <v>6755</v>
       </c>
       <c r="D3557" s="0" t="s">
         <v>15</v>
@@ -71537,13 +71531,13 @@
     </row>
     <row r="3558" spans="1:4">
       <c r="A3558" s="0" t="n">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="B3558" s="0" t="s">
-        <v>6758</v>
+        <v>6756</v>
       </c>
       <c r="C3558" s="0" t="s">
-        <v>6759</v>
+        <v>6757</v>
       </c>
       <c r="D3558" s="0" t="s">
         <v>15</v>
@@ -71551,13 +71545,13 @@
     </row>
     <row r="3559" spans="1:4">
       <c r="A3559" s="0" t="n">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="B3559" s="0" t="s">
-        <v>6760</v>
+        <v>6758</v>
       </c>
       <c r="C3559" s="0" t="s">
-        <v>6761</v>
+        <v>6759</v>
       </c>
       <c r="D3559" s="0" t="s">
         <v>15</v>
@@ -71565,13 +71559,13 @@
     </row>
     <row r="3560" spans="1:4">
       <c r="A3560" s="0" t="n">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="B3560" s="0" t="s">
-        <v>6762</v>
+        <v>6760</v>
       </c>
       <c r="C3560" s="0" t="s">
-        <v>6762</v>
+        <v>6761</v>
       </c>
       <c r="D3560" s="0" t="s">
         <v>15</v>
@@ -71579,13 +71573,13 @@
     </row>
     <row r="3561" spans="1:4">
       <c r="A3561" s="0" t="n">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="B3561" s="0" t="s">
-        <v>6763</v>
+        <v>6762</v>
       </c>
       <c r="C3561" s="0" t="s">
-        <v>6764</v>
+        <v>6762</v>
       </c>
       <c r="D3561" s="0" t="s">
         <v>15</v>
@@ -71593,13 +71587,13 @@
     </row>
     <row r="3562" spans="1:4">
       <c r="A3562" s="0" t="n">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="B3562" s="0" t="s">
-        <v>6765</v>
+        <v>6763</v>
       </c>
       <c r="C3562" s="0" t="s">
-        <v>6766</v>
+        <v>6764</v>
       </c>
       <c r="D3562" s="0" t="s">
         <v>15</v>
@@ -71610,10 +71604,10 @@
         <v>3570</v>
       </c>
       <c r="B3563" s="0" t="s">
-        <v>6767</v>
+        <v>6765</v>
       </c>
       <c r="C3563" s="0" t="s">
-        <v>6768</v>
+        <v>6766</v>
       </c>
       <c r="D3563" s="0" t="s">
         <v>15</v>
@@ -71624,10 +71618,10 @@
         <v>3571</v>
       </c>
       <c r="B3564" s="0" t="s">
-        <v>6769</v>
+        <v>6767</v>
       </c>
       <c r="C3564" s="0" t="s">
-        <v>6770</v>
+        <v>6768</v>
       </c>
       <c r="D3564" s="0" t="s">
         <v>15</v>
@@ -71638,10 +71632,10 @@
         <v>3572</v>
       </c>
       <c r="B3565" s="0" t="s">
-        <v>6771</v>
+        <v>6769</v>
       </c>
       <c r="C3565" s="0" t="s">
-        <v>6772</v>
+        <v>6770</v>
       </c>
       <c r="D3565" s="0" t="s">
         <v>15</v>
@@ -71652,10 +71646,10 @@
         <v>3573</v>
       </c>
       <c r="B3566" s="0" t="s">
-        <v>6773</v>
+        <v>6771</v>
       </c>
       <c r="C3566" s="0" t="s">
-        <v>6773</v>
+        <v>6771</v>
       </c>
       <c r="D3566" s="0" t="s">
         <v>15</v>
@@ -71666,10 +71660,10 @@
         <v>3574</v>
       </c>
       <c r="B3567" s="0" t="s">
-        <v>6774</v>
+        <v>6772</v>
       </c>
       <c r="C3567" s="0" t="s">
-        <v>6774</v>
+        <v>6772</v>
       </c>
       <c r="D3567" s="0" t="s">
         <v>15</v>
@@ -71680,10 +71674,10 @@
         <v>3575</v>
       </c>
       <c r="B3568" s="0" t="s">
-        <v>6775</v>
+        <v>6773</v>
       </c>
       <c r="C3568" s="0" t="s">
-        <v>6776</v>
+        <v>6774</v>
       </c>
       <c r="D3568" s="0" t="s">
         <v>15</v>
@@ -71694,10 +71688,10 @@
         <v>3576</v>
       </c>
       <c r="B3569" s="0" t="s">
-        <v>6777</v>
+        <v>6775</v>
       </c>
       <c r="C3569" s="0" t="s">
-        <v>6778</v>
+        <v>6776</v>
       </c>
       <c r="D3569" s="0" t="s">
         <v>15</v>
@@ -71708,10 +71702,10 @@
         <v>3577</v>
       </c>
       <c r="B3570" s="0" t="s">
-        <v>6779</v>
+        <v>6777</v>
       </c>
       <c r="C3570" s="0" t="s">
-        <v>6780</v>
+        <v>6778</v>
       </c>
       <c r="D3570" s="0" t="s">
         <v>15</v>
@@ -71722,10 +71716,10 @@
         <v>3578</v>
       </c>
       <c r="B3571" s="0" t="s">
-        <v>6781</v>
+        <v>6779</v>
       </c>
       <c r="C3571" s="0" t="s">
-        <v>6782</v>
+        <v>6780</v>
       </c>
       <c r="D3571" s="0" t="s">
         <v>15</v>
@@ -71736,10 +71730,10 @@
         <v>3579</v>
       </c>
       <c r="B3572" s="0" t="s">
-        <v>6783</v>
+        <v>6781</v>
       </c>
       <c r="C3572" s="0" t="s">
-        <v>6784</v>
+        <v>6782</v>
       </c>
       <c r="D3572" s="0" t="s">
         <v>15</v>
@@ -71750,10 +71744,10 @@
         <v>3580</v>
       </c>
       <c r="B3573" s="0" t="s">
-        <v>6785</v>
+        <v>6783</v>
       </c>
       <c r="C3573" s="0" t="s">
-        <v>6785</v>
+        <v>6783</v>
       </c>
       <c r="D3573" s="0" t="s">
         <v>15</v>
@@ -71764,10 +71758,10 @@
         <v>3581</v>
       </c>
       <c r="B3574" s="0" t="s">
-        <v>6786</v>
+        <v>6784</v>
       </c>
       <c r="C3574" s="0" t="s">
-        <v>6786</v>
+        <v>6784</v>
       </c>
       <c r="D3574" s="0" t="s">
         <v>15</v>
@@ -71778,10 +71772,10 @@
         <v>3582</v>
       </c>
       <c r="B3575" s="0" t="s">
-        <v>6787</v>
+        <v>6785</v>
       </c>
       <c r="C3575" s="0" t="s">
-        <v>6787</v>
+        <v>6785</v>
       </c>
       <c r="D3575" s="0" t="s">
         <v>15</v>
@@ -71792,10 +71786,10 @@
         <v>3583</v>
       </c>
       <c r="B3576" s="0" t="s">
-        <v>6788</v>
+        <v>6786</v>
       </c>
       <c r="C3576" s="0" t="s">
-        <v>6788</v>
+        <v>6786</v>
       </c>
       <c r="D3576" s="0" t="s">
         <v>15</v>
@@ -71806,10 +71800,10 @@
         <v>3584</v>
       </c>
       <c r="B3577" s="0" t="s">
-        <v>6789</v>
+        <v>6787</v>
       </c>
       <c r="C3577" s="0" t="s">
-        <v>6790</v>
+        <v>6788</v>
       </c>
       <c r="D3577" s="0" t="s">
         <v>15</v>
@@ -71820,10 +71814,10 @@
         <v>3585</v>
       </c>
       <c r="B3578" s="0" t="s">
-        <v>6791</v>
+        <v>6789</v>
       </c>
       <c r="C3578" s="0" t="s">
-        <v>6792</v>
+        <v>6790</v>
       </c>
       <c r="D3578" s="0" t="s">
         <v>15</v>
@@ -71834,10 +71828,10 @@
         <v>3586</v>
       </c>
       <c r="B3579" s="0" t="s">
-        <v>6793</v>
+        <v>6791</v>
       </c>
       <c r="C3579" s="0" t="s">
-        <v>6794</v>
+        <v>6792</v>
       </c>
       <c r="D3579" s="0" t="s">
         <v>15</v>
@@ -71848,10 +71842,10 @@
         <v>3587</v>
       </c>
       <c r="B3580" s="0" t="s">
-        <v>6795</v>
+        <v>6793</v>
       </c>
       <c r="C3580" s="0" t="s">
-        <v>6796</v>
+        <v>6794</v>
       </c>
       <c r="D3580" s="0" t="s">
         <v>15</v>
@@ -71862,10 +71856,10 @@
         <v>3588</v>
       </c>
       <c r="B3581" s="0" t="s">
-        <v>6797</v>
+        <v>6795</v>
       </c>
       <c r="C3581" s="0" t="s">
-        <v>6798</v>
+        <v>6796</v>
       </c>
       <c r="D3581" s="0" t="s">
         <v>15</v>
@@ -71876,10 +71870,10 @@
         <v>3589</v>
       </c>
       <c r="B3582" s="0" t="s">
-        <v>6799</v>
+        <v>6797</v>
       </c>
       <c r="C3582" s="0" t="s">
-        <v>6800</v>
+        <v>6798</v>
       </c>
       <c r="D3582" s="0" t="s">
         <v>15</v>
@@ -71890,10 +71884,10 @@
         <v>3590</v>
       </c>
       <c r="B3583" s="0" t="s">
-        <v>6801</v>
+        <v>6799</v>
       </c>
       <c r="C3583" s="0" t="s">
-        <v>6802</v>
+        <v>6800</v>
       </c>
       <c r="D3583" s="0" t="s">
         <v>15</v>
@@ -71904,10 +71898,10 @@
         <v>3591</v>
       </c>
       <c r="B3584" s="0" t="s">
-        <v>6803</v>
+        <v>6801</v>
       </c>
       <c r="C3584" s="0" t="s">
-        <v>6804</v>
+        <v>6802</v>
       </c>
       <c r="D3584" s="0" t="s">
         <v>15</v>
@@ -71918,10 +71912,10 @@
         <v>3592</v>
       </c>
       <c r="B3585" s="0" t="s">
-        <v>6805</v>
+        <v>6803</v>
       </c>
       <c r="C3585" s="0" t="s">
-        <v>6806</v>
+        <v>6804</v>
       </c>
       <c r="D3585" s="0" t="s">
         <v>15</v>
@@ -71932,10 +71926,10 @@
         <v>3593</v>
       </c>
       <c r="B3586" s="0" t="s">
-        <v>6807</v>
+        <v>6805</v>
       </c>
       <c r="C3586" s="0" t="s">
-        <v>6808</v>
+        <v>6806</v>
       </c>
       <c r="D3586" s="0" t="s">
         <v>15</v>
@@ -71946,10 +71940,10 @@
         <v>3594</v>
       </c>
       <c r="B3587" s="0" t="s">
-        <v>6809</v>
+        <v>6807</v>
       </c>
       <c r="C3587" s="0" t="s">
-        <v>6810</v>
+        <v>6808</v>
       </c>
       <c r="D3587" s="0" t="s">
         <v>15</v>
@@ -71960,10 +71954,10 @@
         <v>3595</v>
       </c>
       <c r="B3588" s="0" t="s">
-        <v>6811</v>
+        <v>6809</v>
       </c>
       <c r="C3588" s="0" t="s">
-        <v>6812</v>
+        <v>6810</v>
       </c>
       <c r="D3588" s="0" t="s">
         <v>15</v>
@@ -71974,10 +71968,10 @@
         <v>3596</v>
       </c>
       <c r="B3589" s="0" t="s">
-        <v>6813</v>
+        <v>6811</v>
       </c>
       <c r="C3589" s="0" t="s">
-        <v>6814</v>
+        <v>6812</v>
       </c>
       <c r="D3589" s="0" t="s">
         <v>15</v>
@@ -71988,10 +71982,10 @@
         <v>3597</v>
       </c>
       <c r="B3590" s="0" t="s">
-        <v>6815</v>
+        <v>6813</v>
       </c>
       <c r="C3590" s="0" t="s">
-        <v>6816</v>
+        <v>6814</v>
       </c>
       <c r="D3590" s="0" t="s">
         <v>15</v>
@@ -72002,10 +71996,10 @@
         <v>3598</v>
       </c>
       <c r="B3591" s="0" t="s">
-        <v>6817</v>
+        <v>6815</v>
       </c>
       <c r="C3591" s="0" t="s">
-        <v>6818</v>
+        <v>6816</v>
       </c>
       <c r="D3591" s="0" t="s">
         <v>15</v>
@@ -72016,10 +72010,10 @@
         <v>3599</v>
       </c>
       <c r="B3592" s="0" t="s">
-        <v>6819</v>
+        <v>6817</v>
       </c>
       <c r="C3592" s="0" t="s">
-        <v>6820</v>
+        <v>6818</v>
       </c>
       <c r="D3592" s="0" t="s">
         <v>15</v>
@@ -72030,10 +72024,10 @@
         <v>3600</v>
       </c>
       <c r="B3593" s="0" t="s">
-        <v>6821</v>
+        <v>6819</v>
       </c>
       <c r="C3593" s="0" t="s">
-        <v>6822</v>
+        <v>6820</v>
       </c>
       <c r="D3593" s="0" t="s">
         <v>15</v>
@@ -72044,10 +72038,10 @@
         <v>3601</v>
       </c>
       <c r="B3594" s="0" t="s">
-        <v>6823</v>
+        <v>6821</v>
       </c>
       <c r="C3594" s="0" t="s">
-        <v>6824</v>
+        <v>6822</v>
       </c>
       <c r="D3594" s="0" t="s">
         <v>15</v>
@@ -72058,10 +72052,10 @@
         <v>3602</v>
       </c>
       <c r="B3595" s="0" t="s">
-        <v>6825</v>
+        <v>6823</v>
       </c>
       <c r="C3595" s="0" t="s">
-        <v>6826</v>
+        <v>6824</v>
       </c>
       <c r="D3595" s="0" t="s">
         <v>15</v>
@@ -72072,10 +72066,10 @@
         <v>3603</v>
       </c>
       <c r="B3596" s="0" t="s">
-        <v>6827</v>
+        <v>6825</v>
       </c>
       <c r="C3596" s="0" t="s">
-        <v>6828</v>
+        <v>6826</v>
       </c>
       <c r="D3596" s="0" t="s">
         <v>15</v>
@@ -72086,10 +72080,10 @@
         <v>3604</v>
       </c>
       <c r="B3597" s="0" t="s">
-        <v>6829</v>
+        <v>6827</v>
       </c>
       <c r="C3597" s="0" t="s">
-        <v>6830</v>
+        <v>6828</v>
       </c>
       <c r="D3597" s="0" t="s">
         <v>15</v>
@@ -72100,10 +72094,10 @@
         <v>3605</v>
       </c>
       <c r="B3598" s="0" t="s">
-        <v>6831</v>
+        <v>6829</v>
       </c>
       <c r="C3598" s="0" t="s">
-        <v>6831</v>
+        <v>6829</v>
       </c>
       <c r="D3598" s="0" t="s">
         <v>15</v>
@@ -72114,10 +72108,10 @@
         <v>3606</v>
       </c>
       <c r="B3599" s="0" t="s">
-        <v>6832</v>
+        <v>6830</v>
       </c>
       <c r="C3599" s="0" t="s">
-        <v>6833</v>
+        <v>6831</v>
       </c>
       <c r="D3599" s="0" t="s">
         <v>15</v>
@@ -72128,10 +72122,10 @@
         <v>3607</v>
       </c>
       <c r="B3600" s="0" t="s">
-        <v>6834</v>
+        <v>6832</v>
       </c>
       <c r="C3600" s="0" t="s">
-        <v>6835</v>
+        <v>6833</v>
       </c>
       <c r="D3600" s="0" t="s">
         <v>15</v>
@@ -72142,10 +72136,10 @@
         <v>3608</v>
       </c>
       <c r="B3601" s="0" t="s">
-        <v>6836</v>
+        <v>6834</v>
       </c>
       <c r="C3601" s="0" t="s">
-        <v>6837</v>
+        <v>6835</v>
       </c>
       <c r="D3601" s="0" t="s">
         <v>15</v>
@@ -72156,10 +72150,10 @@
         <v>3609</v>
       </c>
       <c r="B3602" s="0" t="s">
-        <v>6838</v>
+        <v>6836</v>
       </c>
       <c r="C3602" s="0" t="s">
-        <v>6839</v>
+        <v>6837</v>
       </c>
       <c r="D3602" s="0" t="s">
         <v>15</v>
@@ -72170,10 +72164,10 @@
         <v>3610</v>
       </c>
       <c r="B3603" s="0" t="s">
-        <v>6840</v>
+        <v>6838</v>
       </c>
       <c r="C3603" s="0" t="s">
-        <v>6841</v>
+        <v>6839</v>
       </c>
       <c r="D3603" s="0" t="s">
         <v>15</v>
@@ -72184,10 +72178,10 @@
         <v>3611</v>
       </c>
       <c r="B3604" s="0" t="s">
-        <v>6842</v>
+        <v>6840</v>
       </c>
       <c r="C3604" s="0" t="s">
-        <v>6843</v>
+        <v>6841</v>
       </c>
       <c r="D3604" s="0" t="s">
         <v>15</v>
@@ -72198,10 +72192,10 @@
         <v>3612</v>
       </c>
       <c r="B3605" s="0" t="s">
-        <v>6844</v>
+        <v>6842</v>
       </c>
       <c r="C3605" s="0" t="s">
-        <v>6845</v>
+        <v>6843</v>
       </c>
       <c r="D3605" s="0" t="s">
         <v>15</v>
@@ -72212,10 +72206,10 @@
         <v>3613</v>
       </c>
       <c r="B3606" s="0" t="s">
-        <v>6846</v>
+        <v>6844</v>
       </c>
       <c r="C3606" s="0" t="s">
-        <v>6847</v>
+        <v>6845</v>
       </c>
       <c r="D3606" s="0" t="s">
         <v>15</v>
@@ -72226,10 +72220,10 @@
         <v>3614</v>
       </c>
       <c r="B3607" s="0" t="s">
-        <v>6848</v>
+        <v>6846</v>
       </c>
       <c r="C3607" s="0" t="s">
-        <v>6849</v>
+        <v>6847</v>
       </c>
       <c r="D3607" s="0" t="s">
         <v>15</v>
@@ -72240,10 +72234,10 @@
         <v>3615</v>
       </c>
       <c r="B3608" s="0" t="s">
-        <v>6850</v>
+        <v>6848</v>
       </c>
       <c r="C3608" s="0" t="s">
-        <v>6851</v>
+        <v>6849</v>
       </c>
       <c r="D3608" s="0" t="s">
         <v>15</v>
@@ -72254,10 +72248,10 @@
         <v>3616</v>
       </c>
       <c r="B3609" s="0" t="s">
-        <v>6852</v>
+        <v>6850</v>
       </c>
       <c r="C3609" s="0" t="s">
-        <v>6853</v>
+        <v>6851</v>
       </c>
       <c r="D3609" s="0" t="s">
         <v>15</v>
@@ -72268,10 +72262,10 @@
         <v>3617</v>
       </c>
       <c r="B3610" s="0" t="s">
-        <v>6854</v>
+        <v>6852</v>
       </c>
       <c r="C3610" s="0" t="s">
-        <v>6855</v>
+        <v>6853</v>
       </c>
       <c r="D3610" s="0" t="s">
         <v>15</v>
@@ -72282,10 +72276,10 @@
         <v>3618</v>
       </c>
       <c r="B3611" s="0" t="s">
-        <v>6856</v>
+        <v>6854</v>
       </c>
       <c r="C3611" s="0" t="s">
-        <v>6857</v>
+        <v>6855</v>
       </c>
       <c r="D3611" s="0" t="s">
         <v>15</v>
@@ -72296,10 +72290,10 @@
         <v>3619</v>
       </c>
       <c r="B3612" s="0" t="s">
-        <v>6858</v>
+        <v>6856</v>
       </c>
       <c r="C3612" s="0" t="s">
-        <v>6859</v>
+        <v>6857</v>
       </c>
       <c r="D3612" s="0" t="s">
         <v>15</v>
@@ -72310,10 +72304,10 @@
         <v>3622</v>
       </c>
       <c r="B3613" s="0" t="s">
-        <v>6860</v>
+        <v>6858</v>
       </c>
       <c r="C3613" s="0" t="s">
-        <v>6861</v>
+        <v>6859</v>
       </c>
       <c r="D3613" s="0" t="s">
         <v>15</v>
@@ -72324,10 +72318,10 @@
         <v>3623</v>
       </c>
       <c r="B3614" s="0" t="s">
-        <v>6862</v>
+        <v>6860</v>
       </c>
       <c r="C3614" s="0" t="s">
-        <v>6863</v>
+        <v>6861</v>
       </c>
       <c r="D3614" s="0" t="s">
         <v>15</v>
@@ -72338,10 +72332,10 @@
         <v>3624</v>
       </c>
       <c r="B3615" s="0" t="s">
-        <v>6864</v>
+        <v>6862</v>
       </c>
       <c r="C3615" s="0" t="s">
-        <v>6865</v>
+        <v>6863</v>
       </c>
       <c r="D3615" s="0" t="s">
         <v>15</v>
@@ -72352,10 +72346,10 @@
         <v>3625</v>
       </c>
       <c r="B3616" s="0" t="s">
-        <v>6866</v>
+        <v>6864</v>
       </c>
       <c r="C3616" s="0" t="s">
-        <v>6867</v>
+        <v>6865</v>
       </c>
       <c r="D3616" s="0" t="s">
         <v>15</v>
@@ -72366,10 +72360,10 @@
         <v>3626</v>
       </c>
       <c r="B3617" s="0" t="s">
-        <v>6868</v>
+        <v>6866</v>
       </c>
       <c r="C3617" s="0" t="s">
-        <v>6869</v>
+        <v>6867</v>
       </c>
       <c r="D3617" s="0" t="s">
         <v>15</v>
@@ -72380,10 +72374,10 @@
         <v>3627</v>
       </c>
       <c r="B3618" s="0" t="s">
-        <v>6870</v>
+        <v>6868</v>
       </c>
       <c r="C3618" s="0" t="s">
-        <v>6871</v>
+        <v>6869</v>
       </c>
       <c r="D3618" s="0" t="s">
         <v>15</v>
@@ -72394,10 +72388,10 @@
         <v>3628</v>
       </c>
       <c r="B3619" s="0" t="s">
-        <v>6872</v>
+        <v>6870</v>
       </c>
       <c r="C3619" s="0" t="s">
-        <v>6873</v>
+        <v>6871</v>
       </c>
       <c r="D3619" s="0" t="s">
         <v>15</v>
@@ -72408,10 +72402,10 @@
         <v>3629</v>
       </c>
       <c r="B3620" s="0" t="s">
-        <v>6874</v>
+        <v>6872</v>
       </c>
       <c r="C3620" s="0" t="s">
-        <v>6875</v>
+        <v>6873</v>
       </c>
       <c r="D3620" s="0" t="s">
         <v>15</v>
@@ -72422,10 +72416,10 @@
         <v>3630</v>
       </c>
       <c r="B3621" s="0" t="s">
-        <v>6874</v>
+        <v>6872</v>
       </c>
       <c r="C3621" s="0" t="s">
-        <v>6875</v>
+        <v>6873</v>
       </c>
       <c r="D3621" s="0" t="s">
         <v>15</v>
@@ -72436,10 +72430,10 @@
         <v>3631</v>
       </c>
       <c r="B3622" s="0" t="s">
-        <v>6876</v>
+        <v>6874</v>
       </c>
       <c r="C3622" s="0" t="s">
-        <v>6876</v>
+        <v>6874</v>
       </c>
       <c r="D3622" s="0" t="s">
         <v>15</v>
@@ -72450,10 +72444,10 @@
         <v>3632</v>
       </c>
       <c r="B3623" s="0" t="s">
-        <v>6877</v>
+        <v>6875</v>
       </c>
       <c r="C3623" s="0" t="s">
-        <v>6878</v>
+        <v>6876</v>
       </c>
       <c r="D3623" s="0" t="s">
         <v>15</v>
@@ -72464,10 +72458,10 @@
         <v>3633</v>
       </c>
       <c r="B3624" s="0" t="s">
-        <v>6879</v>
+        <v>6877</v>
       </c>
       <c r="C3624" s="0" t="s">
-        <v>6880</v>
+        <v>6878</v>
       </c>
       <c r="D3624" s="0" t="s">
         <v>15</v>
@@ -72478,10 +72472,10 @@
         <v>3634</v>
       </c>
       <c r="B3625" s="0" t="s">
-        <v>6881</v>
+        <v>6879</v>
       </c>
       <c r="C3625" s="0" t="s">
-        <v>6882</v>
+        <v>6880</v>
       </c>
       <c r="D3625" s="0" t="s">
         <v>15</v>
@@ -72492,10 +72486,10 @@
         <v>3635</v>
       </c>
       <c r="B3626" s="0" t="s">
-        <v>6883</v>
+        <v>6881</v>
       </c>
       <c r="C3626" s="0" t="s">
-        <v>6884</v>
+        <v>6882</v>
       </c>
       <c r="D3626" s="0" t="s">
         <v>15</v>
@@ -72506,10 +72500,10 @@
         <v>3636</v>
       </c>
       <c r="B3627" s="0" t="s">
-        <v>6885</v>
+        <v>6883</v>
       </c>
       <c r="C3627" s="0" t="s">
-        <v>6886</v>
+        <v>6884</v>
       </c>
       <c r="D3627" s="0" t="s">
         <v>15</v>
@@ -72520,10 +72514,10 @@
         <v>3637</v>
       </c>
       <c r="B3628" s="0" t="s">
-        <v>6887</v>
+        <v>6885</v>
       </c>
       <c r="C3628" s="0" t="s">
-        <v>6888</v>
+        <v>6886</v>
       </c>
       <c r="D3628" s="0" t="s">
         <v>15</v>
@@ -72534,10 +72528,10 @@
         <v>3638</v>
       </c>
       <c r="B3629" s="0" t="s">
-        <v>6889</v>
+        <v>6887</v>
       </c>
       <c r="C3629" s="0" t="s">
-        <v>6890</v>
+        <v>6888</v>
       </c>
       <c r="D3629" s="0" t="s">
         <v>15</v>
@@ -72548,10 +72542,10 @@
         <v>3639</v>
       </c>
       <c r="B3630" s="0" t="s">
-        <v>6891</v>
+        <v>6889</v>
       </c>
       <c r="C3630" s="0" t="s">
-        <v>6892</v>
+        <v>6890</v>
       </c>
       <c r="D3630" s="0" t="s">
         <v>15</v>
@@ -72562,10 +72556,10 @@
         <v>3640</v>
       </c>
       <c r="B3631" s="0" t="s">
-        <v>6893</v>
+        <v>6891</v>
       </c>
       <c r="C3631" s="0" t="s">
-        <v>6894</v>
+        <v>6892</v>
       </c>
       <c r="D3631" s="0" t="s">
         <v>15</v>
@@ -72576,10 +72570,10 @@
         <v>3641</v>
       </c>
       <c r="B3632" s="0" t="s">
-        <v>6895</v>
+        <v>6893</v>
       </c>
       <c r="C3632" s="0" t="s">
-        <v>6895</v>
+        <v>6893</v>
       </c>
       <c r="D3632" s="0" t="s">
         <v>15</v>
@@ -72590,10 +72584,10 @@
         <v>3642</v>
       </c>
       <c r="B3633" s="0" t="s">
-        <v>6896</v>
+        <v>6894</v>
       </c>
       <c r="C3633" s="0" t="s">
-        <v>6897</v>
+        <v>6895</v>
       </c>
       <c r="D3633" s="0" t="s">
         <v>15</v>
@@ -72604,10 +72598,10 @@
         <v>3643</v>
       </c>
       <c r="B3634" s="0" t="s">
-        <v>6898</v>
+        <v>6896</v>
       </c>
       <c r="C3634" s="0" t="s">
-        <v>6899</v>
+        <v>6897</v>
       </c>
       <c r="D3634" s="0" t="s">
         <v>15</v>
@@ -72618,10 +72612,10 @@
         <v>3644</v>
       </c>
       <c r="B3635" s="0" t="s">
-        <v>6900</v>
+        <v>6898</v>
       </c>
       <c r="C3635" s="0" t="s">
-        <v>6901</v>
+        <v>6899</v>
       </c>
       <c r="D3635" s="0" t="s">
         <v>15</v>
@@ -72632,10 +72626,10 @@
         <v>3645</v>
       </c>
       <c r="B3636" s="0" t="s">
-        <v>6902</v>
+        <v>6900</v>
       </c>
       <c r="C3636" s="0" t="s">
-        <v>6903</v>
+        <v>6901</v>
       </c>
       <c r="D3636" s="0" t="s">
         <v>15</v>
@@ -72646,10 +72640,10 @@
         <v>3646</v>
       </c>
       <c r="B3637" s="0" t="s">
-        <v>6904</v>
+        <v>6902</v>
       </c>
       <c r="C3637" s="0" t="s">
-        <v>6904</v>
+        <v>6902</v>
       </c>
       <c r="D3637" s="0" t="s">
         <v>15</v>
@@ -72660,10 +72654,10 @@
         <v>3647</v>
       </c>
       <c r="B3638" s="0" t="s">
-        <v>6905</v>
+        <v>6903</v>
       </c>
       <c r="C3638" s="0" t="s">
-        <v>6905</v>
+        <v>6903</v>
       </c>
       <c r="D3638" s="0" t="s">
         <v>15</v>
@@ -72674,10 +72668,10 @@
         <v>3648</v>
       </c>
       <c r="B3639" s="0" t="s">
-        <v>6906</v>
+        <v>6904</v>
       </c>
       <c r="C3639" s="0" t="s">
-        <v>6907</v>
+        <v>6905</v>
       </c>
       <c r="D3639" s="0" t="s">
         <v>15</v>
@@ -72688,10 +72682,10 @@
         <v>3649</v>
       </c>
       <c r="B3640" s="0" t="s">
-        <v>6908</v>
+        <v>6906</v>
       </c>
       <c r="C3640" s="0" t="s">
-        <v>6909</v>
+        <v>6907</v>
       </c>
       <c r="D3640" s="0" t="s">
         <v>15</v>
@@ -72702,10 +72696,10 @@
         <v>3650</v>
       </c>
       <c r="B3641" s="0" t="s">
-        <v>6910</v>
+        <v>6908</v>
       </c>
       <c r="C3641" s="0" t="s">
-        <v>6911</v>
+        <v>6909</v>
       </c>
       <c r="D3641" s="0" t="s">
         <v>15</v>
@@ -72716,10 +72710,10 @@
         <v>3651</v>
       </c>
       <c r="B3642" s="0" t="s">
-        <v>6912</v>
+        <v>6910</v>
       </c>
       <c r="C3642" s="0" t="s">
-        <v>6913</v>
+        <v>6911</v>
       </c>
       <c r="D3642" s="0" t="s">
         <v>15</v>
@@ -72730,10 +72724,10 @@
         <v>3652</v>
       </c>
       <c r="B3643" s="0" t="s">
-        <v>6914</v>
+        <v>6912</v>
       </c>
       <c r="C3643" s="0" t="s">
-        <v>6915</v>
+        <v>6913</v>
       </c>
       <c r="D3643" s="0" t="s">
         <v>15</v>
@@ -72744,10 +72738,10 @@
         <v>3653</v>
       </c>
       <c r="B3644" s="0" t="s">
-        <v>6916</v>
+        <v>6914</v>
       </c>
       <c r="C3644" s="0" t="s">
-        <v>6917</v>
+        <v>6915</v>
       </c>
       <c r="D3644" s="0" t="s">
         <v>15</v>
@@ -72758,10 +72752,10 @@
         <v>3654</v>
       </c>
       <c r="B3645" s="0" t="s">
-        <v>6918</v>
+        <v>6916</v>
       </c>
       <c r="C3645" s="0" t="s">
-        <v>6919</v>
+        <v>6917</v>
       </c>
       <c r="D3645" s="0" t="s">
         <v>15</v>
@@ -72772,10 +72766,10 @@
         <v>3655</v>
       </c>
       <c r="B3646" s="0" t="s">
-        <v>6920</v>
+        <v>6918</v>
       </c>
       <c r="C3646" s="0" t="s">
-        <v>6921</v>
+        <v>6919</v>
       </c>
       <c r="D3646" s="0" t="s">
         <v>15</v>
@@ -72786,10 +72780,10 @@
         <v>3656</v>
       </c>
       <c r="B3647" s="0" t="s">
-        <v>6922</v>
+        <v>6920</v>
       </c>
       <c r="C3647" s="0" t="s">
-        <v>6922</v>
+        <v>6920</v>
       </c>
       <c r="D3647" s="0" t="s">
         <v>15</v>
@@ -72800,10 +72794,10 @@
         <v>3657</v>
       </c>
       <c r="B3648" s="0" t="s">
-        <v>6923</v>
+        <v>6921</v>
       </c>
       <c r="C3648" s="0" t="s">
-        <v>6923</v>
+        <v>6921</v>
       </c>
       <c r="D3648" s="0" t="s">
         <v>15</v>
@@ -72814,10 +72808,10 @@
         <v>3658</v>
       </c>
       <c r="B3649" s="0" t="s">
-        <v>6924</v>
+        <v>6922</v>
       </c>
       <c r="C3649" s="0" t="s">
-        <v>6924</v>
+        <v>6922</v>
       </c>
       <c r="D3649" s="0" t="s">
         <v>15</v>
@@ -72828,10 +72822,10 @@
         <v>3659</v>
       </c>
       <c r="B3650" s="0" t="s">
-        <v>6925</v>
+        <v>6923</v>
       </c>
       <c r="C3650" s="0" t="s">
-        <v>6925</v>
+        <v>6923</v>
       </c>
       <c r="D3650" s="0" t="s">
         <v>15</v>
@@ -72842,10 +72836,10 @@
         <v>3660</v>
       </c>
       <c r="B3651" s="0" t="s">
-        <v>6926</v>
+        <v>6924</v>
       </c>
       <c r="C3651" s="0" t="s">
-        <v>6926</v>
+        <v>6924</v>
       </c>
       <c r="D3651" s="0" t="s">
         <v>15</v>
@@ -72856,10 +72850,10 @@
         <v>3661</v>
       </c>
       <c r="B3652" s="0" t="s">
-        <v>6927</v>
+        <v>6925</v>
       </c>
       <c r="C3652" s="0" t="s">
-        <v>6927</v>
+        <v>6925</v>
       </c>
       <c r="D3652" s="0" t="s">
         <v>15</v>
@@ -72870,10 +72864,10 @@
         <v>3662</v>
       </c>
       <c r="B3653" s="0" t="s">
-        <v>6928</v>
+        <v>6926</v>
       </c>
       <c r="C3653" s="0" t="s">
-        <v>6928</v>
+        <v>6926</v>
       </c>
       <c r="D3653" s="0" t="s">
         <v>15</v>
@@ -72884,10 +72878,10 @@
         <v>3663</v>
       </c>
       <c r="B3654" s="0" t="s">
-        <v>6929</v>
+        <v>6927</v>
       </c>
       <c r="C3654" s="0" t="s">
-        <v>6929</v>
+        <v>6927</v>
       </c>
       <c r="D3654" s="0" t="s">
         <v>15</v>
@@ -72898,10 +72892,10 @@
         <v>3664</v>
       </c>
       <c r="B3655" s="0" t="s">
-        <v>6930</v>
+        <v>6928</v>
       </c>
       <c r="C3655" s="0" t="s">
-        <v>6930</v>
+        <v>6928</v>
       </c>
       <c r="D3655" s="0" t="s">
         <v>15</v>
@@ -72912,10 +72906,10 @@
         <v>3665</v>
       </c>
       <c r="B3656" s="0" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C3656" s="0" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="D3656" s="0" t="s">
         <v>15</v>
@@ -72926,10 +72920,10 @@
         <v>3666</v>
       </c>
       <c r="B3657" s="0" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
       <c r="C3657" s="0" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="D3657" s="0" t="s">
         <v>15</v>
@@ -72940,10 +72934,10 @@
         <v>3667</v>
       </c>
       <c r="B3658" s="0" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
       <c r="C3658" s="0" t="s">
-        <v>6935</v>
+        <v>6933</v>
       </c>
       <c r="D3658" s="0" t="s">
         <v>15</v>
@@ -72954,10 +72948,10 @@
         <v>3668</v>
       </c>
       <c r="B3659" s="0" t="s">
-        <v>6936</v>
+        <v>6934</v>
       </c>
       <c r="C3659" s="0" t="s">
-        <v>6937</v>
+        <v>6935</v>
       </c>
       <c r="D3659" s="0" t="s">
         <v>15</v>
@@ -72968,10 +72962,10 @@
         <v>3669</v>
       </c>
       <c r="B3660" s="0" t="s">
-        <v>6938</v>
+        <v>6936</v>
       </c>
       <c r="C3660" s="0" t="s">
-        <v>6939</v>
+        <v>6937</v>
       </c>
       <c r="D3660" s="0" t="s">
         <v>15</v>
@@ -72982,10 +72976,10 @@
         <v>3670</v>
       </c>
       <c r="B3661" s="0" t="s">
-        <v>6940</v>
+        <v>6938</v>
       </c>
       <c r="C3661" s="0" t="s">
-        <v>6941</v>
+        <v>6939</v>
       </c>
       <c r="D3661" s="0" t="s">
         <v>15</v>
@@ -72996,10 +72990,10 @@
         <v>3671</v>
       </c>
       <c r="B3662" s="0" t="s">
-        <v>6942</v>
+        <v>6940</v>
       </c>
       <c r="C3662" s="0" t="s">
-        <v>6943</v>
+        <v>6941</v>
       </c>
       <c r="D3662" s="0" t="s">
         <v>15</v>
@@ -73010,10 +73004,10 @@
         <v>3672</v>
       </c>
       <c r="B3663" s="0" t="s">
-        <v>6944</v>
+        <v>6942</v>
       </c>
       <c r="C3663" s="0" t="s">
-        <v>6945</v>
+        <v>6943</v>
       </c>
       <c r="D3663" s="0" t="s">
         <v>15</v>
@@ -73024,10 +73018,10 @@
         <v>3673</v>
       </c>
       <c r="B3664" s="0" t="s">
-        <v>6946</v>
+        <v>6944</v>
       </c>
       <c r="C3664" s="0" t="s">
-        <v>6947</v>
+        <v>6945</v>
       </c>
       <c r="D3664" s="0" t="s">
         <v>15</v>
@@ -73038,10 +73032,10 @@
         <v>3674</v>
       </c>
       <c r="B3665" s="0" t="s">
-        <v>6948</v>
+        <v>6946</v>
       </c>
       <c r="C3665" s="0" t="s">
-        <v>6949</v>
+        <v>6947</v>
       </c>
       <c r="D3665" s="0" t="s">
         <v>15</v>
@@ -73052,7 +73046,7 @@
         <v>3675</v>
       </c>
       <c r="B3666" s="0" t="s">
-        <v>6950</v>
+        <v>6948</v>
       </c>
       <c r="C3666" s="0" t="s">
         <v>721</v>
@@ -73066,10 +73060,10 @@
         <v>3676</v>
       </c>
       <c r="B3667" s="0" t="s">
-        <v>6951</v>
+        <v>6949</v>
       </c>
       <c r="C3667" s="0" t="s">
-        <v>6952</v>
+        <v>6950</v>
       </c>
       <c r="D3667" s="0" t="s">
         <v>15</v>
@@ -73080,10 +73074,10 @@
         <v>3677</v>
       </c>
       <c r="B3668" s="0" t="s">
-        <v>6953</v>
+        <v>6951</v>
       </c>
       <c r="C3668" s="0" t="s">
-        <v>6954</v>
+        <v>6952</v>
       </c>
       <c r="D3668" s="0" t="s">
         <v>15</v>
@@ -73094,10 +73088,10 @@
         <v>3679</v>
       </c>
       <c r="B3669" s="0" t="s">
-        <v>6955</v>
+        <v>6953</v>
       </c>
       <c r="C3669" s="0" t="s">
-        <v>6956</v>
+        <v>6954</v>
       </c>
       <c r="D3669" s="0" t="s">
         <v>15</v>
@@ -73108,10 +73102,10 @@
         <v>3681</v>
       </c>
       <c r="B3670" s="0" t="s">
-        <v>6957</v>
+        <v>6955</v>
       </c>
       <c r="C3670" s="0" t="s">
-        <v>6958</v>
+        <v>6956</v>
       </c>
       <c r="D3670" s="0" t="s">
         <v>15</v>
@@ -73122,10 +73116,10 @@
         <v>3682</v>
       </c>
       <c r="B3671" s="0" t="s">
-        <v>6959</v>
+        <v>6957</v>
       </c>
       <c r="C3671" s="0" t="s">
-        <v>6960</v>
+        <v>6958</v>
       </c>
       <c r="D3671" s="0" t="s">
         <v>15</v>
@@ -73136,10 +73130,10 @@
         <v>3683</v>
       </c>
       <c r="B3672" s="0" t="s">
-        <v>6961</v>
+        <v>6959</v>
       </c>
       <c r="C3672" s="0" t="s">
-        <v>6962</v>
+        <v>6960</v>
       </c>
       <c r="D3672" s="0" t="s">
         <v>15</v>
@@ -73150,10 +73144,10 @@
         <v>3684</v>
       </c>
       <c r="B3673" s="0" t="s">
-        <v>6963</v>
+        <v>6961</v>
       </c>
       <c r="C3673" s="0" t="s">
-        <v>6964</v>
+        <v>6962</v>
       </c>
       <c r="D3673" s="0" t="s">
         <v>15</v>
@@ -73164,10 +73158,10 @@
         <v>3685</v>
       </c>
       <c r="B3674" s="0" t="s">
-        <v>6965</v>
+        <v>6963</v>
       </c>
       <c r="C3674" s="0" t="s">
-        <v>6966</v>
+        <v>6964</v>
       </c>
       <c r="D3674" s="0" t="s">
         <v>15</v>
@@ -73178,10 +73172,10 @@
         <v>3686</v>
       </c>
       <c r="B3675" s="0" t="s">
-        <v>6967</v>
+        <v>6965</v>
       </c>
       <c r="C3675" s="0" t="s">
-        <v>6968</v>
+        <v>6966</v>
       </c>
       <c r="D3675" s="0" t="s">
         <v>15</v>
@@ -73192,10 +73186,10 @@
         <v>3687</v>
       </c>
       <c r="B3676" s="0" t="s">
-        <v>6969</v>
+        <v>6967</v>
       </c>
       <c r="C3676" s="0" t="s">
-        <v>6970</v>
+        <v>6968</v>
       </c>
       <c r="D3676" s="0" t="s">
         <v>15</v>
@@ -73206,10 +73200,10 @@
         <v>3688</v>
       </c>
       <c r="B3677" s="0" t="s">
-        <v>6971</v>
+        <v>6969</v>
       </c>
       <c r="C3677" s="0" t="s">
-        <v>6972</v>
+        <v>6970</v>
       </c>
       <c r="D3677" s="0" t="s">
         <v>15</v>
@@ -73220,10 +73214,10 @@
         <v>3689</v>
       </c>
       <c r="B3678" s="0" t="s">
-        <v>6973</v>
+        <v>6971</v>
       </c>
       <c r="C3678" s="0" t="s">
-        <v>6974</v>
+        <v>6972</v>
       </c>
       <c r="D3678" s="0" t="s">
         <v>15</v>
@@ -73234,10 +73228,10 @@
         <v>3690</v>
       </c>
       <c r="B3679" s="0" t="s">
-        <v>6975</v>
+        <v>6973</v>
       </c>
       <c r="C3679" s="0" t="s">
-        <v>6976</v>
+        <v>6974</v>
       </c>
       <c r="D3679" s="0" t="s">
         <v>15</v>
@@ -73248,10 +73242,10 @@
         <v>3691</v>
       </c>
       <c r="B3680" s="0" t="s">
-        <v>6977</v>
+        <v>6975</v>
       </c>
       <c r="C3680" s="0" t="s">
-        <v>6978</v>
+        <v>6976</v>
       </c>
       <c r="D3680" s="0" t="s">
         <v>15</v>
@@ -73262,10 +73256,10 @@
         <v>3692</v>
       </c>
       <c r="B3681" s="0" t="s">
-        <v>6979</v>
+        <v>6977</v>
       </c>
       <c r="C3681" s="0" t="s">
-        <v>6980</v>
+        <v>6978</v>
       </c>
       <c r="D3681" s="0" t="s">
         <v>15</v>
@@ -73276,10 +73270,10 @@
         <v>3693</v>
       </c>
       <c r="B3682" s="0" t="s">
-        <v>6981</v>
+        <v>6979</v>
       </c>
       <c r="C3682" s="0" t="s">
-        <v>6982</v>
+        <v>6980</v>
       </c>
       <c r="D3682" s="0" t="s">
         <v>15</v>
@@ -73290,10 +73284,10 @@
         <v>3694</v>
       </c>
       <c r="B3683" s="0" t="s">
-        <v>6983</v>
+        <v>6981</v>
       </c>
       <c r="C3683" s="0" t="s">
-        <v>6984</v>
+        <v>6982</v>
       </c>
       <c r="D3683" s="0" t="s">
         <v>15</v>
@@ -73304,10 +73298,10 @@
         <v>3695</v>
       </c>
       <c r="B3684" s="0" t="s">
-        <v>6985</v>
+        <v>6983</v>
       </c>
       <c r="C3684" s="0" t="s">
-        <v>6986</v>
+        <v>6984</v>
       </c>
       <c r="D3684" s="0" t="s">
         <v>15</v>
@@ -73318,10 +73312,10 @@
         <v>3696</v>
       </c>
       <c r="B3685" s="0" t="s">
-        <v>6987</v>
+        <v>6985</v>
       </c>
       <c r="C3685" s="0" t="s">
-        <v>6988</v>
+        <v>6986</v>
       </c>
       <c r="D3685" s="0" t="s">
         <v>15</v>
@@ -73332,10 +73326,10 @@
         <v>3697</v>
       </c>
       <c r="B3686" s="0" t="s">
-        <v>6989</v>
+        <v>6987</v>
       </c>
       <c r="C3686" s="0" t="s">
-        <v>6990</v>
+        <v>6988</v>
       </c>
       <c r="D3686" s="0" t="s">
         <v>15</v>
@@ -73346,10 +73340,10 @@
         <v>3698</v>
       </c>
       <c r="B3687" s="0" t="s">
-        <v>6991</v>
+        <v>6989</v>
       </c>
       <c r="C3687" s="0" t="s">
-        <v>6992</v>
+        <v>6990</v>
       </c>
       <c r="D3687" s="0" t="s">
         <v>15</v>
@@ -73360,10 +73354,10 @@
         <v>3699</v>
       </c>
       <c r="B3688" s="0" t="s">
-        <v>6993</v>
+        <v>6991</v>
       </c>
       <c r="C3688" s="0" t="s">
-        <v>6994</v>
+        <v>6992</v>
       </c>
       <c r="D3688" s="0" t="s">
         <v>15</v>
@@ -73374,10 +73368,10 @@
         <v>3700</v>
       </c>
       <c r="B3689" s="0" t="s">
-        <v>6995</v>
+        <v>6993</v>
       </c>
       <c r="C3689" s="0" t="s">
-        <v>6996</v>
+        <v>6994</v>
       </c>
       <c r="D3689" s="0" t="s">
         <v>15</v>
@@ -73388,10 +73382,10 @@
         <v>3701</v>
       </c>
       <c r="B3690" s="0" t="s">
-        <v>6997</v>
+        <v>6995</v>
       </c>
       <c r="C3690" s="0" t="s">
-        <v>6998</v>
+        <v>6996</v>
       </c>
       <c r="D3690" s="0" t="s">
         <v>15</v>
@@ -73402,10 +73396,10 @@
         <v>3702</v>
       </c>
       <c r="B3691" s="0" t="s">
-        <v>6999</v>
+        <v>6997</v>
       </c>
       <c r="C3691" s="0" t="s">
-        <v>7000</v>
+        <v>6998</v>
       </c>
       <c r="D3691" s="0" t="s">
         <v>15</v>
@@ -73416,10 +73410,10 @@
         <v>3703</v>
       </c>
       <c r="B3692" s="0" t="s">
-        <v>7001</v>
+        <v>6999</v>
       </c>
       <c r="C3692" s="0" t="s">
-        <v>7002</v>
+        <v>7000</v>
       </c>
       <c r="D3692" s="0" t="s">
         <v>15</v>
@@ -73430,10 +73424,10 @@
         <v>3704</v>
       </c>
       <c r="B3693" s="0" t="s">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="C3693" s="0" t="s">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="D3693" s="0" t="s">
         <v>15</v>
@@ -73444,10 +73438,10 @@
         <v>3705</v>
       </c>
       <c r="B3694" s="0" t="s">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C3694" s="0" t="s">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="D3694" s="0" t="s">
         <v>15</v>
@@ -73458,10 +73452,10 @@
         <v>3706</v>
       </c>
       <c r="B3695" s="0" t="s">
-        <v>7007</v>
+        <v>7005</v>
       </c>
       <c r="C3695" s="0" t="s">
-        <v>7008</v>
+        <v>7006</v>
       </c>
       <c r="D3695" s="0" t="s">
         <v>15</v>
@@ -73472,10 +73466,10 @@
         <v>3707</v>
       </c>
       <c r="B3696" s="0" t="s">
-        <v>7009</v>
+        <v>7007</v>
       </c>
       <c r="C3696" s="0" t="s">
-        <v>7010</v>
+        <v>7008</v>
       </c>
       <c r="D3696" s="0" t="s">
         <v>15</v>
@@ -73486,10 +73480,10 @@
         <v>3708</v>
       </c>
       <c r="B3697" s="0" t="s">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="C3697" s="0" t="s">
-        <v>7012</v>
+        <v>7010</v>
       </c>
       <c r="D3697" s="0" t="s">
         <v>15</v>
@@ -73500,10 +73494,10 @@
         <v>3709</v>
       </c>
       <c r="B3698" s="0" t="s">
-        <v>7013</v>
+        <v>7011</v>
       </c>
       <c r="C3698" s="0" t="s">
-        <v>7014</v>
+        <v>7012</v>
       </c>
       <c r="D3698" s="0" t="s">
         <v>15</v>
@@ -73514,10 +73508,10 @@
         <v>3710</v>
       </c>
       <c r="B3699" s="0" t="s">
-        <v>7015</v>
+        <v>7013</v>
       </c>
       <c r="C3699" s="0" t="s">
-        <v>7016</v>
+        <v>7014</v>
       </c>
       <c r="D3699" s="0" t="s">
         <v>15</v>
@@ -73528,10 +73522,10 @@
         <v>3711</v>
       </c>
       <c r="B3700" s="0" t="s">
-        <v>7017</v>
+        <v>7015</v>
       </c>
       <c r="C3700" s="0" t="s">
-        <v>7018</v>
+        <v>7016</v>
       </c>
       <c r="D3700" s="0" t="s">
         <v>15</v>
@@ -73542,10 +73536,10 @@
         <v>3712</v>
       </c>
       <c r="B3701" s="0" t="s">
-        <v>7019</v>
+        <v>7017</v>
       </c>
       <c r="C3701" s="0" t="s">
-        <v>7020</v>
+        <v>7018</v>
       </c>
       <c r="D3701" s="0" t="s">
         <v>15</v>
@@ -73556,10 +73550,10 @@
         <v>3713</v>
       </c>
       <c r="B3702" s="0" t="s">
-        <v>7021</v>
+        <v>7019</v>
       </c>
       <c r="C3702" s="0" t="s">
-        <v>7022</v>
+        <v>7020</v>
       </c>
       <c r="D3702" s="0" t="s">
         <v>15</v>
@@ -73570,10 +73564,10 @@
         <v>3714</v>
       </c>
       <c r="B3703" s="0" t="s">
-        <v>7023</v>
+        <v>7021</v>
       </c>
       <c r="C3703" s="0" t="s">
-        <v>7024</v>
+        <v>7022</v>
       </c>
       <c r="D3703" s="0" t="s">
         <v>15</v>
@@ -73584,10 +73578,10 @@
         <v>3715</v>
       </c>
       <c r="B3704" s="0" t="s">
-        <v>7025</v>
+        <v>7023</v>
       </c>
       <c r="C3704" s="0" t="s">
-        <v>7026</v>
+        <v>7024</v>
       </c>
       <c r="D3704" s="0" t="s">
         <v>15</v>
@@ -73598,10 +73592,10 @@
         <v>3716</v>
       </c>
       <c r="B3705" s="0" t="s">
-        <v>7027</v>
+        <v>7025</v>
       </c>
       <c r="C3705" s="0" t="s">
-        <v>7028</v>
+        <v>7026</v>
       </c>
       <c r="D3705" s="0" t="s">
         <v>15</v>
@@ -73612,10 +73606,10 @@
         <v>3717</v>
       </c>
       <c r="B3706" s="0" t="s">
-        <v>7029</v>
+        <v>7027</v>
       </c>
       <c r="C3706" s="0" t="s">
-        <v>7030</v>
+        <v>7028</v>
       </c>
       <c r="D3706" s="0" t="s">
         <v>15</v>
@@ -73626,10 +73620,10 @@
         <v>3718</v>
       </c>
       <c r="B3707" s="0" t="s">
-        <v>7031</v>
+        <v>7029</v>
       </c>
       <c r="C3707" s="0" t="s">
-        <v>7032</v>
+        <v>7030</v>
       </c>
       <c r="D3707" s="0" t="s">
         <v>15</v>
@@ -73640,10 +73634,10 @@
         <v>3719</v>
       </c>
       <c r="B3708" s="0" t="s">
-        <v>7033</v>
+        <v>7031</v>
       </c>
       <c r="C3708" s="0" t="s">
-        <v>7034</v>
+        <v>7032</v>
       </c>
       <c r="D3708" s="0" t="s">
         <v>15</v>
@@ -73654,10 +73648,10 @@
         <v>3720</v>
       </c>
       <c r="B3709" s="0" t="s">
-        <v>7035</v>
+        <v>7033</v>
       </c>
       <c r="C3709" s="0" t="s">
-        <v>7036</v>
+        <v>7034</v>
       </c>
       <c r="D3709" s="0" t="s">
         <v>15</v>
@@ -73668,10 +73662,10 @@
         <v>3721</v>
       </c>
       <c r="B3710" s="0" t="s">
-        <v>7037</v>
+        <v>7035</v>
       </c>
       <c r="C3710" s="0" t="s">
-        <v>7038</v>
+        <v>7036</v>
       </c>
       <c r="D3710" s="0" t="s">
         <v>15</v>
@@ -73682,10 +73676,10 @@
         <v>3722</v>
       </c>
       <c r="B3711" s="0" t="s">
-        <v>7039</v>
+        <v>7037</v>
       </c>
       <c r="C3711" s="0" t="s">
-        <v>7040</v>
+        <v>7038</v>
       </c>
       <c r="D3711" s="0" t="s">
         <v>15</v>
@@ -73696,10 +73690,10 @@
         <v>3723</v>
       </c>
       <c r="B3712" s="0" t="s">
-        <v>7041</v>
+        <v>7039</v>
       </c>
       <c r="C3712" s="0" t="s">
-        <v>7042</v>
+        <v>7040</v>
       </c>
       <c r="D3712" s="0" t="s">
         <v>15</v>
@@ -73710,10 +73704,10 @@
         <v>3724</v>
       </c>
       <c r="B3713" s="0" t="s">
-        <v>7043</v>
+        <v>7041</v>
       </c>
       <c r="C3713" s="0" t="s">
-        <v>7044</v>
+        <v>7042</v>
       </c>
       <c r="D3713" s="0" t="s">
         <v>15</v>
@@ -73724,10 +73718,10 @@
         <v>3725</v>
       </c>
       <c r="B3714" s="0" t="s">
-        <v>7045</v>
+        <v>7043</v>
       </c>
       <c r="C3714" s="0" t="s">
-        <v>7046</v>
+        <v>7044</v>
       </c>
       <c r="D3714" s="0" t="s">
         <v>15</v>
@@ -73738,10 +73732,10 @@
         <v>3726</v>
       </c>
       <c r="B3715" s="0" t="s">
-        <v>7047</v>
+        <v>7045</v>
       </c>
       <c r="C3715" s="0" t="s">
-        <v>7048</v>
+        <v>7046</v>
       </c>
       <c r="D3715" s="0" t="s">
         <v>15</v>
@@ -73752,10 +73746,10 @@
         <v>3727</v>
       </c>
       <c r="B3716" s="0" t="s">
-        <v>7049</v>
+        <v>7047</v>
       </c>
       <c r="C3716" s="0" t="s">
-        <v>7050</v>
+        <v>7048</v>
       </c>
       <c r="D3716" s="0" t="s">
         <v>15</v>
@@ -73766,10 +73760,10 @@
         <v>3728</v>
       </c>
       <c r="B3717" s="0" t="s">
-        <v>7051</v>
+        <v>7049</v>
       </c>
       <c r="C3717" s="0" t="s">
-        <v>7052</v>
+        <v>7050</v>
       </c>
       <c r="D3717" s="0" t="s">
         <v>15</v>
@@ -73780,10 +73774,10 @@
         <v>3729</v>
       </c>
       <c r="B3718" s="0" t="s">
-        <v>7053</v>
+        <v>7051</v>
       </c>
       <c r="C3718" s="0" t="s">
-        <v>7053</v>
+        <v>7051</v>
       </c>
       <c r="D3718" s="0" t="s">
         <v>15</v>
@@ -73794,10 +73788,10 @@
         <v>3730</v>
       </c>
       <c r="B3719" s="0" t="s">
-        <v>7054</v>
+        <v>7052</v>
       </c>
       <c r="C3719" s="0" t="s">
-        <v>7055</v>
+        <v>7053</v>
       </c>
       <c r="D3719" s="0" t="s">
         <v>15</v>
@@ -73808,10 +73802,10 @@
         <v>3731</v>
       </c>
       <c r="B3720" s="0" t="s">
-        <v>7056</v>
+        <v>7054</v>
       </c>
       <c r="C3720" s="0" t="s">
-        <v>7057</v>
+        <v>7055</v>
       </c>
       <c r="D3720" s="0" t="s">
         <v>15</v>
@@ -73822,10 +73816,10 @@
         <v>3732</v>
       </c>
       <c r="B3721" s="0" t="s">
-        <v>7058</v>
+        <v>7056</v>
       </c>
       <c r="C3721" s="0" t="s">
-        <v>7059</v>
+        <v>7057</v>
       </c>
       <c r="D3721" s="0" t="s">
         <v>15</v>
@@ -73836,10 +73830,10 @@
         <v>3733</v>
       </c>
       <c r="B3722" s="0" t="s">
-        <v>7060</v>
+        <v>7058</v>
       </c>
       <c r="C3722" s="0" t="s">
-        <v>7061</v>
+        <v>7059</v>
       </c>
       <c r="D3722" s="0" t="s">
         <v>15</v>
@@ -73850,10 +73844,10 @@
         <v>3734</v>
       </c>
       <c r="B3723" s="0" t="s">
-        <v>7062</v>
+        <v>7060</v>
       </c>
       <c r="C3723" s="0" t="s">
-        <v>7063</v>
+        <v>7061</v>
       </c>
       <c r="D3723" s="0" t="s">
         <v>15</v>
@@ -73864,10 +73858,10 @@
         <v>3735</v>
       </c>
       <c r="B3724" s="0" t="s">
-        <v>7064</v>
+        <v>7062</v>
       </c>
       <c r="C3724" s="0" t="s">
-        <v>7065</v>
+        <v>7063</v>
       </c>
       <c r="D3724" s="0" t="s">
         <v>15</v>
@@ -73878,10 +73872,10 @@
         <v>3736</v>
       </c>
       <c r="B3725" s="0" t="s">
-        <v>7066</v>
+        <v>7064</v>
       </c>
       <c r="C3725" s="0" t="s">
-        <v>7067</v>
+        <v>7065</v>
       </c>
       <c r="D3725" s="0" t="s">
         <v>15</v>
@@ -73892,10 +73886,10 @@
         <v>3737</v>
       </c>
       <c r="B3726" s="0" t="s">
-        <v>7068</v>
+        <v>7066</v>
       </c>
       <c r="C3726" s="0" t="s">
-        <v>7069</v>
+        <v>7067</v>
       </c>
       <c r="D3726" s="0" t="s">
         <v>15</v>
@@ -73906,10 +73900,10 @@
         <v>3738</v>
       </c>
       <c r="B3727" s="0" t="s">
-        <v>7070</v>
+        <v>7068</v>
       </c>
       <c r="C3727" s="0" t="s">
-        <v>7071</v>
+        <v>7069</v>
       </c>
       <c r="D3727" s="0" t="s">
         <v>15</v>
@@ -73920,10 +73914,10 @@
         <v>3739</v>
       </c>
       <c r="B3728" s="0" t="s">
-        <v>7072</v>
+        <v>7070</v>
       </c>
       <c r="C3728" s="0" t="s">
-        <v>7073</v>
+        <v>7071</v>
       </c>
       <c r="D3728" s="0" t="s">
         <v>15</v>
@@ -73934,10 +73928,10 @@
         <v>3740</v>
       </c>
       <c r="B3729" s="0" t="s">
-        <v>7074</v>
+        <v>7072</v>
       </c>
       <c r="C3729" s="0" t="s">
-        <v>7075</v>
+        <v>7073</v>
       </c>
       <c r="D3729" s="0" t="s">
         <v>15</v>
@@ -73948,10 +73942,10 @@
         <v>3741</v>
       </c>
       <c r="B3730" s="0" t="s">
-        <v>7076</v>
+        <v>7074</v>
       </c>
       <c r="C3730" s="0" t="s">
-        <v>7077</v>
+        <v>7075</v>
       </c>
       <c r="D3730" s="0" t="s">
         <v>15</v>
@@ -73962,10 +73956,10 @@
         <v>3742</v>
       </c>
       <c r="B3731" s="0" t="s">
-        <v>7078</v>
+        <v>7076</v>
       </c>
       <c r="C3731" s="0" t="s">
-        <v>7079</v>
+        <v>7077</v>
       </c>
       <c r="D3731" s="0" t="s">
         <v>15</v>
@@ -73976,10 +73970,10 @@
         <v>3743</v>
       </c>
       <c r="B3732" s="0" t="s">
-        <v>7080</v>
+        <v>7078</v>
       </c>
       <c r="C3732" s="0" t="s">
-        <v>7081</v>
+        <v>7079</v>
       </c>
       <c r="D3732" s="0" t="s">
         <v>15</v>
@@ -73990,10 +73984,10 @@
         <v>3744</v>
       </c>
       <c r="B3733" s="0" t="s">
-        <v>7082</v>
+        <v>7080</v>
       </c>
       <c r="C3733" s="0" t="s">
-        <v>7083</v>
+        <v>7081</v>
       </c>
       <c r="D3733" s="0" t="s">
         <v>15</v>
@@ -74004,10 +73998,10 @@
         <v>3745</v>
       </c>
       <c r="B3734" s="0" t="s">
-        <v>7084</v>
+        <v>7082</v>
       </c>
       <c r="C3734" s="0" t="s">
-        <v>7085</v>
+        <v>7083</v>
       </c>
       <c r="D3734" s="0" t="s">
         <v>15</v>
@@ -74018,10 +74012,10 @@
         <v>3746</v>
       </c>
       <c r="B3735" s="0" t="s">
-        <v>7086</v>
+        <v>7084</v>
       </c>
       <c r="C3735" s="0" t="s">
-        <v>7087</v>
+        <v>7085</v>
       </c>
       <c r="D3735" s="0" t="s">
         <v>15</v>
@@ -74032,10 +74026,10 @@
         <v>3747</v>
       </c>
       <c r="B3736" s="0" t="s">
-        <v>7088</v>
+        <v>7086</v>
       </c>
       <c r="C3736" s="0" t="s">
-        <v>7089</v>
+        <v>7087</v>
       </c>
       <c r="D3736" s="0" t="s">
         <v>15</v>
@@ -74046,10 +74040,10 @@
         <v>3748</v>
       </c>
       <c r="B3737" s="0" t="s">
-        <v>7090</v>
+        <v>7088</v>
       </c>
       <c r="C3737" s="0" t="s">
-        <v>7091</v>
+        <v>7089</v>
       </c>
       <c r="D3737" s="0" t="s">
         <v>15</v>
@@ -74060,10 +74054,10 @@
         <v>3749</v>
       </c>
       <c r="B3738" s="0" t="s">
-        <v>7092</v>
+        <v>7090</v>
       </c>
       <c r="C3738" s="0" t="s">
-        <v>7093</v>
+        <v>7091</v>
       </c>
       <c r="D3738" s="0" t="s">
         <v>15</v>
@@ -74074,10 +74068,10 @@
         <v>3750</v>
       </c>
       <c r="B3739" s="0" t="s">
-        <v>7094</v>
+        <v>7092</v>
       </c>
       <c r="C3739" s="0" t="s">
-        <v>7095</v>
+        <v>7093</v>
       </c>
       <c r="D3739" s="0" t="s">
         <v>15</v>
@@ -74088,10 +74082,10 @@
         <v>3751</v>
       </c>
       <c r="B3740" s="0" t="s">
-        <v>7096</v>
+        <v>7094</v>
       </c>
       <c r="C3740" s="0" t="s">
-        <v>7097</v>
+        <v>7095</v>
       </c>
       <c r="D3740" s="0" t="s">
         <v>15</v>
@@ -74102,10 +74096,10 @@
         <v>3752</v>
       </c>
       <c r="B3741" s="0" t="s">
-        <v>7098</v>
+        <v>7096</v>
       </c>
       <c r="C3741" s="0" t="s">
-        <v>7099</v>
+        <v>7097</v>
       </c>
       <c r="D3741" s="0" t="s">
         <v>15</v>
@@ -74116,10 +74110,10 @@
         <v>3753</v>
       </c>
       <c r="B3742" s="0" t="s">
-        <v>7100</v>
+        <v>7098</v>
       </c>
       <c r="C3742" s="0" t="s">
-        <v>7101</v>
+        <v>7099</v>
       </c>
       <c r="D3742" s="0" t="s">
         <v>15</v>
@@ -74130,10 +74124,10 @@
         <v>3754</v>
       </c>
       <c r="B3743" s="0" t="s">
-        <v>7102</v>
+        <v>7100</v>
       </c>
       <c r="C3743" s="0" t="s">
-        <v>7103</v>
+        <v>7101</v>
       </c>
       <c r="D3743" s="0" t="s">
         <v>15</v>
@@ -74144,10 +74138,10 @@
         <v>3755</v>
       </c>
       <c r="B3744" s="0" t="s">
-        <v>7104</v>
+        <v>7102</v>
       </c>
       <c r="C3744" s="0" t="s">
-        <v>7105</v>
+        <v>7103</v>
       </c>
       <c r="D3744" s="0" t="s">
         <v>15</v>
@@ -74158,10 +74152,10 @@
         <v>3756</v>
       </c>
       <c r="B3745" s="0" t="s">
-        <v>7106</v>
+        <v>7104</v>
       </c>
       <c r="C3745" s="0" t="s">
-        <v>7107</v>
+        <v>7105</v>
       </c>
       <c r="D3745" s="0" t="s">
         <v>15</v>
@@ -74172,10 +74166,10 @@
         <v>3757</v>
       </c>
       <c r="B3746" s="0" t="s">
-        <v>7108</v>
+        <v>7106</v>
       </c>
       <c r="C3746" s="0" t="s">
-        <v>7109</v>
+        <v>7107</v>
       </c>
       <c r="D3746" s="0" t="s">
         <v>15</v>
@@ -74186,10 +74180,10 @@
         <v>3758</v>
       </c>
       <c r="B3747" s="0" t="s">
-        <v>7110</v>
+        <v>7108</v>
       </c>
       <c r="C3747" s="0" t="s">
-        <v>7111</v>
+        <v>7109</v>
       </c>
       <c r="D3747" s="0" t="s">
         <v>15</v>
@@ -74200,10 +74194,10 @@
         <v>3759</v>
       </c>
       <c r="B3748" s="0" t="s">
-        <v>7112</v>
+        <v>7110</v>
       </c>
       <c r="C3748" s="0" t="s">
-        <v>7113</v>
+        <v>7111</v>
       </c>
       <c r="D3748" s="0" t="s">
         <v>15</v>
@@ -74214,10 +74208,10 @@
         <v>3760</v>
       </c>
       <c r="B3749" s="0" t="s">
-        <v>7114</v>
+        <v>7112</v>
       </c>
       <c r="C3749" s="0" t="s">
-        <v>7113</v>
+        <v>7111</v>
       </c>
       <c r="D3749" s="0" t="s">
         <v>15</v>
@@ -74228,10 +74222,10 @@
         <v>3761</v>
       </c>
       <c r="B3750" s="0" t="s">
-        <v>7115</v>
+        <v>7113</v>
       </c>
       <c r="C3750" s="0" t="s">
-        <v>7116</v>
+        <v>7114</v>
       </c>
       <c r="D3750" s="0" t="s">
         <v>15</v>
@@ -74242,10 +74236,10 @@
         <v>3762</v>
       </c>
       <c r="B3751" s="0" t="s">
-        <v>7117</v>
+        <v>7115</v>
       </c>
       <c r="C3751" s="0" t="s">
-        <v>7118</v>
+        <v>7116</v>
       </c>
       <c r="D3751" s="0" t="s">
         <v>15</v>
@@ -74256,10 +74250,10 @@
         <v>3763</v>
       </c>
       <c r="B3752" s="0" t="s">
-        <v>7119</v>
+        <v>7117</v>
       </c>
       <c r="C3752" s="0" t="s">
-        <v>7120</v>
+        <v>7118</v>
       </c>
       <c r="D3752" s="0" t="s">
         <v>15</v>
@@ -74270,10 +74264,10 @@
         <v>3764</v>
       </c>
       <c r="B3753" s="0" t="s">
-        <v>7121</v>
+        <v>7119</v>
       </c>
       <c r="C3753" s="0" t="s">
-        <v>7122</v>
+        <v>7120</v>
       </c>
       <c r="D3753" s="0" t="s">
         <v>15</v>
@@ -74284,10 +74278,10 @@
         <v>3765</v>
       </c>
       <c r="B3754" s="0" t="s">
-        <v>7123</v>
+        <v>7121</v>
       </c>
       <c r="C3754" s="0" t="s">
-        <v>7124</v>
+        <v>7122</v>
       </c>
       <c r="D3754" s="0" t="s">
         <v>15</v>
@@ -74298,10 +74292,10 @@
         <v>3766</v>
       </c>
       <c r="B3755" s="0" t="s">
-        <v>7125</v>
+        <v>7123</v>
       </c>
       <c r="C3755" s="0" t="s">
-        <v>7126</v>
+        <v>7124</v>
       </c>
       <c r="D3755" s="0" t="s">
         <v>15</v>
@@ -74312,10 +74306,10 @@
         <v>3767</v>
       </c>
       <c r="B3756" s="0" t="s">
-        <v>7127</v>
+        <v>7125</v>
       </c>
       <c r="C3756" s="0" t="s">
-        <v>7128</v>
+        <v>7126</v>
       </c>
       <c r="D3756" s="0" t="s">
         <v>15</v>
@@ -74326,10 +74320,10 @@
         <v>3768</v>
       </c>
       <c r="B3757" s="0" t="s">
-        <v>7129</v>
+        <v>7127</v>
       </c>
       <c r="C3757" s="0" t="s">
-        <v>7130</v>
+        <v>7128</v>
       </c>
       <c r="D3757" s="0" t="s">
         <v>15</v>
@@ -74340,10 +74334,10 @@
         <v>3769</v>
       </c>
       <c r="B3758" s="0" t="s">
-        <v>7131</v>
+        <v>7129</v>
       </c>
       <c r="C3758" s="0" t="s">
-        <v>7132</v>
+        <v>7130</v>
       </c>
       <c r="D3758" s="0" t="s">
         <v>15</v>
@@ -74354,10 +74348,10 @@
         <v>3770</v>
       </c>
       <c r="B3759" s="0" t="s">
-        <v>7133</v>
+        <v>7131</v>
       </c>
       <c r="C3759" s="0" t="s">
-        <v>7134</v>
+        <v>7132</v>
       </c>
       <c r="D3759" s="0" t="s">
         <v>15</v>
@@ -74368,10 +74362,10 @@
         <v>3771</v>
       </c>
       <c r="B3760" s="0" t="s">
-        <v>7135</v>
+        <v>7133</v>
       </c>
       <c r="C3760" s="0" t="s">
-        <v>7135</v>
+        <v>7133</v>
       </c>
       <c r="D3760" s="0" t="s">
         <v>15</v>
@@ -74382,10 +74376,10 @@
         <v>3772</v>
       </c>
       <c r="B3761" s="0" t="s">
-        <v>7136</v>
+        <v>7134</v>
       </c>
       <c r="C3761" s="0" t="s">
-        <v>7137</v>
+        <v>7135</v>
       </c>
       <c r="D3761" s="0" t="s">
         <v>15</v>
@@ -74396,10 +74390,10 @@
         <v>3773</v>
       </c>
       <c r="B3762" s="0" t="s">
-        <v>7138</v>
+        <v>7136</v>
       </c>
       <c r="C3762" s="0" t="s">
-        <v>7139</v>
+        <v>7137</v>
       </c>
       <c r="D3762" s="0" t="s">
         <v>15</v>
@@ -74410,10 +74404,10 @@
         <v>3774</v>
       </c>
       <c r="B3763" s="0" t="s">
-        <v>7140</v>
+        <v>7138</v>
       </c>
       <c r="C3763" s="0" t="s">
-        <v>7141</v>
+        <v>7139</v>
       </c>
       <c r="D3763" s="0" t="s">
         <v>15</v>
@@ -74424,10 +74418,10 @@
         <v>3775</v>
       </c>
       <c r="B3764" s="0" t="s">
-        <v>7142</v>
+        <v>7140</v>
       </c>
       <c r="C3764" s="0" t="s">
-        <v>7143</v>
+        <v>7141</v>
       </c>
       <c r="D3764" s="0" t="s">
         <v>15</v>
@@ -74438,10 +74432,10 @@
         <v>3776</v>
       </c>
       <c r="B3765" s="0" t="s">
-        <v>7144</v>
+        <v>7142</v>
       </c>
       <c r="C3765" s="0" t="s">
-        <v>7145</v>
+        <v>7143</v>
       </c>
       <c r="D3765" s="0" t="s">
         <v>15</v>
@@ -74452,10 +74446,10 @@
         <v>3777</v>
       </c>
       <c r="B3766" s="0" t="s">
-        <v>7146</v>
+        <v>7144</v>
       </c>
       <c r="C3766" s="0" t="s">
-        <v>7147</v>
+        <v>7145</v>
       </c>
       <c r="D3766" s="0" t="s">
         <v>15</v>
@@ -74466,10 +74460,10 @@
         <v>3778</v>
       </c>
       <c r="B3767" s="0" t="s">
-        <v>7148</v>
+        <v>7146</v>
       </c>
       <c r="C3767" s="0" t="s">
-        <v>7149</v>
+        <v>7147</v>
       </c>
       <c r="D3767" s="0" t="s">
         <v>15</v>
@@ -74480,10 +74474,10 @@
         <v>3779</v>
       </c>
       <c r="B3768" s="0" t="s">
-        <v>7150</v>
+        <v>7148</v>
       </c>
       <c r="C3768" s="0" t="s">
-        <v>7150</v>
+        <v>7148</v>
       </c>
       <c r="D3768" s="0" t="s">
         <v>15</v>
@@ -74494,10 +74488,10 @@
         <v>3780</v>
       </c>
       <c r="B3769" s="0" t="s">
-        <v>7151</v>
+        <v>7149</v>
       </c>
       <c r="C3769" s="0" t="s">
-        <v>7151</v>
+        <v>7149</v>
       </c>
       <c r="D3769" s="0" t="s">
         <v>15</v>
@@ -74508,10 +74502,10 @@
         <v>3781</v>
       </c>
       <c r="B3770" s="0" t="s">
-        <v>7152</v>
+        <v>7150</v>
       </c>
       <c r="C3770" s="0" t="s">
-        <v>7153</v>
+        <v>7151</v>
       </c>
       <c r="D3770" s="0" t="s">
         <v>15</v>
@@ -74522,10 +74516,10 @@
         <v>3782</v>
       </c>
       <c r="B3771" s="0" t="s">
-        <v>7154</v>
+        <v>7152</v>
       </c>
       <c r="C3771" s="0" t="s">
-        <v>7155</v>
+        <v>7153</v>
       </c>
       <c r="D3771" s="0" t="s">
         <v>15</v>
@@ -74536,10 +74530,10 @@
         <v>3783</v>
       </c>
       <c r="B3772" s="0" t="s">
-        <v>7156</v>
+        <v>7154</v>
       </c>
       <c r="C3772" s="0" t="s">
-        <v>7156</v>
+        <v>7154</v>
       </c>
       <c r="D3772" s="0" t="s">
         <v>15</v>
@@ -74550,10 +74544,10 @@
         <v>3784</v>
       </c>
       <c r="B3773" s="0" t="s">
-        <v>7157</v>
+        <v>7155</v>
       </c>
       <c r="C3773" s="0" t="s">
-        <v>7158</v>
+        <v>7156</v>
       </c>
       <c r="D3773" s="0" t="s">
         <v>15</v>
@@ -74564,10 +74558,10 @@
         <v>3785</v>
       </c>
       <c r="B3774" s="0" t="s">
-        <v>7159</v>
+        <v>7157</v>
       </c>
       <c r="C3774" s="0" t="s">
-        <v>7160</v>
+        <v>7158</v>
       </c>
       <c r="D3774" s="0" t="s">
         <v>15</v>
@@ -74578,10 +74572,10 @@
         <v>3786</v>
       </c>
       <c r="B3775" s="0" t="s">
-        <v>7161</v>
+        <v>7159</v>
       </c>
       <c r="C3775" s="0" t="s">
-        <v>7162</v>
+        <v>7160</v>
       </c>
       <c r="D3775" s="0" t="s">
         <v>15</v>
@@ -74592,10 +74586,10 @@
         <v>3787</v>
       </c>
       <c r="B3776" s="0" t="s">
-        <v>7163</v>
+        <v>7161</v>
       </c>
       <c r="C3776" s="0" t="s">
-        <v>7163</v>
+        <v>7161</v>
       </c>
       <c r="D3776" s="0" t="s">
         <v>15</v>
@@ -74606,10 +74600,10 @@
         <v>3788</v>
       </c>
       <c r="B3777" s="0" t="s">
-        <v>7164</v>
+        <v>7162</v>
       </c>
       <c r="C3777" s="0" t="s">
-        <v>7165</v>
+        <v>7163</v>
       </c>
       <c r="D3777" s="0" t="s">
         <v>15</v>
@@ -74620,10 +74614,10 @@
         <v>3789</v>
       </c>
       <c r="B3778" s="0" t="s">
-        <v>7166</v>
+        <v>7164</v>
       </c>
       <c r="C3778" s="0" t="s">
-        <v>7167</v>
+        <v>7165</v>
       </c>
       <c r="D3778" s="0" t="s">
         <v>15</v>
@@ -74634,10 +74628,10 @@
         <v>3790</v>
       </c>
       <c r="B3779" s="0" t="s">
-        <v>7168</v>
+        <v>7166</v>
       </c>
       <c r="C3779" s="0" t="s">
-        <v>7169</v>
+        <v>7167</v>
       </c>
       <c r="D3779" s="0" t="s">
         <v>15</v>
@@ -74648,10 +74642,10 @@
         <v>3792</v>
       </c>
       <c r="B3780" s="0" t="s">
-        <v>7170</v>
+        <v>7168</v>
       </c>
       <c r="C3780" s="0" t="s">
-        <v>7171</v>
+        <v>7169</v>
       </c>
       <c r="D3780" s="0" t="s">
         <v>15</v>
@@ -74662,10 +74656,10 @@
         <v>3791</v>
       </c>
       <c r="B3781" s="0" t="s">
-        <v>7172</v>
+        <v>7170</v>
       </c>
       <c r="C3781" s="0" t="s">
-        <v>7173</v>
+        <v>7171</v>
       </c>
       <c r="D3781" s="0" t="s">
         <v>15</v>
@@ -74676,10 +74670,10 @@
         <v>3793</v>
       </c>
       <c r="B3782" s="0" t="s">
-        <v>7174</v>
+        <v>7172</v>
       </c>
       <c r="C3782" s="0" t="s">
-        <v>7175</v>
+        <v>7173</v>
       </c>
       <c r="D3782" s="0" t="s">
         <v>15</v>
@@ -74690,10 +74684,10 @@
         <v>3794</v>
       </c>
       <c r="B3783" s="0" t="s">
-        <v>7176</v>
+        <v>7174</v>
       </c>
       <c r="C3783" s="0" t="s">
-        <v>7177</v>
+        <v>7175</v>
       </c>
       <c r="D3783" s="0" t="s">
         <v>15</v>
@@ -74704,10 +74698,10 @@
         <v>3795</v>
       </c>
       <c r="B3784" s="0" t="s">
-        <v>7178</v>
+        <v>7176</v>
       </c>
       <c r="C3784" s="0" t="s">
-        <v>7179</v>
+        <v>7177</v>
       </c>
       <c r="D3784" s="0" t="s">
         <v>15</v>
@@ -74718,10 +74712,10 @@
         <v>3796</v>
       </c>
       <c r="B3785" s="0" t="s">
-        <v>7180</v>
+        <v>7178</v>
       </c>
       <c r="C3785" s="0" t="s">
-        <v>7181</v>
+        <v>7179</v>
       </c>
       <c r="D3785" s="0" t="s">
         <v>15</v>
@@ -74732,10 +74726,10 @@
         <v>3797</v>
       </c>
       <c r="B3786" s="0" t="s">
-        <v>7182</v>
+        <v>7180</v>
       </c>
       <c r="C3786" s="0" t="s">
-        <v>7183</v>
+        <v>7181</v>
       </c>
       <c r="D3786" s="0" t="s">
         <v>15</v>
@@ -74746,10 +74740,10 @@
         <v>3798</v>
       </c>
       <c r="B3787" s="0" t="s">
-        <v>7184</v>
+        <v>7182</v>
       </c>
       <c r="C3787" s="0" t="s">
-        <v>7185</v>
+        <v>7183</v>
       </c>
       <c r="D3787" s="0" t="s">
         <v>15</v>
@@ -74760,10 +74754,10 @@
         <v>3799</v>
       </c>
       <c r="B3788" s="0" t="s">
-        <v>7186</v>
+        <v>7184</v>
       </c>
       <c r="C3788" s="0" t="s">
-        <v>7187</v>
+        <v>7185</v>
       </c>
       <c r="D3788" s="0" t="s">
         <v>15</v>
@@ -74774,10 +74768,10 @@
         <v>3800</v>
       </c>
       <c r="B3789" s="0" t="s">
-        <v>7188</v>
+        <v>7186</v>
       </c>
       <c r="C3789" s="0" t="s">
-        <v>7189</v>
+        <v>7187</v>
       </c>
       <c r="D3789" s="0" t="s">
         <v>15</v>
@@ -74788,10 +74782,10 @@
         <v>3801</v>
       </c>
       <c r="B3790" s="0" t="s">
-        <v>7190</v>
+        <v>7188</v>
       </c>
       <c r="C3790" s="0" t="s">
-        <v>7190</v>
+        <v>7188</v>
       </c>
       <c r="D3790" s="0" t="s">
         <v>15</v>
@@ -74802,10 +74796,10 @@
         <v>3802</v>
       </c>
       <c r="B3791" s="0" t="s">
-        <v>7191</v>
+        <v>7189</v>
       </c>
       <c r="C3791" s="0" t="s">
-        <v>7191</v>
+        <v>7189</v>
       </c>
       <c r="D3791" s="0" t="s">
         <v>15</v>
@@ -74816,10 +74810,10 @@
         <v>3803</v>
       </c>
       <c r="B3792" s="0" t="s">
-        <v>7192</v>
+        <v>7190</v>
       </c>
       <c r="C3792" s="0" t="s">
-        <v>7193</v>
+        <v>7191</v>
       </c>
       <c r="D3792" s="0" t="s">
         <v>15</v>
@@ -74830,10 +74824,10 @@
         <v>3804</v>
       </c>
       <c r="B3793" s="0" t="s">
-        <v>7194</v>
+        <v>7192</v>
       </c>
       <c r="C3793" s="0" t="s">
-        <v>7195</v>
+        <v>7193</v>
       </c>
       <c r="D3793" s="0" t="s">
         <v>15</v>
@@ -74844,10 +74838,10 @@
         <v>3805</v>
       </c>
       <c r="B3794" s="0" t="s">
-        <v>7196</v>
+        <v>7194</v>
       </c>
       <c r="C3794" s="0" t="s">
-        <v>7197</v>
+        <v>7195</v>
       </c>
       <c r="D3794" s="0" t="s">
         <v>15</v>
@@ -74858,10 +74852,10 @@
         <v>3806</v>
       </c>
       <c r="B3795" s="0" t="s">
-        <v>7198</v>
+        <v>7196</v>
       </c>
       <c r="C3795" s="0" t="s">
-        <v>7199</v>
+        <v>7197</v>
       </c>
       <c r="D3795" s="0" t="s">
         <v>15</v>
@@ -74872,10 +74866,10 @@
         <v>3807</v>
       </c>
       <c r="B3796" s="0" t="s">
-        <v>7200</v>
+        <v>7198</v>
       </c>
       <c r="C3796" s="0" t="s">
-        <v>7201</v>
+        <v>7199</v>
       </c>
       <c r="D3796" s="0" t="s">
         <v>15</v>
@@ -74886,10 +74880,10 @@
         <v>3808</v>
       </c>
       <c r="B3797" s="0" t="s">
-        <v>7202</v>
+        <v>7200</v>
       </c>
       <c r="C3797" s="0" t="s">
-        <v>7203</v>
+        <v>7201</v>
       </c>
       <c r="D3797" s="0" t="s">
         <v>15</v>
@@ -74900,10 +74894,10 @@
         <v>3809</v>
       </c>
       <c r="B3798" s="0" t="s">
-        <v>7204</v>
+        <v>7202</v>
       </c>
       <c r="C3798" s="0" t="s">
-        <v>7204</v>
+        <v>7202</v>
       </c>
       <c r="D3798" s="0" t="s">
         <v>15</v>
@@ -74914,10 +74908,10 @@
         <v>3810</v>
       </c>
       <c r="B3799" s="0" t="s">
-        <v>7205</v>
+        <v>7203</v>
       </c>
       <c r="C3799" s="0" t="s">
-        <v>7206</v>
+        <v>7204</v>
       </c>
       <c r="D3799" s="0" t="s">
         <v>15</v>
@@ -74928,10 +74922,10 @@
         <v>3811</v>
       </c>
       <c r="B3800" s="0" t="s">
-        <v>7207</v>
+        <v>7205</v>
       </c>
       <c r="C3800" s="0" t="s">
-        <v>7208</v>
+        <v>7206</v>
       </c>
       <c r="D3800" s="0" t="s">
         <v>15</v>
@@ -74942,10 +74936,10 @@
         <v>3812</v>
       </c>
       <c r="B3801" s="0" t="s">
-        <v>7209</v>
+        <v>7207</v>
       </c>
       <c r="C3801" s="0" t="s">
-        <v>7210</v>
+        <v>7208</v>
       </c>
       <c r="D3801" s="0" t="s">
         <v>15</v>
@@ -74956,10 +74950,10 @@
         <v>3813</v>
       </c>
       <c r="B3802" s="0" t="s">
-        <v>7211</v>
+        <v>7209</v>
       </c>
       <c r="C3802" s="0" t="s">
-        <v>7211</v>
+        <v>7209</v>
       </c>
       <c r="D3802" s="0" t="s">
         <v>15</v>
@@ -74970,10 +74964,10 @@
         <v>3814</v>
       </c>
       <c r="B3803" s="0" t="s">
-        <v>7212</v>
+        <v>7210</v>
       </c>
       <c r="C3803" s="0" t="s">
-        <v>7213</v>
+        <v>7211</v>
       </c>
       <c r="D3803" s="0" t="s">
         <v>15</v>
@@ -74984,10 +74978,10 @@
         <v>3815</v>
       </c>
       <c r="B3804" s="0" t="s">
-        <v>7214</v>
+        <v>7212</v>
       </c>
       <c r="C3804" s="0" t="s">
-        <v>7215</v>
+        <v>7213</v>
       </c>
       <c r="D3804" s="0" t="s">
         <v>15</v>
@@ -74998,10 +74992,10 @@
         <v>3816</v>
       </c>
       <c r="B3805" s="0" t="s">
-        <v>7216</v>
+        <v>7214</v>
       </c>
       <c r="C3805" s="0" t="s">
-        <v>7217</v>
+        <v>7215</v>
       </c>
       <c r="D3805" s="0" t="s">
         <v>15</v>
@@ -75012,10 +75006,10 @@
         <v>3817</v>
       </c>
       <c r="B3806" s="0" t="s">
-        <v>7218</v>
+        <v>7216</v>
       </c>
       <c r="C3806" s="0" t="s">
-        <v>7219</v>
+        <v>7217</v>
       </c>
       <c r="D3806" s="0" t="s">
         <v>15</v>
@@ -75026,10 +75020,10 @@
         <v>3818</v>
       </c>
       <c r="B3807" s="0" t="s">
-        <v>7220</v>
+        <v>7218</v>
       </c>
       <c r="C3807" s="0" t="s">
-        <v>7221</v>
+        <v>7219</v>
       </c>
       <c r="D3807" s="0" t="s">
         <v>15</v>
@@ -75040,10 +75034,10 @@
         <v>3819</v>
       </c>
       <c r="B3808" s="0" t="s">
-        <v>7222</v>
+        <v>7220</v>
       </c>
       <c r="C3808" s="0" t="s">
-        <v>7223</v>
+        <v>7221</v>
       </c>
       <c r="D3808" s="0" t="s">
         <v>15</v>
@@ -75054,10 +75048,10 @@
         <v>3820</v>
       </c>
       <c r="B3809" s="0" t="s">
-        <v>7224</v>
+        <v>7222</v>
       </c>
       <c r="C3809" s="0" t="s">
-        <v>7225</v>
+        <v>7223</v>
       </c>
       <c r="D3809" s="0" t="s">
         <v>15</v>
